--- a/data/latest_ransomware_news.xlsx
+++ b/data/latest_ransomware_news.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G14"/>
+  <dimension ref="A1:G17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -898,6 +898,105 @@
         <v>46011.59137731481</v>
       </c>
     </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Qilin</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>"Qilin ransomware" OR "Qilin threat actor" OR "Qilin cyber attack"</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Nissan confirms data compromise from Red Hat hack - SC Media</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>Tue, 23 Dec 2025 18:19:11 GMT</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMihgFBVV95cUxNLXR1V3lEZjBrd2h0TWF4REozNU83M2o5bUUxemY2eWh1Y3RQTngwYzktbW1JakpvdnN5NG10aGl1SG5zcjNSMG9TUWxMemJDWE9MTENyMG44aUlqbmNBVndZZHl2S2Rtbkh1d2l6NEdIcGxtLV9PaTMzTm9NbTd2OS1DdFMwUQ?oc=5</t>
+        </is>
+      </c>
+      <c r="F15" t="n">
+        <v>7</v>
+      </c>
+      <c r="G15" s="2" t="n">
+        <v>46014.76332175926</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Medusa</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>"Medusa ransomware" OR "Medusa threat actor" OR "Medusa cyber attack"</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>WordPress plugin auth bypass exploited almost immediately after disclosure - MSN</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>Tue, 23 Dec 2025 15:59:23 GMT</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMi9wJBVV95cUxOMldFd3JmaVBiM2lmSnNtMFhjOHRFUDZzVTdWd0hhSFZNMkR5a19hTEFIeEExUGZWcTRuTHNtXzdSbUJ2MVJxSzZhd0ZxVHBtUTRUTzZualVpQ2xUdzRQdWpFNndDZm4wd1dnWXZ3WUkwYi1tSVNuaWd2REdRbkthdUpXdjJadzNpVmNscE9ITTZlaFhHZVg1Y1dYbHNUUHNLb2NKQU9uME1Wd2w1bm1kR3NMSHJRUkhkUVBSR1B2QlJfVEF6UVZfUlJ3NjBuR1gxaVVONUQybEpKQy16bWFxcFJQR0dMbENnZzNoZVRuMzU2NHFCX1lBeU04WDV2WDBrZ2lROV81OVd5ZDZsemk2MEdHZUhiOG1GUUdvT0N1LTdRc2gxRWk4c3FzVkgyczNrT2s4NV91X1FaMEp1RmtDdC00YTRQaENlNjZ3ZnRuak81Mk5JZGEwWFY5Zzh6YkFpUVZFejV3M3d0Y3NvYko3WmtlUTBmNG8?oc=5</t>
+        </is>
+      </c>
+      <c r="F16" t="n">
+        <v>7</v>
+      </c>
+      <c r="G16" s="2" t="n">
+        <v>46014.66623842593</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Medusa</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>"Medusa ransomware" OR "Medusa threat actor" OR "Medusa cyber attack"</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>CISA loses key employee behind early ransomware warnings - itsecuritynews.info</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>Tue, 23 Dec 2025 16:02:53 GMT</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMikwFBVV95cUxQYnNvUnJieV9TaVdiSEFzRTJobUxaam1XOG82d3lZRktPSEJnWVhRNlY0VEJ0Q25QMi16bzhHa0NIX0FKNWRrVXUteTZGeXJ1NmItNHhfN1FxeHEyNkNNYzdDb2pVcG14VXEwc25hNU84Zm5iN1VDcTNTTkltUEZXdU5aZEVab2NYaVl5QnpraTk5R0k?oc=5</t>
+        </is>
+      </c>
+      <c r="F17" t="n">
+        <v>7</v>
+      </c>
+      <c r="G17" s="2" t="n">
+        <v>46014.66866898148</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/latest_ransomware_news.xlsx
+++ b/data/latest_ransomware_news.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G17"/>
+  <dimension ref="A1:G32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -997,6 +997,501 @@
         <v>46014.66866898148</v>
       </c>
     </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Dragonforce</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>"Dragonforce ransomware" OR "Dragonforce threat actor" OR "Dragonforce cyber attack"</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>How the UK Retail Sector Responded to the Scattered Spider Hack Wave - Infosecurity Magazine</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>Tue, 30 Dec 2025 10:00:00 GMT</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMijwFBVV95cUxQWGttVDRCa2pLcnF3MWFIZnhhR3N6UGFaLWdxYWxEbGRmemRNNFFsc2NHelNSM21SbDJfcEh2WHM5eXY0b0NWSVYza2V5RzFRenh5eWhoTTJBSG1MV3Y4YTB1VkJla1RuWGRFQzQ2ZUgyWS1XcGdFTGZaZnBndEg0NmlaZ2Vzem94WVVoREdSNA?oc=5</t>
+        </is>
+      </c>
+      <c r="F18" t="n">
+        <v>7</v>
+      </c>
+      <c r="G18" s="2" t="n">
+        <v>46021.41666666666</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Qilin</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>"Qilin ransomware" OR "Qilin threat actor" OR "Qilin cyber attack"</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Micro Focus Data Breach Lawsuit Investigation - Claim Depot</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>Sat, 27 Dec 2025 15:08:41 GMT</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiekFVX3lxTE5iV29GLVhac2VNcmM0OWRrbzNDRFM1T0otRlhMZUdLRkd1MHBtZDlCMUNNby1FOTdnMFhCVXFyOHR3THpyNWNDeF9oSkNYeWlxaDN3WEtVMVRRTHpzekR0UEp6MllYSFd2SWJGcE1VNjdaV3MwLWktWU53?oc=5</t>
+        </is>
+      </c>
+      <c r="F19" t="n">
+        <v>7</v>
+      </c>
+      <c r="G19" s="2" t="n">
+        <v>46018.63103009259</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Akira</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>"Akira ransomware" OR "Akira threat actor" OR "Akira cyber attack"</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Best of 2025: New Akira Ransomware Decryptor Leans on Nvidia GPU Power - Security Boulevard</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>Thu, 25 Dec 2025 15:05:36 GMT</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMingFBVV95cUxNaFE4Uld2cXBqQ29PWHQtWVpHNm5lZ250WTZkYWY3WnR6WHZnU2RLUkV2b3BVY1FmamY5dGRIdjRjYmlIQkg4d3NIRllFXzNLN01UQ3FTb203aEV6dlIyU2ZHcTJyRU5feEVRSDhUY0dkc1lYbW5HcnRzMVZ6SzFVaVIxaE1zcUNVWklDZmRaZ2hSTW0wUl83dC1tZ3NiUQ?oc=5</t>
+        </is>
+      </c>
+      <c r="F20" t="n">
+        <v>7</v>
+      </c>
+      <c r="G20" s="2" t="n">
+        <v>46016.62888888889</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Akira</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>"Akira ransomware" OR "Akira threat actor" OR "Akira cyber attack"</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Fintech firm Marquis alerts dozens of US banks and credit unions of a data breach after ransomware attack - MSN</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>Tue, 30 Dec 2025 09:58:27 GMT</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMilAJBVV95cUxOOUk2VVVyWDFPajVuX01MVnJZaXJlenlrc0Y2cGRmamI4MUxMREswZ2J6S1gwMDNWN2lQZjFvYlVveWVOc3g1WFRTVlF4S0w3ZVFRWnV6MkxoVTFHRHl5elBWODg2bVNtR3hfNXhaVHFoSm13UXM3aVZtbXVGZ3h0M3dtUVVzdUZaSVRuNXhuSlZoRUdEVERleS1nWUlSbFFPWkwwQzktWmVjbEpfLTlNLXVEMEFiajFtVU1vZDRmekViYlFOSW96RUtGNGdyVU52Mk9kaF9LbVFTdktRNGRvRDhyWXFDSDhOZ2puVGVnWGEwbURhMm9fMFZ4cE5vcWZ4UVNQTXAweHR3SHJZcWZ3TzZxdlU?oc=5</t>
+        </is>
+      </c>
+      <c r="F21" t="n">
+        <v>7</v>
+      </c>
+      <c r="G21" s="2" t="n">
+        <v>46021.41559027778</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Everest</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>"Everest ransomware" OR "Everest threat actor" OR "Everest cyber attack"</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Chrysler allegedly compromised by Everest ransomware gang - SC Media</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>Mon, 29 Dec 2025 15:05:30 GMT</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMikAFBVV95cUxOMkhlQnVKNnFRU1RWM2NPLWE0SFk2clhzRmpuek8xTWVYaEczOU9COUZZcWkxMlZ6V2RSNzNxSGxRdThtZzdOak1TeUg0VXp5bG1IOGZJMlotTVpYVjdWd3VNT0c4WXRMZG9TT3hqYkgyOEJ1NzZadG51WElXcHM5NlRwQVM0ZXdCRm5vZDU2bGE?oc=5</t>
+        </is>
+      </c>
+      <c r="F22" t="n">
+        <v>7</v>
+      </c>
+      <c r="G22" s="2" t="n">
+        <v>46020.62881944444</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Lynx</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>"Lynx ransomware" OR "Lynx threat actor" OR "Lynx cyber attack"</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>CSA Tax &amp; Advisory hack claimed by Lynx ransomware - SC Media</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>Tue, 30 Dec 2025 16:20:51 GMT</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMihAFBVV95cUxORVZyS1VFR290dFRub0FuVzhvNmowcDhTUHZ3a0R3VTFpSDR4NHdtYTU0dWVxbHJneGcwN0VWemFJUTg5RHgtQlF3Z3ZuUVc0ZW9JeEFoMDJ6MWJSdDZYNmNIb3NBeXhIMnNRNGxDd0VYSEM3Mm1kaUhUb2taWmg1eHkyTnQ?oc=5</t>
+        </is>
+      </c>
+      <c r="F23" t="n">
+        <v>7</v>
+      </c>
+      <c r="G23" s="2" t="n">
+        <v>46021.68114583333</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Lynx</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>"Lynx ransomware" OR "Lynx threat actor" OR "Lynx cyber attack"</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Hackers claim tax data theft just weeks before filing season - Cybernews</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>Mon, 29 Dec 2025 11:18:59 GMT</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMib0FVX3lxTFBRTndqanlFX29EX1hSZUdWVmhVaGNfdWhxbGVXZlBvSkpXWU1PT3NfajdlbHVLWmdUWnBpM0JjYUxEUjJBQ3FrYU1EbEs5dnN4UXd3Q2k0SHI5TURvQkd3c0NVVVNBQTBHc2tXUVdKcw?oc=5</t>
+        </is>
+      </c>
+      <c r="F24" t="n">
+        <v>7</v>
+      </c>
+      <c r="G24" s="2" t="n">
+        <v>46020.4715162037</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>TheGentlemen</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>"The Gentlemen ransomware" OR "The Gentlemen threat actor" OR "The Gentlemen cyber attack"</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Romanian energy provider hit by Gentlemen ransomware attack - BleepingComputer</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>Mon, 29 Dec 2025 14:26:00 GMT</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMisAFBVV95cUxPMHREd2xWYmJSSDBCZFdlRG02WmNfbkJfRmJlT1RhVkpLRUVHUnZtMHVVU2pueFlBbkFHbmVrUHJOdm1nM3NhSzd4WkJNR2lRREdmLUlDNE92WnJFRTc3QWZTbGU3dW4zcExBU2xLUnlWZ193a0ZqQ25WaFZUM2ptQzlxcHZDQlZadU1yaEM2Njc1TTZEcnlQMlpaQ2pDNWRtYVRlYjJjemlqTDctc0tkTdIBsAFBVV95cUxPMHREd2xWYmJSSDBCZFdlRG02WmNfbkJfRmJlT1RhVkpLRUVHUnZtMHVVU2pueFlBbkFHbmVrUHJOdm1nM3NhSzd4WkJNR2lRREdmLUlDNE92WnJFRTc3QWZTbGU3dW4zcExBU2xLUnlWZ193a0ZqQ25WaFZUM2ptQzlxcHZDQlZadU1yaEM2Njc1TTZEcnlQMlpaQ2pDNWRtYVRlYjJjemlqTDctc0tkTQ?oc=5</t>
+        </is>
+      </c>
+      <c r="F25" t="n">
+        <v>7</v>
+      </c>
+      <c r="G25" s="2" t="n">
+        <v>46020.60138888889</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>Medusa</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>"Medusa ransomware" OR "Medusa threat actor" OR "Medusa cyber attack"</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Spyware combing for data 'of use to China' hidden inside religious and cultural apps - MSN</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>Mon, 29 Dec 2025 17:46:12 GMT</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMi6gJBVV95cUxPd1ZQeTlEX2djaHp1b0ZKcGcyRmtwOXE1c3FTZ1FJTHI3N0xFOGYtMTRuNlcwaXdOcmh2OFZFMXpOOWozQXh0dUU3Q0Jtd1NObFBvNF9ybjZzMjVPUW12OG56U1VGcTJvbVJqeHhoV19mLTdMOGtuajNyRjRCMFZtY3J5bFh2Zjl4cGtLRHBOTDZLNWIxS3ZmcTd1YzR2VXppRFQ2U2tobHVsbTN1UG85MjBaUzBra0dtNGs1djctcGhQOFpSdS1uODhOdnhlSVBCY0V0cWRKdjVNZUVqRUxBQ3VhVmkyLWN5LVhRTGdDNXJmTm5xXy1zVktFX0ViWERtNHNhZDQwMDJmcmVQa3k0alFQZ1BITzluMVEzRGx3WndENUFQRFlpRnNtaS1aclIxd1FxVnllajBOOVFRSTQ3aGh2MHBNWVZjdUF0S1VaeElSMlgtdWhuNV9Nc1BHT3U5WXRiQWMyR2VzQQ?oc=5</t>
+        </is>
+      </c>
+      <c r="F26" t="n">
+        <v>7</v>
+      </c>
+      <c r="G26" s="2" t="n">
+        <v>46020.74041666667</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>Medusa</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>"Medusa ransomware" OR "Medusa threat actor" OR "Medusa cyber attack"</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Thousands of PostgreSQL servers are being hijacked to mine crypto - MSN</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>Mon, 29 Dec 2025 18:07:37 GMT</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMi9gJBVV95cUxPNjBacGxlU3RpWktab24wYjBSZ3VGV2V2OXVBZ1pRYkpnTndQdGNfRnA2WnRCZ0xMRllnbEpxNF9IdWNLZWNSd0E3blJMOGF0OFA0SXJTdzd0eG40VW9ueWdTQ3ZKcGJwMFFZU2liT0FQYVpGTlJvSERyWWNkV0RiZ3FsejI3OUlBWDdLRzRxMUc4c2xaUkktdTF6TGU2WktfSHJxdjZROXI2OHZtbThrVm5YWS1MYTlwOUFTdDFHZDFibjZRemFQbFM3alpHS3hDYzFXTURDV0VaOXVqTnJJMllvLW9tNkttaFlPd0FjaUdoSmpIT1Vocnd3eFVNamtvWExLY1pTVnowd09OWDFXSVN4REx6VnBWenRPLXFKNXlrLVoxVFVDLVZsUlpNRERDQlhaTDhXdEV0NHFrRFVYaVE4UzZxbTZUYUVPanJGZUNWNFdVQXVHOXRXbXoyeDA2UmNKM0hvdkQtcmZucjJra25oRnNkQQ?oc=5</t>
+        </is>
+      </c>
+      <c r="F27" t="n">
+        <v>7</v>
+      </c>
+      <c r="G27" s="2" t="n">
+        <v>46020.75528935185</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>Medusa</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>"Medusa ransomware" OR "Medusa threat actor" OR "Medusa cyber attack"</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Cyber Attack Rumors Swirl as NASCAR Faces $4 Million Ransom Demand - MSN</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>Fri, 26 Dec 2025 11:04:02 GMT</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMilANBVV95cUxPTUgwT0ptTkNIX2FVVW9TcnplLVhJZXhkNU5Fc0dUSGw3NFNBTjNRTFdISlJRWGN2eFVfTW9zUm14MDBaS21yNTBES1cxVlhGRDZ6YjFKSXNaQmlSMFB3Wm11eExtdU8tR3ZYdk1CR2tsYUhLejFjUG5jZ3p0ZmpNYW0zbndKN21wU2dtSWJZSU1oS2RjbWVhcS00bmRQMml3UXVIYXNMWDBHbHZ5WVRyNGpfUjVMVDAwYzV0dzlsQzRkRVF3RGxTNm9NOUVfSW1SRTZlV3VNMnJyakpScWxSenpqRGlDQXc0cHNtVVZPVmtzaXYtS2FoN3hCbWpGcmhidHlQX3oyNHJvSHgtMHQ2UXhCUTU0R3VmSmcwQ2oweHJhaXduUE5HX1ZCcy1ydUFwYjdEcnJXaTM1cUlIdWh1MUlFa1hqVVUybENmRFRHdE04THpEOGFkV1pjcEhpYzQxLVJhMm5OUHlqOWxwZHE4VWVIX2hmTjNVYjUtUEpLZUFVSnNOX3BCTXZCM1FFRTRCVjBNdg?oc=5</t>
+        </is>
+      </c>
+      <c r="F28" t="n">
+        <v>7</v>
+      </c>
+      <c r="G28" s="2" t="n">
+        <v>46017.46113425926</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>Cl0p</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>"Cl0p ransomware" OR "Cl0p threat actor" OR "Cl0p cyber attack"</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Phoenix U data breach exposes 3.4M victims in Oracle zero-day attacks by Cl0p gang - Cybernews</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>Thu, 25 Dec 2025 20:03:38 GMT</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMijwFBVV95cUxNSV9uS1RwMGVQSV9oZ2JCd2ZweFVlb1lZNkdrQVh5aDdUMFlpMW5XT3BEeFNNN2I0cFdZOW1fVDJFVUdGaHVBRWdyWEwyNm5wTW1wY2VvanFRY2t2d1ZwZnhvNDJxZ1B2X3dHV2gxR1VsbnVxa1BXS0JOcUtONUFENkpxR3d1WlA3bUlQRE9uUQ?oc=5</t>
+        </is>
+      </c>
+      <c r="F29" t="n">
+        <v>7</v>
+      </c>
+      <c r="G29" s="2" t="n">
+        <v>46016.83585648148</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>Cl0p</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>"Cl0p ransomware" OR "Cl0p threat actor" OR "Cl0p cyber attack"</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>Latest Oracle EBS Victims Include Korean Air, University of Phoenix - The Cyber Express</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>Tue, 30 Dec 2025 18:18:12 GMT</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMieEFVX3lxTE1yOGtqbzNGWk1vbHJ6U0hucmFFUU1KVHhfa1ZxSnFJTG5IQUJGYjRDd3h6Z3FqTmdDcGQ0aG5KcFg2UnM3Qzl1Z3M0ZU00ZlR6dUIyeXk4TDh5TTZ1VDV5OVpJbEpuZGFFbzlHUWFoX3pvU1R1SG5jdA?oc=5</t>
+        </is>
+      </c>
+      <c r="F30" t="n">
+        <v>7</v>
+      </c>
+      <c r="G30" s="2" t="n">
+        <v>46021.76263888889</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>Interlock</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>"Interlock ransomware" OR "Interlock threat actor" OR "Interlock cyber attack"</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>Salvation Army allegedly breached by Interlock ransomware - SC Media</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>Tue, 30 Dec 2025 16:18:48 GMT</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMikAFBVV95cUxPMHl0TG43VTR6ZmVxTzFpUjZNZUJhcXBDLXd5VmZPbm1ybXBOTzQ5blhKa2pyUVo5RHVPc0ZnSmF6ME9hT0xjYWVxV3FNU0htTklpMmtFNS1sODAySF84NDFpMGdSNkltMXB0ZEV5S0dJS2pUbXRZV0ktMmZhREJ2T2k4NzJKbEduNFRtTWdjYkY?oc=5</t>
+        </is>
+      </c>
+      <c r="F31" t="n">
+        <v>7</v>
+      </c>
+      <c r="G31" s="2" t="n">
+        <v>46021.67972222222</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>Safepay</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>"Safepay ransomware" OR "Safepay threat actor" OR "Safepay cyber attack"</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>Acronis Drives Security Momentum Through TRU Intelligence, Industry Recognition, and Platform Advancements - The Globe and Mail</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>Mon, 29 Dec 2025 13:54:05 GMT</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMimwJBVV95cUxPaWtBdzZpLWoyNHdpa0pSbDh3T2RWQ2ZzM3BXelpiMFZaRlgxM3RvakV3S2FkbUIxb3RNUlBESWdKTFJzZDJ4eUMwM3k5bExkLUpTMmtfQml6Ym5BczZ6OVNaVHd5Mkh5VUk3aXBjVEF4UVJDaEtHaHIzbVlyRXNwNzJBa3pFbHFGQ2U3Y21MelVVVERVdkU4ZUxoUmNLSTRUY0EwRmQteGRZTWtFeXFCLWJuX0M5c0lFRHNpQ2Y5cXo5elFKMDZLaldpN1hyS0hXLXc3TDVGVm9nVUhVSkZsamNIc2JtM21Yc1M1YmM2WDZPbTNLUDM3SlQ0QUhLQ0sxQTFzSG9kSnBibDh3YXdzNnVmYW1GRWNqNjhZ?oc=5</t>
+        </is>
+      </c>
+      <c r="F32" t="n">
+        <v>7</v>
+      </c>
+      <c r="G32" s="2" t="n">
+        <v>46020.57922453704</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/latest_ransomware_news.xlsx
+++ b/data/latest_ransomware_news.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G32"/>
+  <dimension ref="A1:G48"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1492,6 +1492,534 @@
         <v>46020.57922453704</v>
       </c>
     </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Dragonforce</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>"Dragonforce ransomware" OR "Dragonforce threat actor" OR "Dragonforce cyber attack"</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>Scattered Spider attacks cost UK retailers hundreds of millions - SC Media</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>Fri, 02 Jan 2026 16:30:06 GMT</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMimAFBVV95cUxNUFhPY0tzVDJKcHNNVElhNXBuSF9xU3F5NHlSZ0hELXhIOHlNeTJtTkhWQ0NtOGpLRUUydXUyZmt3N3FCU1lKRmFPc0lDbDkyX3FhUGRLV3ptOHhiajY2anB5WFhsSjVaQy1pLTExVU44dFdBaTc5My1NbTl1Zm9UcHZrQkxucGRoTmNwV2h3RzFlVFNZaVBaRQ?oc=5</t>
+        </is>
+      </c>
+      <c r="F33" t="n">
+        <v>7</v>
+      </c>
+      <c r="G33" s="2" t="n">
+        <v>46024.68756944445</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>Qilin</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>"Qilin ransomware" OR "Qilin threat actor" OR "Qilin cyber attack"</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Over 478K compromised in Covenant Health breach - SC Media</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>Mon, 05 Jan 2026 23:32:14 GMT</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMigwFBVV95cUxPV2lPYkNocERMY1h2cmFGbFpsTVhBZ0hlVEtMMWRtMU8tZzM3MWVpaW9IektzNVNRMy1VNDdWSGJ3MHVEVkNMV1dlQlFHYXIweGRaNXBLMmo0blZWZUZxOGxDTXZraS1udHNPenlxbWxiZUlQR2pEWXBUbzJsVFVraG1SNA?oc=5</t>
+        </is>
+      </c>
+      <c r="F34" t="n">
+        <v>7</v>
+      </c>
+      <c r="G34" s="2" t="n">
+        <v>46027.9807175926</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>Akira</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>"Akira ransomware" OR "Akira threat actor" OR "Akira cyber attack"</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Akira Ransomware Attack Exposes Data Of 7,600 At MetroWest Community FCU - CUToday</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>Wed, 31 Dec 2025 15:38:38 GMT</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMirgFBVV95cUxQU0RfcVpnZjJzdlpfRVQ1NDVyNnFWbk5qb2V3OUlTZUJUWkszaG90N0ppWjM1MjNUQi1SbElCRkx3RHkzV21SN1AyWEg1YmlGcVFtSDN1R05jOWdoOGUxYTJZMFhDMHllQ3JpNHN0eW1ITm5HeGx5UHk2Q2ltc0hRN05EOUFPaFpBMk1vMVBuMG0wc2NpMlBxWXg5NVctcUp1MXBicV9sdHcwVFFaMkE?oc=5</t>
+        </is>
+      </c>
+      <c r="F35" t="n">
+        <v>7</v>
+      </c>
+      <c r="G35" s="2" t="n">
+        <v>46022.6518287037</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>Akira</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>"Akira ransomware" OR "Akira threat actor" OR "Akira cyber attack"</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>Hackers spotted using unsecured webcam to launch cyberattack - MSN</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>Sun, 04 Jan 2026 19:59:10 GMT</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMizAJBVV95cUxOOTE1dFhiRXJfbTdkNXVadFRnX011ZHY3MFM0WE1PME1nSC1ZaEpYZUtsUDU1eTVSTnptc2p0ODBxZzk1YmlHNTBKNkF5MzhBYUpIb19wX2dOY3BIdzVRUDBKYlpDb19JR1h2T0VjZ0pPbERqcUZVNlVyeU5EOVBIQTNHQm5SMWdSUU9uVDd0SExwWmptVmNHYzdKR0tIREZJZzQ1RUtlMHhfLWdhNHdvVVhLUnhwZjU0LXZyMHBOV0N5X1FnWFgzR3phZjdmZ0MtRWFsRlNrXzZzX0VzWG1WZ3BrbWZMVDZXaElqWndkTDVkWF90ZF94OHB1ajVCbWtIT0NwTW5QaEpxMnVVVGQ5cGRNUndRSW9zMkNwWGJUVk5wTE8waGdhbVI2WjQ3dWpLcldUWXdTQ0MtYUlZVmNwNXZwaFN1YmNINUFkXw?oc=5</t>
+        </is>
+      </c>
+      <c r="F36" t="n">
+        <v>7</v>
+      </c>
+      <c r="G36" s="2" t="n">
+        <v>46026.83275462963</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>Akira</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>"Akira ransomware" OR "Akira threat actor" OR "Akira cyber attack"</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>Cerenade Data Breach: 100 GB of Sensitive Data Stolen - Claim Depot</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>Mon, 05 Jan 2026 20:20:55 GMT</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiYkFVX3lxTE15NzdGYjBfSS04TG5IVzE3NTQyeWR4WTk4UUpZUl9FNHRQR3M0NmRHeTlrQmI2b09ZaXdOQVdDY2t5U250ZVlXUTlqam9hamMtUzBWSGtIYnRJU2oyVHhxWFdn?oc=5</t>
+        </is>
+      </c>
+      <c r="F37" t="n">
+        <v>7</v>
+      </c>
+      <c r="G37" s="2" t="n">
+        <v>46027.8478587963</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Akira</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>"Akira ransomware" OR "Akira threat actor" OR "Akira cyber attack"</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>Apache OpenOffice says it wasn't hit by cyberattack - despite ransomware hacker claims - MSN</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>Tue, 06 Jan 2026 14:07:23 GMT</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMi8gFBVV95cUxOWHNocHpYZEJRcUpsd2lPOHViM1dSZ0NuM3ZxVF8wckZDZkZTLTB3Y3M1R1ZhRGszbk5aZFJvbU1SN19OTE5lUjQtd3JFVERucEZWRlhyYndPMFV4RW92ZTdUajBzR3lkSmZiWHE1YTh4ak0xWG5SS3pteGc2ZTM5anN6RUx3T2p1dm1aUFdubWpQOUNubXNWSXpsMFJmWjRDN1lhRWNrUy1uTE02bFFGMVh5eW1EZjIzV1piTkl3bWZQc29pdVl3cW83ZjRUYk4xZDhjTWE2VE9nQzU0dXJBdFpqeEJHNzFwVl9BVjhFQ0N4Zw?oc=5</t>
+        </is>
+      </c>
+      <c r="F38" t="n">
+        <v>7</v>
+      </c>
+      <c r="G38" s="2" t="n">
+        <v>46028.58846064815</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Everest</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>"Everest ransomware" OR "Everest threat actor" OR "Everest cyber attack"</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>Allegedly stolen ASUS data completely exposed by Everest ransomware - SC Media</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>Fri, 02 Jan 2026 15:14:03 GMT</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMingFBVV95cUxNbGZCYnpVakltenhfQWNPTnplRXZTM21MbmNfc05xYVdBVUJyenRMUVlJNVhGeWdwUEU0YVJlbEktT1pCaUx6OS1IVWlwZWRkYm01RG1CRmZPckNoYXBCTFE3WXczNE82R2ZyWlRWMUxidXM2SVFjcnNiaGEwWTVIYjhSQW82Qmh3MGQxMUk0bmlFNnVnTGFpRXpySk1FZw?oc=5</t>
+        </is>
+      </c>
+      <c r="F39" t="n">
+        <v>7</v>
+      </c>
+      <c r="G39" s="2" t="n">
+        <v>46024.63475694445</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>LockBit</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>"LockBit ransomware" OR "LockBit threat actor" OR "LockBit cyber attack"</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>British school closed indefinitely after major cyber incident - SC Media UK</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>Tue, 06 Jan 2026 13:26:07 GMT</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiqgFBVV95cUxPSGZla3I3dms5Ykt6YnpSLXBESTRsT09MMjdrcVdpc1BrQlhQRGFoODFfUERLWEN1U2kzNS1qM0J5Qk9PS21iVXNvdU5ZYWVUU0dWb05LeDctbU1ET2VTQkVaN1lBcm5lbllORmdYaF93SlUtNUQxSUlWTWVydXlMRXkyRXBlQUY3eUh5Y0pEc1Zta3RRQklmSTlQbUtKSEViNHBtTUZQTUZuQQ?oc=5</t>
+        </is>
+      </c>
+      <c r="F40" t="n">
+        <v>7</v>
+      </c>
+      <c r="G40" s="2" t="n">
+        <v>46028.55980324074</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>LockBit</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>"LockBit ransomware" OR "LockBit threat actor" OR "LockBit cyber attack"</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>EU vows to defend tech laws despite US retaliation threats - SC Media UK</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>Tue, 06 Jan 2026 13:26:08 GMT</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMipgFBVV95cUxQZUdqTlZSZEd3amJjYkQ4TUhNeVNJMldvMlM4VDVSeHJNSVFadWI0LWxxekxEbDg1TGx1NXpaMmVCQnlhRU9jLTk2UXJlVFFiOXd3dzJUYkJkSW1hUU1aVmJBUDItbHVqM3F3MHpMMHFLcE4zWmVfS1NZa0dPZDBpWkVyWmNsVEI1STJpR29XR1VhT0RNaVJwZjBwUEJIU3YwaWVyYWpR?oc=5</t>
+        </is>
+      </c>
+      <c r="F41" t="n">
+        <v>7</v>
+      </c>
+      <c r="G41" s="2" t="n">
+        <v>46028.55981481481</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Play</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>"Play ransomware" OR "Play threat actor" OR "Play cyber attack"</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>Play ransomware touts Garner Foods hack - SC Media</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>Mon, 05 Jan 2026 23:30:05 GMT</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMieEFVX3lxTE13U0RScEZ5RzJRdUhXSU93dTU0Tm5lOEQ5dTVQejQ0OTR5WncyYk1Ddzl4TGVFQlE0c0dkMFdRQ2NzSzBJT0tVbldSQ2N6X25sS0tGcXJRbFplUXJlRk1WWFdHd2R2OXJ6LUgybjdlbDVBT2JJcDRfRA?oc=5</t>
+        </is>
+      </c>
+      <c r="F42" t="n">
+        <v>7</v>
+      </c>
+      <c r="G42" s="2" t="n">
+        <v>46027.97922453703</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Play</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>"Play ransomware" OR "Play threat actor" OR "Play cyber attack"</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>DKNY licensee threatened by Russia-linked hackers - Cybernews</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>Fri, 02 Jan 2026 14:00:13 GMT</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMieEFVX3lxTE0yVDBSaTZmcXNFZG5FSUJEQm0xTm5yTF9tN3doRTZsQmpyYWRmYlZka1FRX3ZQa3MxeUw2V2V3akVCNnE5NVBtVW1waXRuTG9HaHJERnRzUnI3MmFUclNwcXJUMzhyVDdKQ2FjMnAwcHJHYl83bDg5eg?oc=5</t>
+        </is>
+      </c>
+      <c r="F43" t="n">
+        <v>7</v>
+      </c>
+      <c r="G43" s="2" t="n">
+        <v>46024.5834837963</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Medusa</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>"Medusa ransomware" OR "Medusa threat actor" OR "Medusa cyber attack"</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>Thousands of PostgreSQL servers are being hijacked to mine crypto - MSN</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>Tue, 06 Jan 2026 15:58:48 GMT</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMi0gJBVV95cUxPa01aTEdBam9iRENYUExhOXpJdVdYQk0xZWRFeEtjS0hXTlJBQWZTT3BlUzZOUUV4SExLMTZycnJ5cEtodWl6Wmp3Wk1QaEZDcm9Mcm5SMmxPdXJWWjFDMGdMRno4TXFZY1JDX29GZk1icm1QcWQtSWFrMkl3M3B2US1NODdiMmZpRDluM2NjamE0b1BKNHNtc0FxUmhCemtnekZwamVXM1YzRU5nYUJVM01OVTZCUmktNWJEWDZ2WVE1VFNGb3FxZk5taEZnT1N0d3IxT29YQXhiYUtObjVLV21BMG5wbTFia0dtU09xa1RVVG84Q2s5em5mT2pkdDhpdmwxa3gycncxX0xJMGpZZlI2M092LVBDREplWU53cXFEQXRzNkRtTkJlS1FqLW83YTJzM1ZKUjRoeVNtSE1vTm80UEo1OUFoU3lHcHFVNWtCZw?oc=5</t>
+        </is>
+      </c>
+      <c r="F44" t="n">
+        <v>7</v>
+      </c>
+      <c r="G44" s="2" t="n">
+        <v>46028.66583333333</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>Medusa</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>"Medusa ransomware" OR "Medusa threat actor" OR "Medusa cyber attack"</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>"Downfall" of 4chan? Infamous site hit with alleged hack as attackers cause major outage, leak source code - MSN</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>Fri, 02 Jan 2026 22:30:18 GMT</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMihANBVV95cUxOMDNyUUJwNXlHYV9iOTNMQWhmU2V2MUMzdnFvbEU5dmVRSW5Pa01QTDlYZUFhZDZvLU1SQWp0VTJXVVgtSnRWSTFaRWxxVndIMUsyYjZrNVlNM2d0WFdQbDM5dlZjMU5tWnFza0ltTnBxR3VqNjdfNTRNNVZGbDZkdERtQzJ0dE9Kd0RLbDNOcWJ4YVFOSkNMaC10dXpxNVRKWmMxSkRYMkkyM0lMdmtqRWRvMnB3MHRMLWNBQkVtQXdtM2FycllxREJGMW1WRkQtQjdlUElyN25BOXpfemF5MnpROW1jWUxrU3BvZzNkT3BqOTJRQ3F4NTJWTWxYZmk0eEdKMkhhRjZsd2R5Sk5HSmN6akZOeGR6amdsNE9MX0Q3T2trWVh2UXJvTXFXa01CaVM5ZERyOElmbjU1aThocC1OX0hMekRTWjJNNk5xa3hLUzZMUkk2NnlTNUpiRUhycEM0cG1rUWI4b1ZwR2JpMVNfZFhWdGJuYjRaMF9TazZCaWw3?oc=5</t>
+        </is>
+      </c>
+      <c r="F45" t="n">
+        <v>7</v>
+      </c>
+      <c r="G45" s="2" t="n">
+        <v>46024.93770833333</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Medusa</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>"Medusa ransomware" OR "Medusa threat actor" OR "Medusa cyber attack"</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>Cyber Attack Rumors Swirl as NASCAR Faces $4 Million Ransom Demand - MSN</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>Tue, 06 Jan 2026 08:31:13 GMT</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMikANBVV95cUxPckZJRGpfQVZhVW5VbVZVMUJqeVZCV2d2NlFzY1M1eFVRcXp1UWR2Y2MzMFd1dDVicVNHb3dmbzhrWVZKVXdlYUptWHRVVVNZbl8zdUZBYWJqc3E3aWZDTUctbGloYXozOHNIM3kwQmV0dUNFT2d0SVoxNy14V2JVdVUwemhvMTVYVGdvSXlsUzdYXy1Vb1F6VnFwd1d5dG1FRDdEbEh1TUUtWlRudVJrUGRpS0VNMExMRTcza1ZNWW9IQW9GSXpLVFI2WHlXRTkzWVVZaDBISWFlVmVCaW0tYU00LWR3OFZfZEdiUHdzeHNOWk1xeW5yVmFCUVJsU0JvbVZ3R3NSRmpsaWJ0MTNUNlJFRWxuZkQ3eFZfNGZIa1lPd1FGMHBYZGRaOHdxRTQ0R1BDaGU5dV9nUlBPVFlzdnVqY1lsbXoyYjVoWm9fQXdPLW5xNWoyckNQRXlpM2Y4cVVhRWd3bjFvWFNMa2dLb2ZpMTZtYVdwZF9jNUhGblB5QndtSmpXbzNTVTVISDNW?oc=5</t>
+        </is>
+      </c>
+      <c r="F46" t="n">
+        <v>7</v>
+      </c>
+      <c r="G46" s="2" t="n">
+        <v>46028.35501157407</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>Cl0p</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>"Cl0p ransomware" OR "Cl0p threat actor" OR "Cl0p cyber attack"</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>Massive Breach at University of Phoenix Due to the Oracle EBS Exploit, Korean Air Confirms Breach Claimed by CL0P - TechNadu</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>Wed, 31 Dec 2025 09:26:27 GMT</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMi3gFBVV95cUxNWl9wUHpBd3BHNDBDb3dvTG1xcDNpS3NWMGh3anNhLWUtb0xYeHQ3WnZxdk9lQW1oTURLa2taU3JFSVNVNHJVaTI0MGNpOVhqWlY3bTNORS03YmtDMzY1YVZFTXNOVmdRZ0x6ZzhhVUVucnpwb3FaaHl6bWhFMzFoeHVRc1l1dlg2U0FRRS04c0RXUGoyUXpuREFoSU1EZjlGREZmY3ZqeWxmbmNDTHA5RkpWQzdlcDUzRGpreWFZTGwzN19jeXdYRXRod1pVX1BabDZpUEZSeUlqcGdCNXc?oc=5</t>
+        </is>
+      </c>
+      <c r="F47" t="n">
+        <v>7</v>
+      </c>
+      <c r="G47" s="2" t="n">
+        <v>46022.39336805556</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>Devman</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>"Devman ransomware" OR "Devman threat actor" OR "Devman cyber attack"</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>Resecurity says security breach was nothing more than hackers duped by a honeypot - BetaNews</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>Sun, 04 Jan 2026 13:06:43 GMT</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMitAFBVV95cUxOWF9PWmVQdWt6ZlZGYnRoR1hJa040QXYtXzJRb1pmeWNFT3BseW5YcGlLVUp5Q0RpYkt4b015UWFCY0pvUW45UlhYb09ucW5sVHFjeklyQTE5Q3NHckE3YjE0NDEtQnhwNjRVYnFPZmZaalA2cm5YbGYtQlBjNmVQOGUwR010dDFWXzIxZzJqRS1OWUVnLTF2SVRVOXFGOUVkZTZLVjVVUEpYOTh5N3VIVFo1LUY?oc=5</t>
+        </is>
+      </c>
+      <c r="F48" t="n">
+        <v>7</v>
+      </c>
+      <c r="G48" s="2" t="n">
+        <v>46026.54633101852</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/latest_ransomware_news.xlsx
+++ b/data/latest_ransomware_news.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G48"/>
+  <dimension ref="A1:G63"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2020,6 +2020,501 @@
         <v>46026.54633101852</v>
       </c>
     </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>Qilin</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>"Qilin ransomware" OR "Qilin threat actor" OR "Qilin cyber attack"</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>Qilin ransomware gang alleges cyberattack against Cressi - SC Media</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>Fri, 09 Jan 2026 17:39:30 GMT</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMijwFBVV95cUxPZ2h0cHZOTjlUMENJeEtSQ3g2SUdXUWRYbFNFdXFYM0d0c214WThpcERUcW9SR0lheWk3YnlNblN6NmFyMGEzUGVLaFNSakN1c1l6N1BYWkVaV0ZVRkRUNldGRjdHUGctV1cwUkZhNDVaMnU1Y3VqeHQyekZIQ1NiVlpIbHY1eTd1c05POHVwcw?oc=5</t>
+        </is>
+      </c>
+      <c r="F49" t="n">
+        <v>7</v>
+      </c>
+      <c r="G49" s="2" t="n">
+        <v>46031.73576388889</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>Qilin</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>"Qilin ransomware" OR "Qilin threat actor" OR "Qilin cyber attack"</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>Hale Makua Health Services falls victim to Qilin Ransomware - Claim Depot</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>Fri, 09 Jan 2026 22:49:34 GMT</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiZEFVX3lxTE1hUXlOMmMwUTd2T1k4RTBIcDBBUDJKaDBFSFZHWW5jbkdENndoU2gzWF9IQ292R28xSk9hcmh2UEpXSkxWYnVaR0w1STdHRjlVcGozVFdrd0E1MGdpZUZTb0oyUnI?oc=5</t>
+        </is>
+      </c>
+      <c r="F50" t="n">
+        <v>7</v>
+      </c>
+      <c r="G50" s="2" t="n">
+        <v>46031.95108796296</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>Qilin</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>"Qilin ransomware" OR "Qilin threat actor" OR "Qilin cyber attack"</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>Valley Eye Associates Data Breach Exposes Protected Health Information - Claim Depot</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>Fri, 09 Jan 2026 22:29:33 GMT</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMic0FVX3lxTE9EaGo5TnhiSEJORzBwZmFRcGR1NHAtZjJsd3g0TEs5Z1dxSHVBejNMR2FZdzlLU19Wa1R1blpHdUxLYVBpc0Y4b2NMTGoxUEpMVWdySjFiUEQ5aWhRem5TaFg0VHRWVVk3NTg4WVVnblQ5NEU?oc=5</t>
+        </is>
+      </c>
+      <c r="F51" t="n">
+        <v>7</v>
+      </c>
+      <c r="G51" s="2" t="n">
+        <v>46031.9371875</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>Akira</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>"Akira ransomware" OR "Akira threat actor" OR "Akira cyber attack"</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>Akira Ransomware Attack on Triple Eight Transport - DeXpose</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>Fri, 09 Jan 2026 00:00:00 GMT</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMifkFVX3lxTE5XLVdaU1JRZ0ZsbXNTRi1rV2k2Rm1FcERYXzVrWV9PSy1DMFp3WEszanU3ZEo3MG9rMDM5eDd2WEw1QjlZZFRtMmdrNVhaVTdwel8yV0NfdXgxN1ZvZ3Jnd3FxajJQdFNKa2FhRDdMbnlxOWp4T1ZLcW8yZkt2QQ?oc=5</t>
+        </is>
+      </c>
+      <c r="F52" t="n">
+        <v>7</v>
+      </c>
+      <c r="G52" s="2" t="n">
+        <v>46031</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>Everest</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>"Everest ransomware" OR "Everest threat actor" OR "Everest cyber attack"</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>Nissan Vulnerability Exposed Following Chrysler Hack News - RS Web Solutions</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>Wed, 14 Jan 2026 01:00:00 GMT</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMisAFBVV95cUxPT1ZEU1NnazBLczNGWUFNS0E1YkotdUJDdnlfdEZ5V0RIeVp2Y1F5TWJXTnVhOWdhVXZEWWdNYnBfSWllNmVXWFFFN1dyM3c3Q0FMblliSjg1RE43dkk3QXQxRjhFRHJyVklRV3VSdUhoN3VZdW5KUThvMlR6dXhESTBPVnJSck5vcGZBQVhiV2hXeWVTcUNHZ1RaWlpSbVBnemdIT29STmx6eS1kLWM4bA?oc=5</t>
+        </is>
+      </c>
+      <c r="F53" t="n">
+        <v>7</v>
+      </c>
+      <c r="G53" s="2" t="n">
+        <v>46036.04166666666</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>LockBit</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>"LockBit ransomware" OR "LockBit threat actor" OR "LockBit cyber attack"</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>LockBit ransomware developer extradited to face crimes in the United States - MSN</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>Mon, 12 Jan 2026 20:35:36 GMT</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMi2AJBVV95cUxNX0RtamJUZTZyNERqYTl0TC1tRHFXUGo2RnA3UUNubjZONWt5RnFWM3Fsd1E4eC11cHNkVDQtMHZCdVk4NmhqdWlWQUxoT082WEFpNEJtSlBRRm83Y2h1Z1o0ZnlNekxQN0xrazQyNFVPckZwQjJGUmIwZGIyQVhERlpPX2hoS3VaXzZ0Mm4xOGNpbXFtaktKN0hFNTNnaVpBdFZEMDNnak9ZR3VuWEZBbGhEaU1ZNUxrUmlpaEQxRDNDczFMWkpFNkNNU1NFc29YZFBKZXp3a0xEWVVfNUx4X0pqaEU4YjJqejVlQVJWOElUYzBYRTZuY3ZQNkFubEhoRGQ2cEhSSkcxMXlaSFV6bEo5RHdhLTlRSXd2a3FmTkdlSWY1T0NxaW40MzRTeThsNkVBLWFnSEo4b2JId0FRSm5IOElHZFItMHI0MHVWOURNUXJ2Sloydg?oc=5</t>
+        </is>
+      </c>
+      <c r="F54" t="n">
+        <v>7</v>
+      </c>
+      <c r="G54" s="2" t="n">
+        <v>46034.85805555555</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>LockBit</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>"LockBit ransomware" OR "LockBit threat actor" OR "LockBit cyber attack"</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>Afternoon Book Club: ‘Locked Up’ by Zachary Lewis explores cybersecurity - KFVS12</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>Thu, 08 Jan 2026 23:18:00 GMT</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMipwFBVV95cUxQMW1rejVMT2hINHZ4ZWlvdE9Bam1ORXJ5a29TR0VxMC1UX1A3dmNoYUFuRXhTVXpzVjNjdmY0Q0l4a0Vnb1B1bVgybG16c2VPdnh6OGNjV0lPRmlIdlJNRzBULWFrOGx2RE9MYlhCckdkRG40Y1FENHJTQ0FIYm9TYU1FWkdROGROeTg2SDNrcUpPWWY0dG0zaDhGclZEWUd6bTJ4eERoNNIBuwFBVV95cUxQRFloRDdGZTZYSUttTFFIbU9nbWZTRDBSTWc4dlZLSEN5VlJKeUtsQXFYcmRjWmtZVXljdzlwSGh0VkJWR1ZKT0JFSFZyT3lJZ2FWYmdIMGpDdTUtNmxvMkJZdjBja3FpZi1yd2otUlAtN0ZMZlpTR1Z1V19SbHhjaWZ3bEtwdTlVQ3dQcFd4djZkeGlCN2x5dk5VZk9ESU9XNlVtTGk3cDJZY3ppYV95ZXJkMUplU0hydTk0?oc=5</t>
+        </is>
+      </c>
+      <c r="F55" t="n">
+        <v>7</v>
+      </c>
+      <c r="G55" s="2" t="n">
+        <v>46030.97083333333</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>LockBit</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>"LockBit ransomware" OR "LockBit threat actor" OR "LockBit cyber attack"</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>Operation Cronos Leader Gets Nod From King Charles - itsecuritynews.info</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>Mon, 12 Jan 2026 09:33:18 GMT</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiiwFBVV95cUxOdVBJMm1rZ0FsYnJ3d24tMlhGMjNyNEQ2bFNyVkZoY2VRYWFYSUpyZXNsWVVfRDg4NkxXN2JFX1hfV3k3QWxLRW5XZzFCeTFOb1VMTFZXU2VhamRWdXV5RGxWc3VYSUNBT3lrYktjMnh3cm5oclloWDJkeE03T2Y1Q1U2bVo2RjFjbFFJ?oc=5</t>
+        </is>
+      </c>
+      <c r="F56" t="n">
+        <v>7</v>
+      </c>
+      <c r="G56" s="2" t="n">
+        <v>46034.398125</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>Lynx</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>"Lynx ransomware" OR "Lynx threat actor" OR "Lynx cyber attack"</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>Lynx ransomware group claims Regis subsidiary on dark web leak site - Digital Watch Observatory</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>Fri, 09 Jan 2026 11:53:50 GMT</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMickFVX3lxTE5rQmFIWGRCbVY5OFZoUFlPMVQxZzBzZzRPTlp5MlVMYU5QSjVzT25GVk9iVXhUMlhnb1BreE4tMG5aZHd2S2hfUGdLSFZXOVdpdUpjak1jVzZuNVExS0I2MDVGMm1uOGRaS1k5eWJ0bTZKUQ?oc=5</t>
+        </is>
+      </c>
+      <c r="F57" t="n">
+        <v>7</v>
+      </c>
+      <c r="G57" s="2" t="n">
+        <v>46031.4957175926</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>Lynx</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>"Lynx ransomware" OR "Lynx threat actor" OR "Lynx cyber attack"</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>Exclusive: Victorian Catholic college suffers alleged cyber attack - Cyber Daily</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>Thu, 08 Jan 2026 06:24:50 GMT</t>
+        </is>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiqgFBVV95cUxOSnlmS0pVc3pEaGRIY05icTlIZGlOM1VVNHJGTmJpdEphX205NG5GbUdNX3ZIYl8tRDFmZ3d6LUdMcy1KN01xVjdwS2NncnZfR09iZ3pzZmpQZlk1Tm54aFhTMm83WUpRb0NrZ19PSEswdmk5MFJNTWZWWjlVTjFpWFVOTVVacFprVlE4bU9qaFZXS0c0S1BXcVNraURBRHR1d2QwRjZLY3kwZw?oc=5</t>
+        </is>
+      </c>
+      <c r="F58" t="n">
+        <v>7</v>
+      </c>
+      <c r="G58" s="2" t="n">
+        <v>46030.26724537037</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>Medusa</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>"Medusa ransomware" OR "Medusa threat actor" OR "Medusa cyber attack"</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>Madusa Ransomware 2025: RMM Abuse in Ransomware Campaigns - Darktrace</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>Thu, 08 Jan 2026 21:59:03 GMT</t>
+        </is>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiqgFBVV95cUxNaTlfbldnbnBVak13X2FndEZFcjFvYTlrVnR2X3VZRE1zSjJrejlrazBBa19ETVYxSFV1VXh3Q1d6WEpWOEUweDd1eWFxYXJ6LUU3ZFNrQzhmQktKR0s5SzgtbEIzLVBvMDcwaGlpVG5wRGRsbzdQMi1ZaHU3c3pDVUYtdDJKM2FMNHpUSkFRSmpwN2J1Z0dDNXdjam9hM2s3UHRVVFpyVDhjQQ?oc=5</t>
+        </is>
+      </c>
+      <c r="F59" t="n">
+        <v>7</v>
+      </c>
+      <c r="G59" s="2" t="n">
+        <v>46030.91600694445</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>Medusa</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>"Medusa ransomware" OR "Medusa threat actor" OR "Medusa cyber attack"</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>Interpol operation arrests 300 suspects linked to African cybercrime rings - MSN</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>Sun, 11 Jan 2026 13:10:42 GMT</t>
+        </is>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMi3wJBVV95cUxOM056Tk1jNVMtMXphUl9OeWQ2a21Pd252WlNBeEJCVFlCS2JlN3ZHRzF0Um9fcGFHd3l4YWJLdDZnTm5Pckw2VXk1Q1htQ2FTbVNJcUtQU2RPTVc1Z1RTTTdOeXYwNFY4U2N3RWdBWFl4YXh6bERjWS02bmZzb3RSWERoMktxQkl3MzZZZkU3UWNKUEVJWEViU1kwZ3d5UVV0b3o1Rll4Y1FyWXJkTFJUV2Z3NUR1RjBQQklqeFE5aUlMTGYzVXVjMWpTZllPOERLYmlCTkdQM1JlQW1PdXBrZWNPNGd6Z0MySG1rUVp6YXQ5U0UxQnZ5SjNDSnpCbnhOMUUzakF4NW9QcjJ4bC1HT1VqWUM1amF4NnRYcGsyRDI3azhrbkNLTVM3OUVpMVhCZE9UNk5qT24yS1JDTjg0bHJYMFpjNG5RbHhMZ1UwNHVBWGVXMmQ4OW51UUVMZDA?oc=5</t>
+        </is>
+      </c>
+      <c r="F60" t="n">
+        <v>7</v>
+      </c>
+      <c r="G60" s="2" t="n">
+        <v>46033.54909722223</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>Medusa</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>"Medusa ransomware" OR "Medusa threat actor" OR "Medusa cyber attack"</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>News - Pulse Urgent Care Suffers Security Breach, Personal Data Compromised - teiss</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>Thu, 08 Jan 2026 12:03:51 GMT</t>
+        </is>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMipAFBVV95cUxNaUZYZk1ibFdYRGtXUXAtajh3VzZEY0FYU2pnUm9PN0s3UThrY2VrMWFuUTVfOGY5bThJN1Z1WTNMMVNDNnpOMmdrUEpXc1NGZzIxaHpZLUQ2TkhhMjlpNG4zWnNhdlB4R3Z4VUs5aUJMazZjTmttcnczbm5ZNkphZzdvSmlaOE9FZzh1MF9STnpnOGJ2VlprNlNwUHd6NTAxNDlJYQ?oc=5</t>
+        </is>
+      </c>
+      <c r="F61" t="n">
+        <v>7</v>
+      </c>
+      <c r="G61" s="2" t="n">
+        <v>46030.50267361111</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>Medusa</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>"Medusa ransomware" OR "Medusa threat actor" OR "Medusa cyber attack"</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>Analyst's Guide to the ActiveAI Security Platform - Darktrace</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>Thu, 08 Jan 2026 21:33:45 GMT</t>
+        </is>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMilgFBVV95cUxORHdsdUxEaE9HMURBeVFzTnpzQXEtRk45Zk9pNTBSV201YXl2MUYzQ0lVQ0paODhXbmNCVENrOVd1LVpMOU5aMEEtb01HXzQxMW5qODdyVE5qS0xBckQwOEVFLXMyRmFhSTVmajl3Tk5RbnptMUJfd3R4aERBaldoSC1EeFJ4TGlJdWtlc3p3NDh5ZUZMemc?oc=5</t>
+        </is>
+      </c>
+      <c r="F62" t="n">
+        <v>7</v>
+      </c>
+      <c r="G62" s="2" t="n">
+        <v>46030.8984375</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>Safepay</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>"Safepay ransomware" OR "Safepay threat actor" OR "Safepay cyber attack"</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>Conduent Business Services Data Breach Victim Count Swells to More Than 14.7M - The HIPAA Journal</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>Wed, 07 Jan 2026 08:00:00 GMT</t>
+        </is>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMieEFVX3lxTE5YWmhFRk5uQk5fMThleDFMS2VkY1dEdDhVTzdyTm5VT3dsQmJGMWpXMFppZjRuSnFncXlZcjVXazlWRzNDLVRwbmxkMGVhSTl1MGpscnlzNTJyRHlvSGRjeERmem9FMUZPZlh2LUZhZXNmajI0QW12RA?oc=5</t>
+        </is>
+      </c>
+      <c r="F63" t="n">
+        <v>7</v>
+      </c>
+      <c r="G63" s="2" t="n">
+        <v>46029.33333333334</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/latest_ransomware_news.xlsx
+++ b/data/latest_ransomware_news.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G63"/>
+  <dimension ref="A1:G74"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2515,6 +2515,369 @@
         <v>46029.33333333334</v>
       </c>
     </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>Dragonforce</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>"Dragonforce ransomware" OR "Dragonforce threat actor" OR "Dragonforce cyber attack"</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>Researchers Breakdown DragonForce Ransomware Along with Decryptor for ESXi and Windows Systems - Cyber Security News</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>Wed, 14 Jan 2026 17:44:43 GMT</t>
+        </is>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMigAFBVV95cUxQd0RPTEZvWXRHTVZwangyVjJiRkEzMTJBWDRZd0JTcF9WbHFHR2xiNE10ZEVnVUF5SV9NQ2dRSlBwVjRTVWtmd0xyTzRWZnc5U3Y2Qy1uWTZZblRjSjJLVnRUUXVJUF94NWJLWVN2bXBMcVZNX21YYkJmTnlZSERuS9IBhgFBVV95cUxNLWJXdktPUGFFLW9JcFhVb0ZXcnlfaTVoZkhXZWIwdVlDRnBoS3hVZFNFT0tWbF9NNDhCbzQ3NVlhQkxhVHozcjJJS0ktN2M2eTRNdW1Ra015bkI3UWRCOFBOQ0h3T1lqREJEYTZ6ZmU5RWVMMUVyM28ySFhkcVNmMER1MHBQQQ?oc=5</t>
+        </is>
+      </c>
+      <c r="F64" t="n">
+        <v>7</v>
+      </c>
+      <c r="G64" s="2" t="n">
+        <v>46036.73938657407</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>Qilin</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>"Qilin ransomware" OR "Qilin threat actor" OR "Qilin cyber attack"</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>Moen, maker of high-end kitchen, bathroom fixtures, targeted by ransomware gang - Cybernews</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>Sat, 17 Jan 2026 02:15:30 GMT</t>
+        </is>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMid0FVX3lxTE8tR2xFUmJHU3Rnd1NlZ2stbmRxTGhiZmxfOHkwQW1QalI3R3FKdUk0c2tfR1dXM1pOR2MtWGNzcVN1emJZa255dlRnZDl1QmpLbEx1dHJqS3czTTVYVVRldWpqa3VPbUlMaXVwb1ZVdHBkSjBGcmZR?oc=5</t>
+        </is>
+      </c>
+      <c r="F65" t="n">
+        <v>7</v>
+      </c>
+      <c r="G65" s="2" t="n">
+        <v>46039.09409722222</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>Qilin</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>"Qilin ransomware" OR "Qilin threat actor" OR "Qilin cyber attack"</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>Mid Michigan Medical Billing Service Data Breach Affects 28K Patients - Claim Depot</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>Fri, 16 Jan 2026 18:25:03 GMT</t>
+        </is>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMihwFBVV95cUxNbDFQT3F1eVF6NFRqQjBCY1Y1TEpGdXZpVjBweW16T2l5cU52SUxRY3hTWkF1X3ZkVzR2QkZ3QkU2all4Yi1GSjdUTkktZTRBZDhIZzlsRUtNNmdJQ0FzMG9LV3QzZENQQTFiU2Yzc0lUV0lGZkdDWWlhVU5HSWcyaTI5c1JibFE?oc=5</t>
+        </is>
+      </c>
+      <c r="F66" t="n">
+        <v>7</v>
+      </c>
+      <c r="G66" s="2" t="n">
+        <v>46038.76739583333</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>Everest</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>"Everest ransomware" OR "Everest threat actor" OR "Everest cyber attack"</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>Everest Ransomware Claims McDonalds India Breach Involving Customer Data - Hackread</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>Tue, 20 Jan 2026 22:40:28 GMT</t>
+        </is>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMigwFBVV95cUxPR0gxb0l1RnBCM1ZWZUxKUUdaa0UyTHdGWTlkRHZaeHlkQ2NISGVVUVZka0ItT2twY0V3c21CVEJCQnUzRFU4bWhQbmNJSXZib2FjNi1yZFB3aTAtUl9sX1FOaXVFX1J2T2tNU1pYR1N1RThnYWZ6alNENkplNDRNamV5TQ?oc=5</t>
+        </is>
+      </c>
+      <c r="F67" t="n">
+        <v>7</v>
+      </c>
+      <c r="G67" s="2" t="n">
+        <v>46042.94476851852</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>Everest</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>"Everest ransomware" OR "Everest threat actor" OR "Everest cyber attack"</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>Most SOCs Are Seeing Attacks Too Late. Here's How to Fix It - Cyber Security News</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>Tue, 20 Jan 2026 17:48:02 GMT</t>
+        </is>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMifEFVX3lxTE1qdkozTGhjdFRmTHp6SFpzcHBvSm9nYVp1YjFrc3JhT2FsR21VQl9TZnNMMWgwVzVXbjNSNzRpYlZ2ZlBxTHhTR2RmeG9Nek5aX2E3M0dCTzRQQkVmcjVmcXN5ZktBaThFWDFVMGxmWnBncFdZUm0yU2VyUHPSAXxBVV95cUxNanZKM0xoY3RUZkx6ekhac3Bwb0pvZ2FadWIxa3NyYU9hbEdtVUJfU2ZzTDFoMFc1V24zUjc0aWJWdmZQcUx4U0dkZnhvTXpOWl9hNzNHQk80UEJFZnI1ZnFzeWZLQWk4RVgxVTBsZlpwZ3BXWVJtMlNlclBz?oc=5</t>
+        </is>
+      </c>
+      <c r="F68" t="n">
+        <v>7</v>
+      </c>
+      <c r="G68" s="2" t="n">
+        <v>46042.74168981481</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>Everest</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>"Everest ransomware" OR "Everest threat actor" OR "Everest cyber attack"</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>Sprocket Security Appoints Eric Sheridan as Chief Technology Officer - Cyber Security News</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>Tue, 20 Jan 2026 18:44:11 GMT</t>
+        </is>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMipgFBVV95cUxOdGdpT3ZwZ0x2NjNjUnBBTmdOZVR5ZHViblluSjlreGtTS3hZQ1F0aDNYX2E0RUh6UlN5aWJwRlJrMzFCN2R0ZEZ6RTd4OGxOWUpERll5bUVPOWhpNU44MkVnUXRnZGZYbWJEZzIwRW1kSmpnV21tVUE4YjFhaFVxSkpFRzZDMUpvczhzZy1KLWdxTjV4WWRHODF6VE5PRzdGUWxwcmF30gGmAUFVX3lxTE50Z2lPdnBnTHY2M2NScEFOZ05lVHlkdWJuWW5KOWt4a1NLeFlDUXRoM1hfYTRFSHpSU3lpYnBGUmszMUI3ZHRkRnpFN3g4bE5ZSkRGWXltRU85aGk1TjgyRWdRdGdkZlhtYkRnMjBFbWRKamdXbW1VQThiMWFoVXFKSkVHNkMxSm9zOHNnLUotZ3FONXhZZEc4MXpUTk9HN0ZRbHByYXc?oc=5</t>
+        </is>
+      </c>
+      <c r="F69" t="n">
+        <v>7</v>
+      </c>
+      <c r="G69" s="2" t="n">
+        <v>46042.78068287037</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>Medusa</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>"Medusa ransomware" OR "Medusa threat actor" OR "Medusa cyber attack"</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>Google just announced a huge change to Gmail. Here’s what you need to know - pennlive.com</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>Sun, 18 Jan 2026 10:00:00 GMT</t>
+        </is>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMitgFBVV95cUxNS0RfaDNBN1BXZng5S2t1SUU0aDBTZFlnWGN2elpUM2NuaE5GQ3lSRTlybDZCRFFvMGxtZlRCRTRjVkpDYWpjOVAtREJFczhONHp3Q3RqUUhlbi1IN1NiQ3Jucjh4RHB5V1pRYmd5QmM5UmxyckVXVHJPaTEwQ01pck41UWFEZldVc052eUFOb1pURGlNc3JfZERJVjE3WmhtQkk3eVVKNEIzSm1abWJuSXRmTENBZ9IBygFBVV95cUxNcHRxZjZhMkFHc2FDRThFdnR6WEVZYnM3WEppSmVULW1kN2V5RGh3bnFpSWt3eUVRMTF4MVU0Yk1ZSWhONTh4ODlyNlFHVFZRdGxjQklXc1RFQXlRQUU0VE96SW40VU9IUFdiN1pFckpuSGdMZFJZdU1QQ25YWFNFYVJHRDZkR3RQZWVpOGJmNlYxSWpzY2dKTGc5M2oxcGN0MWN1azdqZTJSaHVnZ1RGckRkWkN3cERQaEpLcWg0VEZSX2hOYjN0YU5R?oc=5</t>
+        </is>
+      </c>
+      <c r="F70" t="n">
+        <v>7</v>
+      </c>
+      <c r="G70" s="2" t="n">
+        <v>46040.41666666666</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>Medusa</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>"Medusa ransomware" OR "Medusa threat actor" OR "Medusa cyber attack"</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>Microsoft Defender is getting a useful upgrade to help stop endpoint attacks - MSN</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>Sat, 17 Jan 2026 11:16:10 GMT</t>
+        </is>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMi4AJBVV95cUxPWHctemN5eUdLSUlaanRZUzlwYUhZSVdnRFdKS2psNmdUeWtsRm0zbFItTGVheDVQa2FCYkRYNVhLc0stWTdqRTN3anVvdFVDMmx3My0zODNQRmU0RHV4Q1l3Q1ZydHV4R3JjUnJCX0M5OEdVX1Z5T1lRRUJfYW44NW9BSjF0SWU1NEFxdmcxd21sNHc3Ukt3Y185Zk11UnVpQ0FOR2FQd0N3Mk9GckxvYTNETU83QU1MaGtxMm1EQ1ZwRDJzS043SHRNa1JPQ0taY09oc2xpa0JFWVBnNnBMV29YUWRtcFh2OVBpRTdHYmppODBJblVKRmZ4QWxOYlpwN1JDRTNvUFRDOUktdEhWTTYxcUNwSnhQbkNLWmVFajBocmhtNGt5TWZiVm1SLWhEOHgwVlZZaEpjZW9wWnVnYms5LU5WbkpWcXFwWlloWmcxdzN6SlBOUjlaYmYtTjNu?oc=5</t>
+        </is>
+      </c>
+      <c r="F71" t="n">
+        <v>7</v>
+      </c>
+      <c r="G71" s="2" t="n">
+        <v>46039.46956018519</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>Cl0p</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>"Cl0p ransomware" OR "Cl0p threat actor" OR "Cl0p cyber attack"</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>Data breach alert! Google warns hackers exploited Oracle apps to steal data and send extortion emails - MSN</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>Sat, 17 Jan 2026 04:44:56 GMT</t>
+        </is>
+      </c>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMi-gJBVV95cUxOQXFFSnFHcHFSb2dialdOSnNsdXRYUUZmZl9fVVI5d2FjQnRTVk1pR2xLS3NaWmY3cWxValhwOG1MaGhWbVAzM01ITmZkS184WkhIUDhuaEl3OF9IeTF5RjJTdXY4dGdJWVduWnJWbDROZmFHZHJuR3ZTQzhrNmhZZDJab2MySGJ2UXlFMjNmU3ExbEZ4cDVwUTJlR2R3UTFBUnp5UXZLM3o3bWdUWklxUF9nMTlnODUxa3ZwVjc3M3duSW5VU0swMC1QdE9JOVhJYjNSVzdIVjk3Tnp4cG5FR1NvQ0MtR1JSMDdUbGlKdWx6X1EzTENLVGFneDdUQU9CNmFLOVpTWl9CS0oyYjFfLUxhQkdUbXhBNXFWODhfMUhsTXVYakU5Q0VKRmpTUTdRU25MelZYcUhYV1VieWJrNlg0aFhWenlCRVRxSVRkS3VyaXRYc0tJRUpFU0I4bkNLUi1NNHdEVFRlNU1sSEs1SWRwLW5nbFgyY2c?oc=5</t>
+        </is>
+      </c>
+      <c r="F72" t="n">
+        <v>7</v>
+      </c>
+      <c r="G72" s="2" t="n">
+        <v>46039.19787037037</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>Cl0p</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>"Cl0p ransomware" OR "Cl0p threat actor" OR "Cl0p cyber attack"</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>Korean Air Employee Data Exposed in Cl0p Ransomware Supply-Chain Attack - itsecuritynews.info</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>Thu, 15 Jan 2026 14:37:10 GMT</t>
+        </is>
+      </c>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMipwFBVV95cUxPRlh6Rzg1QXZOazJZcklvZEJxSE5qS2tIenhXN2lmYTltVXVSaDdRNmxDX0xhX1VlM3doS3Y5SDVyRXdCYTBqZEtPRFRxSklhZW1SVS1pZ25aR1g2aFB0RlhmZ0xmRkg2YjJFbHBxdmZ1N2xNXzhXcG9Eem1RS29YQ043aE4yeUVpT2F5UFRsazc1NHZKWF9zMXdDS01SbDQ2cTFZRXdpVQ?oc=5</t>
+        </is>
+      </c>
+      <c r="F73" t="n">
+        <v>7</v>
+      </c>
+      <c r="G73" s="2" t="n">
+        <v>46037.60914351852</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>Safepay</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>"Safepay ransomware" OR "Safepay threat actor" OR "Safepay cyber attack"</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>Ingram Micro data breach affects 42,000 individuals - Techzine Global</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>Tue, 20 Jan 2026 10:58:15 GMT</t>
+        </is>
+      </c>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMinAFBVV95cUxNTXMweXNqdlo1MDBCZmVJd05vWWhWVEdtTC1WTUt4b1NlMXNic3ZTYldCQmdnMVlSa1BOWFpFMF9Ud1prNWdrbmNoNm96WVRpMWlGSmFnRHZsZWZOODFOd0RrSHhoS3Z6NTJXckVlcGdDNlJkMzA1c05sTWx4cldjWnBmMzl4Ukl0dHkyOUl2MXFzR0hOQnpMWC0wajQ?oc=5</t>
+        </is>
+      </c>
+      <c r="F74" t="n">
+        <v>7</v>
+      </c>
+      <c r="G74" s="2" t="n">
+        <v>46042.45711805556</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/latest_ransomware_news.xlsx
+++ b/data/latest_ransomware_news.xlsx
@@ -20,16 +20,13 @@
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
   </numFmts>
-  <fonts count="2">
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -40,7 +37,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -48,21 +45,12 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
@@ -429,41 +417,41 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G74"/>
+  <dimension ref="A1:G80"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>search_name</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>search_query</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>title</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>published</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>link</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>past_days</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>published_dt_utc</t>
         </is>
@@ -498,7 +486,7 @@
       <c r="F2" t="n">
         <v>7</v>
       </c>
-      <c r="G2" s="2" t="n">
+      <c r="G2" s="1" t="n">
         <v>46009.72517361111</v>
       </c>
     </row>
@@ -531,7 +519,7 @@
       <c r="F3" t="n">
         <v>7</v>
       </c>
-      <c r="G3" s="2" t="n">
+      <c r="G3" s="1" t="n">
         <v>46009.80255787037</v>
       </c>
     </row>
@@ -564,7 +552,7 @@
       <c r="F4" t="n">
         <v>7</v>
       </c>
-      <c r="G4" s="2" t="n">
+      <c r="G4" s="1" t="n">
         <v>46013.73260416667</v>
       </c>
     </row>
@@ -597,7 +585,7 @@
       <c r="F5" t="n">
         <v>7</v>
       </c>
-      <c r="G5" s="2" t="n">
+      <c r="G5" s="1" t="n">
         <v>46008.63925925926</v>
       </c>
     </row>
@@ -630,7 +618,7 @@
       <c r="F6" t="n">
         <v>7</v>
       </c>
-      <c r="G6" s="2" t="n">
+      <c r="G6" s="1" t="n">
         <v>46009.74578703703</v>
       </c>
     </row>
@@ -663,7 +651,7 @@
       <c r="F7" t="n">
         <v>7</v>
       </c>
-      <c r="G7" s="2" t="n">
+      <c r="G7" s="1" t="n">
         <v>46009.90625</v>
       </c>
     </row>
@@ -696,7 +684,7 @@
       <c r="F8" t="n">
         <v>7</v>
       </c>
-      <c r="G8" s="2" t="n">
+      <c r="G8" s="1" t="n">
         <v>46010.76940972222</v>
       </c>
     </row>
@@ -729,7 +717,7 @@
       <c r="F9" t="n">
         <v>7</v>
       </c>
-      <c r="G9" s="2" t="n">
+      <c r="G9" s="1" t="n">
         <v>46012.52083333334</v>
       </c>
     </row>
@@ -762,7 +750,7 @@
       <c r="F10" t="n">
         <v>7</v>
       </c>
-      <c r="G10" s="2" t="n">
+      <c r="G10" s="1" t="n">
         <v>46008.60887731481</v>
       </c>
     </row>
@@ -795,7 +783,7 @@
       <c r="F11" t="n">
         <v>7</v>
       </c>
-      <c r="G11" s="2" t="n">
+      <c r="G11" s="1" t="n">
         <v>46008.20113425926</v>
       </c>
     </row>
@@ -828,7 +816,7 @@
       <c r="F12" t="n">
         <v>7</v>
       </c>
-      <c r="G12" s="2" t="n">
+      <c r="G12" s="1" t="n">
         <v>46007.69114583333</v>
       </c>
     </row>
@@ -861,7 +849,7 @@
       <c r="F13" t="n">
         <v>7</v>
       </c>
-      <c r="G13" s="2" t="n">
+      <c r="G13" s="1" t="n">
         <v>46013.22555555555</v>
       </c>
     </row>
@@ -894,7 +882,7 @@
       <c r="F14" t="n">
         <v>7</v>
       </c>
-      <c r="G14" s="2" t="n">
+      <c r="G14" s="1" t="n">
         <v>46011.59137731481</v>
       </c>
     </row>
@@ -927,7 +915,7 @@
       <c r="F15" t="n">
         <v>7</v>
       </c>
-      <c r="G15" s="2" t="n">
+      <c r="G15" s="1" t="n">
         <v>46014.76332175926</v>
       </c>
     </row>
@@ -960,7 +948,7 @@
       <c r="F16" t="n">
         <v>7</v>
       </c>
-      <c r="G16" s="2" t="n">
+      <c r="G16" s="1" t="n">
         <v>46014.66623842593</v>
       </c>
     </row>
@@ -993,7 +981,7 @@
       <c r="F17" t="n">
         <v>7</v>
       </c>
-      <c r="G17" s="2" t="n">
+      <c r="G17" s="1" t="n">
         <v>46014.66866898148</v>
       </c>
     </row>
@@ -1026,7 +1014,7 @@
       <c r="F18" t="n">
         <v>7</v>
       </c>
-      <c r="G18" s="2" t="n">
+      <c r="G18" s="1" t="n">
         <v>46021.41666666666</v>
       </c>
     </row>
@@ -1059,7 +1047,7 @@
       <c r="F19" t="n">
         <v>7</v>
       </c>
-      <c r="G19" s="2" t="n">
+      <c r="G19" s="1" t="n">
         <v>46018.63103009259</v>
       </c>
     </row>
@@ -1092,7 +1080,7 @@
       <c r="F20" t="n">
         <v>7</v>
       </c>
-      <c r="G20" s="2" t="n">
+      <c r="G20" s="1" t="n">
         <v>46016.62888888889</v>
       </c>
     </row>
@@ -1125,7 +1113,7 @@
       <c r="F21" t="n">
         <v>7</v>
       </c>
-      <c r="G21" s="2" t="n">
+      <c r="G21" s="1" t="n">
         <v>46021.41559027778</v>
       </c>
     </row>
@@ -1158,7 +1146,7 @@
       <c r="F22" t="n">
         <v>7</v>
       </c>
-      <c r="G22" s="2" t="n">
+      <c r="G22" s="1" t="n">
         <v>46020.62881944444</v>
       </c>
     </row>
@@ -1191,7 +1179,7 @@
       <c r="F23" t="n">
         <v>7</v>
       </c>
-      <c r="G23" s="2" t="n">
+      <c r="G23" s="1" t="n">
         <v>46021.68114583333</v>
       </c>
     </row>
@@ -1224,7 +1212,7 @@
       <c r="F24" t="n">
         <v>7</v>
       </c>
-      <c r="G24" s="2" t="n">
+      <c r="G24" s="1" t="n">
         <v>46020.4715162037</v>
       </c>
     </row>
@@ -1257,7 +1245,7 @@
       <c r="F25" t="n">
         <v>7</v>
       </c>
-      <c r="G25" s="2" t="n">
+      <c r="G25" s="1" t="n">
         <v>46020.60138888889</v>
       </c>
     </row>
@@ -1290,7 +1278,7 @@
       <c r="F26" t="n">
         <v>7</v>
       </c>
-      <c r="G26" s="2" t="n">
+      <c r="G26" s="1" t="n">
         <v>46020.74041666667</v>
       </c>
     </row>
@@ -1323,7 +1311,7 @@
       <c r="F27" t="n">
         <v>7</v>
       </c>
-      <c r="G27" s="2" t="n">
+      <c r="G27" s="1" t="n">
         <v>46020.75528935185</v>
       </c>
     </row>
@@ -1356,7 +1344,7 @@
       <c r="F28" t="n">
         <v>7</v>
       </c>
-      <c r="G28" s="2" t="n">
+      <c r="G28" s="1" t="n">
         <v>46017.46113425926</v>
       </c>
     </row>
@@ -1389,7 +1377,7 @@
       <c r="F29" t="n">
         <v>7</v>
       </c>
-      <c r="G29" s="2" t="n">
+      <c r="G29" s="1" t="n">
         <v>46016.83585648148</v>
       </c>
     </row>
@@ -1422,7 +1410,7 @@
       <c r="F30" t="n">
         <v>7</v>
       </c>
-      <c r="G30" s="2" t="n">
+      <c r="G30" s="1" t="n">
         <v>46021.76263888889</v>
       </c>
     </row>
@@ -1455,7 +1443,7 @@
       <c r="F31" t="n">
         <v>7</v>
       </c>
-      <c r="G31" s="2" t="n">
+      <c r="G31" s="1" t="n">
         <v>46021.67972222222</v>
       </c>
     </row>
@@ -1488,7 +1476,7 @@
       <c r="F32" t="n">
         <v>7</v>
       </c>
-      <c r="G32" s="2" t="n">
+      <c r="G32" s="1" t="n">
         <v>46020.57922453704</v>
       </c>
     </row>
@@ -1521,7 +1509,7 @@
       <c r="F33" t="n">
         <v>7</v>
       </c>
-      <c r="G33" s="2" t="n">
+      <c r="G33" s="1" t="n">
         <v>46024.68756944445</v>
       </c>
     </row>
@@ -1554,7 +1542,7 @@
       <c r="F34" t="n">
         <v>7</v>
       </c>
-      <c r="G34" s="2" t="n">
+      <c r="G34" s="1" t="n">
         <v>46027.9807175926</v>
       </c>
     </row>
@@ -1587,7 +1575,7 @@
       <c r="F35" t="n">
         <v>7</v>
       </c>
-      <c r="G35" s="2" t="n">
+      <c r="G35" s="1" t="n">
         <v>46022.6518287037</v>
       </c>
     </row>
@@ -1620,7 +1608,7 @@
       <c r="F36" t="n">
         <v>7</v>
       </c>
-      <c r="G36" s="2" t="n">
+      <c r="G36" s="1" t="n">
         <v>46026.83275462963</v>
       </c>
     </row>
@@ -1653,7 +1641,7 @@
       <c r="F37" t="n">
         <v>7</v>
       </c>
-      <c r="G37" s="2" t="n">
+      <c r="G37" s="1" t="n">
         <v>46027.8478587963</v>
       </c>
     </row>
@@ -1686,7 +1674,7 @@
       <c r="F38" t="n">
         <v>7</v>
       </c>
-      <c r="G38" s="2" t="n">
+      <c r="G38" s="1" t="n">
         <v>46028.58846064815</v>
       </c>
     </row>
@@ -1719,7 +1707,7 @@
       <c r="F39" t="n">
         <v>7</v>
       </c>
-      <c r="G39" s="2" t="n">
+      <c r="G39" s="1" t="n">
         <v>46024.63475694445</v>
       </c>
     </row>
@@ -1752,7 +1740,7 @@
       <c r="F40" t="n">
         <v>7</v>
       </c>
-      <c r="G40" s="2" t="n">
+      <c r="G40" s="1" t="n">
         <v>46028.55980324074</v>
       </c>
     </row>
@@ -1785,7 +1773,7 @@
       <c r="F41" t="n">
         <v>7</v>
       </c>
-      <c r="G41" s="2" t="n">
+      <c r="G41" s="1" t="n">
         <v>46028.55981481481</v>
       </c>
     </row>
@@ -1818,7 +1806,7 @@
       <c r="F42" t="n">
         <v>7</v>
       </c>
-      <c r="G42" s="2" t="n">
+      <c r="G42" s="1" t="n">
         <v>46027.97922453703</v>
       </c>
     </row>
@@ -1851,7 +1839,7 @@
       <c r="F43" t="n">
         <v>7</v>
       </c>
-      <c r="G43" s="2" t="n">
+      <c r="G43" s="1" t="n">
         <v>46024.5834837963</v>
       </c>
     </row>
@@ -1884,7 +1872,7 @@
       <c r="F44" t="n">
         <v>7</v>
       </c>
-      <c r="G44" s="2" t="n">
+      <c r="G44" s="1" t="n">
         <v>46028.66583333333</v>
       </c>
     </row>
@@ -1917,7 +1905,7 @@
       <c r="F45" t="n">
         <v>7</v>
       </c>
-      <c r="G45" s="2" t="n">
+      <c r="G45" s="1" t="n">
         <v>46024.93770833333</v>
       </c>
     </row>
@@ -1950,7 +1938,7 @@
       <c r="F46" t="n">
         <v>7</v>
       </c>
-      <c r="G46" s="2" t="n">
+      <c r="G46" s="1" t="n">
         <v>46028.35501157407</v>
       </c>
     </row>
@@ -1983,7 +1971,7 @@
       <c r="F47" t="n">
         <v>7</v>
       </c>
-      <c r="G47" s="2" t="n">
+      <c r="G47" s="1" t="n">
         <v>46022.39336805556</v>
       </c>
     </row>
@@ -2016,7 +2004,7 @@
       <c r="F48" t="n">
         <v>7</v>
       </c>
-      <c r="G48" s="2" t="n">
+      <c r="G48" s="1" t="n">
         <v>46026.54633101852</v>
       </c>
     </row>
@@ -2049,7 +2037,7 @@
       <c r="F49" t="n">
         <v>7</v>
       </c>
-      <c r="G49" s="2" t="n">
+      <c r="G49" s="1" t="n">
         <v>46031.73576388889</v>
       </c>
     </row>
@@ -2082,7 +2070,7 @@
       <c r="F50" t="n">
         <v>7</v>
       </c>
-      <c r="G50" s="2" t="n">
+      <c r="G50" s="1" t="n">
         <v>46031.95108796296</v>
       </c>
     </row>
@@ -2115,7 +2103,7 @@
       <c r="F51" t="n">
         <v>7</v>
       </c>
-      <c r="G51" s="2" t="n">
+      <c r="G51" s="1" t="n">
         <v>46031.9371875</v>
       </c>
     </row>
@@ -2148,7 +2136,7 @@
       <c r="F52" t="n">
         <v>7</v>
       </c>
-      <c r="G52" s="2" t="n">
+      <c r="G52" s="1" t="n">
         <v>46031</v>
       </c>
     </row>
@@ -2181,7 +2169,7 @@
       <c r="F53" t="n">
         <v>7</v>
       </c>
-      <c r="G53" s="2" t="n">
+      <c r="G53" s="1" t="n">
         <v>46036.04166666666</v>
       </c>
     </row>
@@ -2214,7 +2202,7 @@
       <c r="F54" t="n">
         <v>7</v>
       </c>
-      <c r="G54" s="2" t="n">
+      <c r="G54" s="1" t="n">
         <v>46034.85805555555</v>
       </c>
     </row>
@@ -2247,7 +2235,7 @@
       <c r="F55" t="n">
         <v>7</v>
       </c>
-      <c r="G55" s="2" t="n">
+      <c r="G55" s="1" t="n">
         <v>46030.97083333333</v>
       </c>
     </row>
@@ -2280,7 +2268,7 @@
       <c r="F56" t="n">
         <v>7</v>
       </c>
-      <c r="G56" s="2" t="n">
+      <c r="G56" s="1" t="n">
         <v>46034.398125</v>
       </c>
     </row>
@@ -2313,7 +2301,7 @@
       <c r="F57" t="n">
         <v>7</v>
       </c>
-      <c r="G57" s="2" t="n">
+      <c r="G57" s="1" t="n">
         <v>46031.4957175926</v>
       </c>
     </row>
@@ -2346,7 +2334,7 @@
       <c r="F58" t="n">
         <v>7</v>
       </c>
-      <c r="G58" s="2" t="n">
+      <c r="G58" s="1" t="n">
         <v>46030.26724537037</v>
       </c>
     </row>
@@ -2379,7 +2367,7 @@
       <c r="F59" t="n">
         <v>7</v>
       </c>
-      <c r="G59" s="2" t="n">
+      <c r="G59" s="1" t="n">
         <v>46030.91600694445</v>
       </c>
     </row>
@@ -2412,7 +2400,7 @@
       <c r="F60" t="n">
         <v>7</v>
       </c>
-      <c r="G60" s="2" t="n">
+      <c r="G60" s="1" t="n">
         <v>46033.54909722223</v>
       </c>
     </row>
@@ -2445,7 +2433,7 @@
       <c r="F61" t="n">
         <v>7</v>
       </c>
-      <c r="G61" s="2" t="n">
+      <c r="G61" s="1" t="n">
         <v>46030.50267361111</v>
       </c>
     </row>
@@ -2478,7 +2466,7 @@
       <c r="F62" t="n">
         <v>7</v>
       </c>
-      <c r="G62" s="2" t="n">
+      <c r="G62" s="1" t="n">
         <v>46030.8984375</v>
       </c>
     </row>
@@ -2511,7 +2499,7 @@
       <c r="F63" t="n">
         <v>7</v>
       </c>
-      <c r="G63" s="2" t="n">
+      <c r="G63" s="1" t="n">
         <v>46029.33333333334</v>
       </c>
     </row>
@@ -2544,7 +2532,7 @@
       <c r="F64" t="n">
         <v>7</v>
       </c>
-      <c r="G64" s="2" t="n">
+      <c r="G64" s="1" t="n">
         <v>46036.73938657407</v>
       </c>
     </row>
@@ -2577,7 +2565,7 @@
       <c r="F65" t="n">
         <v>7</v>
       </c>
-      <c r="G65" s="2" t="n">
+      <c r="G65" s="1" t="n">
         <v>46039.09409722222</v>
       </c>
     </row>
@@ -2610,7 +2598,7 @@
       <c r="F66" t="n">
         <v>7</v>
       </c>
-      <c r="G66" s="2" t="n">
+      <c r="G66" s="1" t="n">
         <v>46038.76739583333</v>
       </c>
     </row>
@@ -2643,7 +2631,7 @@
       <c r="F67" t="n">
         <v>7</v>
       </c>
-      <c r="G67" s="2" t="n">
+      <c r="G67" s="1" t="n">
         <v>46042.94476851852</v>
       </c>
     </row>
@@ -2676,7 +2664,7 @@
       <c r="F68" t="n">
         <v>7</v>
       </c>
-      <c r="G68" s="2" t="n">
+      <c r="G68" s="1" t="n">
         <v>46042.74168981481</v>
       </c>
     </row>
@@ -2709,7 +2697,7 @@
       <c r="F69" t="n">
         <v>7</v>
       </c>
-      <c r="G69" s="2" t="n">
+      <c r="G69" s="1" t="n">
         <v>46042.78068287037</v>
       </c>
     </row>
@@ -2742,7 +2730,7 @@
       <c r="F70" t="n">
         <v>7</v>
       </c>
-      <c r="G70" s="2" t="n">
+      <c r="G70" s="1" t="n">
         <v>46040.41666666666</v>
       </c>
     </row>
@@ -2775,7 +2763,7 @@
       <c r="F71" t="n">
         <v>7</v>
       </c>
-      <c r="G71" s="2" t="n">
+      <c r="G71" s="1" t="n">
         <v>46039.46956018519</v>
       </c>
     </row>
@@ -2808,7 +2796,7 @@
       <c r="F72" t="n">
         <v>7</v>
       </c>
-      <c r="G72" s="2" t="n">
+      <c r="G72" s="1" t="n">
         <v>46039.19787037037</v>
       </c>
     </row>
@@ -2841,7 +2829,7 @@
       <c r="F73" t="n">
         <v>7</v>
       </c>
-      <c r="G73" s="2" t="n">
+      <c r="G73" s="1" t="n">
         <v>46037.60914351852</v>
       </c>
     </row>
@@ -2874,8 +2862,206 @@
       <c r="F74" t="n">
         <v>7</v>
       </c>
-      <c r="G74" s="2" t="n">
+      <c r="G74" s="1" t="n">
         <v>46042.45711805556</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>Qilin</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>"Qilin ransomware" OR "Qilin threat actor" OR "Qilin cyber attack"</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>DragonForce Strikes HanseMerkur International - DeXpose</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>Sat, 24 Jan 2026 00:00:00 GMT</t>
+        </is>
+      </c>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMieEFVX3lxTE1VS0VudlduV2xJRlNOSno5WHhkLVVSRXpuUFBSYWtUX3ctQlJXLUZNSGQtcDZfNFVyWTNZZU1OY21aN3R4SUVhRkN0WkxoUEJiUWVoU01Gb194enh0OXJPaTBjaDE4bk1MVmdvT0Q3ZmNhSkdBeXRFcw?oc=5</t>
+        </is>
+      </c>
+      <c r="F75" t="n">
+        <v>7</v>
+      </c>
+      <c r="G75" s="1" t="n">
+        <v>46046</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>Everest</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>"Everest ransomware" OR "Everest threat actor" OR "Everest cyber attack"</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>McDonald’s India hit by alleged Everest ransomware attack - Verdict Food Service</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>Wed, 21 Jan 2026 14:03:08 GMT</t>
+        </is>
+      </c>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMicEFVX3lxTE1hWWZCS20xM1FVTzg1YnludHZpYmExRHVQSVRfM1dHSjdRZE5PRGdKa1Rpc3kyMGZTS2NSNVZnWjA1VEJuMGRJR1czMmdrR01CODRzZk1qRndHcUdvWm45amx4eGU5emhtXzVRb3U2eFc?oc=5</t>
+        </is>
+      </c>
+      <c r="F76" t="n">
+        <v>7</v>
+      </c>
+      <c r="G76" s="1" t="n">
+        <v>46043.58550925926</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>Play</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>"Play ransomware" OR "Play threat actor" OR "Play cyber attack"</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>Play Ransomware Group Strikes Aquatic Control - DeXpose</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>Tue, 27 Jan 2026 00:00:00 GMT</t>
+        </is>
+      </c>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMieEFVX3lxTFBPWHU1UWFUUG9BbEcwZHExd1RiOWpOZ01BXzE3cG1wUkROY29qV0huN0JjaTBaOWtFdllKWWh5TXJ4LUZuTTZpTGsyS2JCbl80WDdQMS1fQWJBbDMxTXBsbGlBMWdhNVczN244MzhSVUZyS1ZaOVlVNw?oc=5</t>
+        </is>
+      </c>
+      <c r="F77" t="n">
+        <v>7</v>
+      </c>
+      <c r="G77" s="1" t="n">
+        <v>46049</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>Cl0p</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>"Cl0p ransomware" OR "Cl0p threat actor" OR "Cl0p cyber attack"</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>ShinyHunters, CL0P Return With New Claimed Victims - The Cyber Express</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>Mon, 26 Jan 2026 19:30:00 GMT</t>
+        </is>
+      </c>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiekFVX3lxTE1JWDNxNnRzN3d3NmdwVkJZRGJqaV9iY0ZVTXhWMUtfRFMzSmZpS2k1cGdVOXdRaGZZQlRqQkIyZW53ME9JRWRxUnF5TVNMUUhSRU9oaVRPeFlUbDQzb01nUzkycWZwWUZ3dHpIbnNQaUgyaGJZY2htejVR?oc=5</t>
+        </is>
+      </c>
+      <c r="F78" t="n">
+        <v>7</v>
+      </c>
+      <c r="G78" s="1" t="n">
+        <v>46048.8125</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>Devman</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>"Devman ransomware" OR "Devman threat actor" OR "Devman cyber attack"</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>Sinobi Ransomware Targets Bayside Dental in USA - DeXpose</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>Thu, 22 Jan 2026 00:00:00 GMT</t>
+        </is>
+      </c>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMie0FVX3lxTE5uSjBnRVB2aGVaUTdzSEVYSXhNcnFESVA1UXQxaWt6bi1EamhRVzZEREpmSlFVYkJhUTk5QVVpZnlnME14WGRpSXBTc3ZtcjRDdjVLSG5ZVTVyMF9ZM2F5OG1IVXpuUUJvczVEbWlVWEpHeno0TTN0bDNZSQ?oc=5</t>
+        </is>
+      </c>
+      <c r="F79" t="n">
+        <v>7</v>
+      </c>
+      <c r="G79" s="1" t="n">
+        <v>46044</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>Safepay</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>"Safepay ransomware" OR "Safepay threat actor" OR "Safepay cyber attack"</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>SafePay Ransomware Attack on Argentina’s Railway Infrastructure Firm ADIFSE - DeXpose</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>Sun, 25 Jan 2026 00:00:00 GMT</t>
+        </is>
+      </c>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMinwFBVV95cUxNZkl5T3RIVlBpUXJtRnloeWJUck5LUm9BS2N3ZF9YTFJOc09OaDczTUVGSEhHSjNFdEtjcHZ6WlJDUHFqLUZFdEJmdjg2V3hhN0o1YWFMQ2NQOW90d19hRVp0Z1lZMjVjTkEtVHJNaFJwdHJCZnByaGl2a2lwa1czWkwtYl9nd0Y1SHNJR0FPdWJ0bFZSRlBTa2pmWDIxVlE?oc=5</t>
+        </is>
+      </c>
+      <c r="F80" t="n">
+        <v>7</v>
+      </c>
+      <c r="G80" s="1" t="n">
+        <v>46047</v>
       </c>
     </row>
   </sheetData>

--- a/data/latest_ransomware_news.xlsx
+++ b/data/latest_ransomware_news.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G80"/>
+  <dimension ref="A1:G90"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3064,6 +3064,336 @@
         <v>46047</v>
       </c>
     </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>Dragonforce</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>"Dragonforce ransomware" OR "Dragonforce threat actor" OR "Dragonforce cyber attack"</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>M&amp;S attackers say they looted 97GB from German insurance giant - Cybernews</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>Tue, 03 Feb 2026 15:33:45 GMT</t>
+        </is>
+      </c>
+      <c r="E81" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMif0FVX3lxTE1teUJfeFVBbTVDZmp5NkRlNmZGb2I0WWV2dXFrVmFNRmN2SjB1MjhZZWdjZEVtdk5ralh4bXZTYUFDNzdSaDB4Sld5OVdZYjNFb3gweTA0cXM2MkJ5YUpwRzRpSG5hbkVQcDN4eW00UDFfazN2cmRGeEx2UldoNjA?oc=5</t>
+        </is>
+      </c>
+      <c r="F81" t="n">
+        <v>7</v>
+      </c>
+      <c r="G81" s="1" t="n">
+        <v>46056.6484375</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>Qilin</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>"Qilin ransomware" OR "Qilin threat actor" OR "Qilin cyber attack"</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>Qilin ransomware gang claims breach of Tulsa International Airport, posts alleged data samples - teiss</t>
+        </is>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>Tue, 03 Feb 2026 21:13:59 GMT</t>
+        </is>
+      </c>
+      <c r="E82" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMi0wFBVV95cUxOV1d1LS1TUFdmZWxlMDZLS0lXazFBU0FzWHF2dlYxbWpDNjZKNDVWT2VUSk1KQnJRY1NXZElIMmtzUkU3R1BGQ3BabUlxeXNveVIzNkNRc0phaHdTR0lwWGpQb01RM0kxWjJGU3ptNWVXVnpFMTBuZGdXcXRLMHVOYU9lRXdFTHVmdEVnZk9vdXVEc011RHV6c054bzlrWkRMQjktNkFxVEs2WXNSMHU4ZEdNMGg1T0hNUDBmenVQRXRnSExfM3RPcWYwWGNleTBXc2ow?oc=5</t>
+        </is>
+      </c>
+      <c r="F82" t="n">
+        <v>7</v>
+      </c>
+      <c r="G82" s="1" t="n">
+        <v>46056.88471064815</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>Akira</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>"Akira ransomware" OR "Akira threat actor" OR "Akira cyber attack"</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>Ransomware Victim Numbers Rise, Despite Drop in Active Extortion Groups - Infosecurity Magazine</t>
+        </is>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>Thu, 29 Jan 2026 13:01:00 GMT</t>
+        </is>
+      </c>
+      <c r="E83" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMigAFBVV95cUxPQW9OSS1FWmJ6WU9BNzhObW0xb09HTXVWTDdoemhKWDMtM291ckJPeDJYRnNwLVBBM1A0b2tKNjZkVHRqQ056MVJMTFIxOXEzdEViN01lcG1KZGxIb3JlZnpEcVhRdFVuOFFmLU9qcGp5aWVqakh1d3RjdFlaVTRLYg?oc=5</t>
+        </is>
+      </c>
+      <c r="F83" t="n">
+        <v>7</v>
+      </c>
+      <c r="G83" s="1" t="n">
+        <v>46051.54236111111</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>Everest</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>"Everest ransomware" OR "Everest threat actor" OR "Everest cyber attack"</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>Was Your Data Exposed in the Latest Under Armour Breach? Here’s What You Should Do - Bitdefender</t>
+        </is>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>Mon, 02 Feb 2026 12:11:15 GMT</t>
+        </is>
+      </c>
+      <c r="E84" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMizwFBVV95cUxOUXRRbHE0ZUIxakNhdi00MF9ld2NVZ2dBRWU5ekRuM2ZYVUkwUzFWVW9JT0g5SEFZWHFEZHFtOWd3TE5MZlFGVHFlYmp3LTJoR1VaNExyYkZmMUVxZlhLVkczZVBBbi0tNVo2RVpyRTFNZHdSdGJNZ2UxVVJyZzU5aFhMamtpTGhEaWpLS1dkN0dXMEhURXJ2S0hGLVgyTFhpV1NDcXVRa09SbzRKM0M2X1p5Y1Z1RjhQWGticGtPRnlXSUVrYWRobzVvTkViS1U?oc=5</t>
+        </is>
+      </c>
+      <c r="F84" t="n">
+        <v>7</v>
+      </c>
+      <c r="G84" s="1" t="n">
+        <v>46055.5078125</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>LockBit</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>"LockBit ransomware" OR "LockBit threat actor" OR "LockBit cyber attack"</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>Hackers attempt to extort parents after school refuses to pay ransom fee - The Record from Recorded Future News</t>
+        </is>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>Mon, 02 Feb 2026 13:06:48 GMT</t>
+        </is>
+      </c>
+      <c r="E85" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMilwFBVV95cUxOajlqLTl6ZkszY0dpOGVINVN6TmswTVgwQ1k1RXNFR0tGQktpWUJKcnVTSVNHSEpiaThocTBralRFNVZTOHZqZzNybWZldC1DRzZJX2hvMklzRnJib1ZZQjVVbFRfSlFaYUIzeGQ5T0Z1Z2RKZlp5VVFVTmhPMG5ybThqM3liQjJyUFVFOExRV29WN3dYRXY0?oc=5</t>
+        </is>
+      </c>
+      <c r="F85" t="n">
+        <v>7</v>
+      </c>
+      <c r="G85" s="1" t="n">
+        <v>46055.54638888889</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>Medusa</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>"Medusa ransomware" OR "Medusa threat actor" OR "Medusa cyber attack"</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>This new phishing campaign can tailor its messages to target you with your favorite businesses - MSN</t>
+        </is>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>Fri, 30 Jan 2026 06:58:32 GMT</t>
+        </is>
+      </c>
+      <c r="E86" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMi-AJBVV95cUxOSjZrOVhyTGJfc290YWZ4clRPNkEwVWFVMHV0MmxvNGJ5MExwT0d3UVFDQW5oVUwxR0V3dTVqSFNab01DSkJwTWx6WEU2ekwzNGhYejhnWDJOUmRnYnBMZmFFUjBMY1Vxemg4RzhfYUhJd0U2THRXUjBMcmRsOWhnai02Rk5jalBSanVMblZnclRURkhIcXNNTmUxT1NCYkhtNnY2MGpqQmVRa1VmZG1xWnZsUFN3VTFzeFl6T3RmYTdzUXZVc0M0QlQxbUVPTjZSQ1ZPMjJodzlNZ085RGtMdjhqU2ZPMHotbllTbzd1eFBUaVZBa3A4dWZ4TVdydmhzYU5ZWU1uRG5ld0RCcmxSQVVTd1IyQVgwUWJXSkFoSC1YcFRnaUUwTWdIR2NDNHZmMF81amwzeEZDX3NDbnVXX2ZHMW5tZHlqN2RNSXM1MEtIR2NQTFhETHJxclg5WmpQNE1FYjM0R0JyOWl6bzQ1NVd0czhWREZu?oc=5</t>
+        </is>
+      </c>
+      <c r="F86" t="n">
+        <v>7</v>
+      </c>
+      <c r="G86" s="1" t="n">
+        <v>46052.29064814815</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>Medusa</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>"Medusa ransomware" OR "Medusa threat actor" OR "Medusa cyber attack"</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>"Slopsquatting" attacks are using AI-hallucinated names resembling popular libraries to spread malware - MSN</t>
+        </is>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>Fri, 30 Jan 2026 12:14:59 GMT</t>
+        </is>
+      </c>
+      <c r="E87" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMigANBVV95cUxNRmJBSjlSbW5IRk5HR3JKWlpoSl9QTk9xN3RKQmMzZnRfMmQxWGJGUkVVd0ZIR3l3eWdvQ1I5UVlrRWpUT3laY1BfbjB1TjNsVkZHMFJ2TDRYR18tczJ4bmZLcVlreUZpUktxV1I5REdhMkNTYmpSQm1ydVROcGsydVBnM3dFNWc4SzJnU2FYbDFWcXpXSW1BRWd1dHU4ZnBMeEtuTXc2cVZhVVJ5c2VnT0RYbEVMRmdfYUxMZEdjYm0ySDVSOGtmZWFqd3VTSVpBaWctNExxc0dwMnhqVHhBcHBlNEUxU2NXVlVzdzhNa2YyN2pBT3dxbzBBMndLWU4tMzlhWGNkQ1VZdU1MaWJDNzhRODZ3dE1qTXVMZlVSTDVsTHI5U0pfam1SWnA3YlR0d0hIS05WZ2lsY0ZRdUplcTcyemxNTHNVQUFTUE4xc0tGOG1FZDNtMmctQUY0cTZSTm96Q3RUN0RXMEd6dkVCSFE4YTNWRnNFNDRSMjlfdnA?oc=5</t>
+        </is>
+      </c>
+      <c r="F87" t="n">
+        <v>7</v>
+      </c>
+      <c r="G87" s="1" t="n">
+        <v>46052.51040509259</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>Cl0p</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>"Cl0p ransomware" OR "Cl0p threat actor" OR "Cl0p cyber attack"</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>Cyber Threats - Cl0p ransomware gang claims cyberattack on Hilton, alleged breach unconfirmed - teiss</t>
+        </is>
+      </c>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>Wed, 28 Jan 2026 21:29:33 GMT</t>
+        </is>
+      </c>
+      <c r="E88" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMivAFBVV95cUxNTnpRc0tZT01BSGZ5MGt3WTEyVzJpQmQzYzJaZzZzOGd0ekJtV1dwQ1RRNTFaTDYwZ01tanl5MEdIc0lRUl9sUENPaTZzSHdNYmlRV1p5eW5EdGROeGJCb1RTd003MUpyQzVHbWY5UnMzQW56TkdueDNrUEltVWNNZG5ocW5EMTFoS2dRRGdwd3c5TTV1ZnE4dm1mcnU5dXdwamtDN3lfclVKN0pMRFhldFFOTjk4SzFtYXg2VQ?oc=5</t>
+        </is>
+      </c>
+      <c r="F88" t="n">
+        <v>7</v>
+      </c>
+      <c r="G88" s="1" t="n">
+        <v>46050.89552083334</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>Cl0p</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>"Cl0p ransomware" OR "Cl0p threat actor" OR "Cl0p cyber attack"</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>Baltimore City Health Department investigates data breach involving insurance eligibility files - teiss</t>
+        </is>
+      </c>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>Wed, 28 Jan 2026 21:29:33 GMT</t>
+        </is>
+      </c>
+      <c r="E89" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMi1gFBVV95cUxPV0xveGh0Mm52V3ZZZGpUWDhPaDV0UElEYXNPT1UxaUhwUk9sN1g5U3AyN2MtYmhQX1lmcTZjdFBydGtuNFlPNXJMWllkaThuaTFLWVc3TUxUeTB6aDNSTnpRV1Bsc2kxZHp2anZwSDBrZHZlOXUyUHlhZUhYNTl2Wm80Y1BjOXZsS2s1YVY3ZEp3QUE5T1BuMXZfY1RtZkhYMG1ndjBJejN2bVE3WTUwdkh2UkFNa01zcTgya0FLYzBXdTk4WUZReG4tdUVOSGlqUEdJd05n?oc=5</t>
+        </is>
+      </c>
+      <c r="F89" t="n">
+        <v>7</v>
+      </c>
+      <c r="G89" s="1" t="n">
+        <v>46050.89552083334</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>Cl0p</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>"Cl0p ransomware" OR "Cl0p threat actor" OR "Cl0p cyber attack"</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>Anywhere Real Estate Data Breach Lawsuit Investigation - Claim Depot</t>
+        </is>
+      </c>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>Mon, 02 Feb 2026 17:03:45 GMT</t>
+        </is>
+      </c>
+      <c r="E90" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMihgFBVV95cUxOcHY3T0pWOFNqYWVnbl9DbVkyVnp5SjZDM2lBUVJSNUx3RnZKa19IVHRCX1lrYXJ1VkQ5RU9BUWZYZ2JQa2RwWjEtd3JPQ3RHWjBjbUJkbTB4TnBCRFV0dThfY3ZiZjJxcUFMOVpzQk9tN29FN0Zob3dhaWJ0VkUydWRsRGtNZw?oc=5</t>
+        </is>
+      </c>
+      <c r="F90" t="n">
+        <v>7</v>
+      </c>
+      <c r="G90" s="1" t="n">
+        <v>46055.7109375</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/latest_ransomware_news.xlsx
+++ b/data/latest_ransomware_news.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G90"/>
+  <dimension ref="A1:G101"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3394,6 +3394,369 @@
         <v>46055.7109375</v>
       </c>
     </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>Dragonforce</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>"Dragonforce ransomware" OR "Dragonforce threat actor" OR "Dragonforce cyber attack"</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>DragonForce Ransomware Campaign Steals Sensitive Information From Businesses - Cyber Press</t>
+        </is>
+      </c>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>Thu, 05 Feb 2026 11:03:25 GMT</t>
+        </is>
+      </c>
+      <c r="E91" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiakFVX3lxTE52dXNBWTRpOWtuRkZKY3I0aUNXTHRGcGpZTllKTGc5dmVHdWhjcXFsOVVrM3JrWlpQNXdRUW05VG01cjh1QkExbEZzVWdOM3JsV3haYWtkN1hUNHd3a3JKbWpia05uOFZBdmc?oc=5</t>
+        </is>
+      </c>
+      <c r="F91" t="n">
+        <v>7</v>
+      </c>
+      <c r="G91" s="1" t="n">
+        <v>46058.46070601852</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>Dragonforce</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>"Dragonforce ransomware" OR "Dragonforce threat actor" OR "Dragonforce cyber attack"</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>DragonForce purports breach of leading German insurer - SC Media</t>
+        </is>
+      </c>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>Thu, 05 Feb 2026 00:45:35 GMT</t>
+        </is>
+      </c>
+      <c r="E92" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiiwFBVV95cUxQSjA2TDhUelZ4bzk5RjRGdi12MkhKWlN6NUxOZGp0OTNlY04xTmszazJOenp0OUswUGVJTWJ5RG1WSG5hT2Y1TC1XRUU5SWcwOEVSUUk2Q1VUemNubDRoWmN1WERqRXVuMEVIZXVsWWM5MVN0clZtOWo5TlhsSGZWWldhYkYxa0J3U0dJ?oc=5</t>
+        </is>
+      </c>
+      <c r="F92" t="n">
+        <v>7</v>
+      </c>
+      <c r="G92" s="1" t="n">
+        <v>46058.03165509259</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>Qilin</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>"Qilin ransomware" OR "Qilin threat actor" OR "Qilin cyber attack"</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>Romanian oil pipeline operator Conpet discloses cyberattack - BleepingComputer</t>
+        </is>
+      </c>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>Thu, 05 Feb 2026 15:15:49 GMT</t>
+        </is>
+      </c>
+      <c r="E93" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiwgFBVV95cUxPQko2WThaMjVqYUUxQ0VfaTVYekdHREp1S2xTR2tZc3JGdjdTcGZFcW1pOUloYjNyT3drTFNFcGVLRG8ybVFETXd6ZjZNNlRrN3hVN1paVHRHdG55TnpGdWgxMHhqOHdzdGJLS3AzeWdYam9XZ1Bub3NCY2NGeEpQU2Q5WlVoX0dNYVZiLUtKNk10aF9KaE5JV2hGczNMLU9DYWxZUzhWbjR0WXZTRHBhWnN4dU84NF92RWR4QmpYeWlHUdIBxwFBVV95cUxNcThNNHFreENPRnBCX0hIT2pCdzFhM1FhMHYzM3YzM0ZIV0tVdUt0SVkzakEzX0ltTXozb1ZkNGRacVYybklQV3ZpV3B6SkF0dl8zTEJaOE51cWR1TjdkNi0yYndqYlRKQ05FVDZrem44UGJZclB1ZzFHRkdYZzFQOWN5Z1hNcjFnOWZHZmxHRnZzLXFMb3ZvUVRBdDNnTGFRYVBja20yVGhwdFI1elhWSVR5VzBRZGRsbUNaUzNkckFLVTF4VWpR?oc=5</t>
+        </is>
+      </c>
+      <c r="F93" t="n">
+        <v>7</v>
+      </c>
+      <c r="G93" s="1" t="n">
+        <v>46058.6359837963</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>Everest</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>"Everest ransomware" OR "Everest threat actor" OR "Everest cyber attack"</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>Discord Announces Global Age Verification Program Coming Early March 2026 - TechPowerUp</t>
+        </is>
+      </c>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>Mon, 09 Feb 2026 22:41:51 GMT</t>
+        </is>
+      </c>
+      <c r="E94" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMisgFBVV95cUxNRXRHd2U2MEVQUDF6N0tGTU03ODhCdk1JNVBaZVlmNWo1TTVtT2tBVS1PLUdqX25QTFYwampwQW1mRVdqVzZQanRqN3dvZUNacTg0WWpqSXRZTlQ5TzZKN3QwNnlXU1hLSWxBMkVXTnJSWU56aTFpTlIzNk9ZcFpIUWZza2JWV1VXUjNhZ3VvNFI3SUk0b3JiVUlOaElGWWZQakZPWE92dVNncnBJV014M2dn0gGyAUFVX3lxTE1FdEd3ZTYwRVBQMXo3S0ZNTTc4OEJ2TUk1UFplWWY1ajVNNW1Pa0FVLU8tR2pfblBMVjBqanBBbWZFV2pXNlBqdGo3d29lQ1pxODRZampJdFlOVDlPNko3dDA2eVdTWEtJbEEyRVdOclJZTnppMWlOUjM2T1lwWkhRZnNrYlZXVVdSM2FndW80UjdJSTRvcmJVSU5oSUZZZlBqRk9YT3Z1U2dycElXTXgzZ2c?oc=5</t>
+        </is>
+      </c>
+      <c r="F94" t="n">
+        <v>7</v>
+      </c>
+      <c r="G94" s="1" t="n">
+        <v>46062.94572916667</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>Everest</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>"Everest ransomware" OR "Everest threat actor" OR "Everest cyber attack"</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>Data Breach Threatens Under Armour’s Brand Integrity - StocksToTrade</t>
+        </is>
+      </c>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>Tue, 10 Feb 2026 19:05:00 GMT</t>
+        </is>
+      </c>
+      <c r="E95" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMigAFBVV95cUxONTU4b2FMZ2JkaW1od2pvRWROcDJXd29rZFFCeVZMcEdzVzJEdEdLREpZblNrdWxEZ2dnQUgzdlRZX0k2S2lGQVlOUktxZVJiOWdQVXhUXzc3WG1WZjl5LXNZYU41TDRNUEtHbE9Na3RZZmNlT2Z2Y1VZTXVMM0hzSA?oc=5</t>
+        </is>
+      </c>
+      <c r="F95" t="n">
+        <v>7</v>
+      </c>
+      <c r="G95" s="1" t="n">
+        <v>46063.79513888889</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>Everest</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>"Everest ransomware" OR "Everest threat actor" OR "Everest cyber attack"</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>Catalyst RCM Data Breach Lawsuit Investigation - Claim Depot</t>
+        </is>
+      </c>
+      <c r="D96" t="inlineStr">
+        <is>
+          <t>Mon, 09 Feb 2026 19:54:26 GMT</t>
+        </is>
+      </c>
+      <c r="E96" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMie0FVX3lxTE9kVHpzNGgyZDFBdGlhdkRCZTFnbXZLclRJLUxNZXhWeE15Z3N2eU9qSEF0eW1UekJQUnBfaGFyYmxrSXlfNEVhMTE4S3NvaU93TllSNWw1ZTBueGFUeG1xYThDQkZsSlBYMHltd3pHOUdzdDlqaldISUl6MA?oc=5</t>
+        </is>
+      </c>
+      <c r="F96" t="n">
+        <v>7</v>
+      </c>
+      <c r="G96" s="1" t="n">
+        <v>46062.82946759259</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>Lynx</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>"Lynx ransomware" OR "Lynx threat actor" OR "Lynx cyber attack"</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>Criminals blackmail toothbrush manufacturer Trisa - blue News</t>
+        </is>
+      </c>
+      <c r="D97" t="inlineStr">
+        <is>
+          <t>Tue, 10 Feb 2026 13:44:00 GMT</t>
+        </is>
+      </c>
+      <c r="E97" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMimAFBVV95cUxNMjY4RURYcElJZld1Y1VKOS1XUFZKREtZaW0wX01jOE1TZlpSNUxKbWx0ZVFUWDdnVUZuZzBRa21jU3dKLWthb3B0cmkteF9lMXVnNUhnRk9NNk5ieHowMXFYWDRweENiZVpoSTRseXdsV1NRRTR1U0ZFZk43N0QtR3psUVU4SkZaOFhRZE1jM0xJWkpCVDFxSw?oc=5</t>
+        </is>
+      </c>
+      <c r="F97" t="n">
+        <v>7</v>
+      </c>
+      <c r="G97" s="1" t="n">
+        <v>46063.57222222222</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>Medusa</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>"Medusa ransomware" OR "Medusa threat actor" OR "Medusa cyber attack"</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>Thousands of websites have now been hijacked by this devious, and growing, malicious scheme - MSN</t>
+        </is>
+      </c>
+      <c r="D98" t="inlineStr">
+        <is>
+          <t>Mon, 09 Feb 2026 00:41:18 GMT</t>
+        </is>
+      </c>
+      <c r="E98" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMi8AJBVV95cUxNNnJJakctbWY0UUlob1YtWmxXTUI0SnF5cHdhQkJFcjFFZjF5Vl9MR3RLZThldmlYcDdsT3ZZNURSVy0xb0NSVUw4NHZjVFpXZlhfTG82cUxXYUNaRjhzSGtFX0ZudER3U1g5NXlDRndtdklmNUd4NHdOa2RhVE9GTFpJWDJjSDV3OWlPMUVhTnRHbjkzcWJIRDcwYU52OThKMVRvZ1dyQ3YxN3NqdTBOVFgzQ1h3VjFMTlRmd2wydnJCck9pcWNWcU9ybTQ0Q3YtU19wWXpINEFXTFpRLUU4d2pSTk9aUGcxWThVMXFpWmxGeUM0R3htVGQ1S2ZFd01vVDFkYloyaEdOellPMm1vb2Zfa1JSOEN3UFpJSW9DdjBzcGN5SUFqaGZ3TWc0UVdWWkphMXFsM244Z3pqSk41SndrOU1IWVFYU2JMdWtSUC1wNUlHemZxQzQyS1prN1BIeS1NZkhFTjJjQlJOOE9fdQ?oc=5</t>
+        </is>
+      </c>
+      <c r="F98" t="n">
+        <v>7</v>
+      </c>
+      <c r="G98" s="1" t="n">
+        <v>46062.02868055556</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>Interlock</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>"Interlock ransomware" OR "Interlock threat actor" OR "Interlock cyber attack"</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>Rancher Manager Security Bug Could Allow Attackers to Steal Admin Credentials - Cyber Press</t>
+        </is>
+      </c>
+      <c r="D99" t="inlineStr">
+        <is>
+          <t>Wed, 04 Feb 2026 12:45:07 GMT</t>
+        </is>
+      </c>
+      <c r="E99" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiYkFVX3lxTE1BV253QmF2UlJLaXFqcy1mLUl3M0JGMjE3N3VKNHpuODQwSGVyTkFEWXBLRUxuVjVwMElJNHFFMnBVMHFtcGhDSHh0aGhORTY5bkdEVEFFUW0xRjJ5bjBCOEpB?oc=5</t>
+        </is>
+      </c>
+      <c r="F99" t="n">
+        <v>7</v>
+      </c>
+      <c r="G99" s="1" t="n">
+        <v>46057.53133101852</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>Safepay</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>"Safepay ransomware" OR "Safepay threat actor" OR "Safepay cyber attack"</t>
+        </is>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>More than 25M compromised by Conduent hack - SC Media</t>
+        </is>
+      </c>
+      <c r="D100" t="inlineStr">
+        <is>
+          <t>Fri, 06 Feb 2026 23:25:54 GMT</t>
+        </is>
+      </c>
+      <c r="E100" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMifEFVX3lxTFA4dnJvQ3RuMEREbi1pZWlpWXQ3OU40VTZ6SWFWeW5abFlQRnVhVThFdWl1bWtVMURNY0FGenp6aWdMZzBnT2JsTWo1UkZyZG1NWEhZeW5pT0Y5X19IeU5nNGZfTVc5Z1Q5SGFYUkUzTFE3R0JRZXZrQ0h6VkY?oc=5</t>
+        </is>
+      </c>
+      <c r="F100" t="n">
+        <v>7</v>
+      </c>
+      <c r="G100" s="1" t="n">
+        <v>46059.97631944445</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>Safepay</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>"Safepay ransomware" OR "Safepay threat actor" OR "Safepay cyber attack"</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>Data breach exposes personal data of 25M Americans - Fox Business</t>
+        </is>
+      </c>
+      <c r="D101" t="inlineStr">
+        <is>
+          <t>Tue, 10 Feb 2026 17:57:00 GMT</t>
+        </is>
+      </c>
+      <c r="E101" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMilAFBVV95cUxPMlNidFJHcWk5ZHNTWk92WWZENFRPdWR5N0tiNFRrNTh1S2hSZHZqOXUyS1B2MldpcUFJUlZIbXNrN3c2a1NWb3dFaXZYaTgtTU5YSjUyRnl1bXRNelN1TEdfN3VHelZpbHZOb0t5MkNWalpiWGg3UzA1UkF5Y2ZTajdYVERic3hhQmticUhwcmFZUE130gGUAUFVX3lxTE8yU2J0UkdxaTlkc1NaT3ZZZkQ0VE91ZHk3S2I0VGs1OHVLaFJkdmo5dTJLUHYyV2lxQUlSVkhtc2s3dzZrU1Zvd0VpdlhpOC1NTlhKNTJGeXVtdE16U3VMR183dUd6Vmlsdk5vS3kyQ1ZqWmJYaDdTMDVSQXljZlNqN1hURGJzeGFCa2JxSHByYVlQTXc?oc=5</t>
+        </is>
+      </c>
+      <c r="F101" t="n">
+        <v>7</v>
+      </c>
+      <c r="G101" s="1" t="n">
+        <v>46063.74791666667</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/latest_ransomware_news.xlsx
+++ b/data/latest_ransomware_news.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G101"/>
+  <dimension ref="A1:G113"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3757,6 +3757,402 @@
         <v>46063.74791666667</v>
       </c>
     </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>Dragonforce</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>"Dragonforce ransomware" OR "Dragonforce threat actor" OR "Dragonforce cyber attack"</t>
+        </is>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>Cyber Crime - DragonForce ransomware group targeted 363 companies in just two years - teiss</t>
+        </is>
+      </c>
+      <c r="D102" t="inlineStr">
+        <is>
+          <t>Mon, 16 Feb 2026 16:33:19 GMT</t>
+        </is>
+      </c>
+      <c r="E102" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiqAFBVV95cUxNNlB3M3RFdm1MVjBDdFRxU2IyZTQ2Vko5RE1CeGRqbUl4Z2tsNzN6NFpuSUppY3JKU1EzUkctc1JtcE1JcFNVOGFYUWczRXZPcGwyWW5qLVgzdVR2YlJxOVpOaTFkdm13cGptNXlPOV80cHBkZmlESHFEZVhxaC1jZFJiTG9nanlha1pyN2dFX1hKUzNrcm9fblR2TEJzVUV0azZFaWU4MVc?oc=5</t>
+        </is>
+      </c>
+      <c r="F102" t="n">
+        <v>7</v>
+      </c>
+      <c r="G102" s="1" t="n">
+        <v>46069.68980324074</v>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>Qilin</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>"Qilin ransomware" OR "Qilin threat actor" OR "Qilin cyber attack"</t>
+        </is>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>Qilin attack-related breach confirmed by Conpet - SC Media</t>
+        </is>
+      </c>
+      <c r="D103" t="inlineStr">
+        <is>
+          <t>Fri, 13 Feb 2026 21:35:39 GMT</t>
+        </is>
+      </c>
+      <c r="E103" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMigwFBVV95cUxOR3dOaUdyaFdydXFLdjN0bExScUVmQXhwc0o0R3lYY1J0eUQ0eElCRGhQTmM1blMyZkNGbmtZeWt3clhwa2FMSl9zczc5V0doMjdVbGRqbVVQdlhqNHNhYUIwNzduMld4NVlZYnE4S0N4S0FKU0c2UHRwQlpCZHVWNTItYw?oc=5</t>
+        </is>
+      </c>
+      <c r="F103" t="n">
+        <v>7</v>
+      </c>
+      <c r="G103" s="1" t="n">
+        <v>46066.89975694445</v>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>Qilin</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>"Qilin ransomware" OR "Qilin threat actor" OR "Qilin cyber attack"</t>
+        </is>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>Georgia healthcare company data breach impacts more than 620,000 - The Record from Recorded Future News</t>
+        </is>
+      </c>
+      <c r="D104" t="inlineStr">
+        <is>
+          <t>Wed, 11 Feb 2026 19:28:24 GMT</t>
+        </is>
+      </c>
+      <c r="E104" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMigwFBVV95cUxPTjZ6d2k1NkJTbVdUdVdHWFV2ZzVFdXByckFCZHVEbFZ3V2F0MzVBTFNyeEpHUmoyaHNFQUdaTUowbU8yYVRNdUU2R21KaGQ0MWdnYUlNQUoxWEZRVkh4UnhuMFRydFFNQVhUazY4bGhXUVNGN1J6ak5PamlaN2hQNk13SQ?oc=5</t>
+        </is>
+      </c>
+      <c r="F104" t="n">
+        <v>7</v>
+      </c>
+      <c r="G104" s="1" t="n">
+        <v>46064.81138888889</v>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>Qilin</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>"Qilin ransomware" OR "Qilin threat actor" OR "Qilin cyber attack"</t>
+        </is>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>News - Odido cyberattack exposes personal data of 6.2 million customers in the Netherlands - teiss</t>
+        </is>
+      </c>
+      <c r="D105" t="inlineStr">
+        <is>
+          <t>Fri, 13 Feb 2026 13:17:59 GMT</t>
+        </is>
+      </c>
+      <c r="E105" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiuAFBVV95cUxNTWttSnFQNWR4andYV2hDd3lyYXlmQ0lEZkpaYlBWaWZ2bGk1eTI0RHpZc0wwMnl0UnpOZWF0aVNUS3ozUFl0REIwR0xYRk8wX1ZFSm5CNDA5bjRCQlBvcFVPWDA4ejlIV19mTGRlZzRCOEZ1VENVSWFoUUU0QUFPamo5dHVsNDM5cjFFZ3d1U3pxaHZGTzJnWU1JQkRubDI3bEl5emNMZ29fY0gtUlhmSmI4VDFSc2lF?oc=5</t>
+        </is>
+      </c>
+      <c r="F105" t="n">
+        <v>7</v>
+      </c>
+      <c r="G105" s="1" t="n">
+        <v>46066.55415509259</v>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>Qilin</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>"Qilin ransomware" OR "Qilin threat actor" OR "Qilin cyber attack"</t>
+        </is>
+      </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>Phishing sites in PH jump 423% in 2025 — report - Newsbytes.PH</t>
+        </is>
+      </c>
+      <c r="D106" t="inlineStr">
+        <is>
+          <t>Mon, 16 Feb 2026 04:33:15 GMT</t>
+        </is>
+      </c>
+      <c r="E106" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMigwFBVV95cUxQSnk5MHpsaUtaUFJxcTVUSkowbjZ0QXk0bTBQc0RNbzFuNXJEbVBNbGhFVkxvZG1aWmFxN1h2bll5RE5XcTlqd2J5U0JrVjltS0V1SlF1ekVPcFdLRzBxMkxaOXY5WFdRZ2ljM1lZZDduaFkzSXEzaGpqVGsxWlFxU2VZYw?oc=5</t>
+        </is>
+      </c>
+      <c r="F106" t="n">
+        <v>7</v>
+      </c>
+      <c r="G106" s="1" t="n">
+        <v>46069.18975694444</v>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>Warlock</t>
+        </is>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>"Warlock ransomware" OR "Warlock threat actor" OR "Warlock cyber attack"</t>
+        </is>
+      </c>
+      <c r="C107" t="inlineStr">
+        <is>
+          <t>SmarterTools network breached using auth-bypass attack against single unpatched virtual machine - MSN</t>
+        </is>
+      </c>
+      <c r="D107" t="inlineStr">
+        <is>
+          <t>Wed, 11 Feb 2026 08:02:35 GMT</t>
+        </is>
+      </c>
+      <c r="E107" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMi4wFBVV95cUxPeHVYOE5aWUxnSkRSNHREdVlSSUNuMFBOUWMwaGFBZDkwN2hnMEhaU1VuMTlsakdOSzZoSWVYVG9scDNqVmM5cXVxYTFDWlZKMWNLaVN6X2RZbHdHRW1sLXRTdDRrWU5ZXzlFTjUtOGFPSVVybngzZ3hoTzY1VTF6b2plVU1UdFpqZGE3Rm9LWmxqcFVCQVBkTVF0aVp3YzNOSFJXZE1QeGFER0FtQ3c2czI4eTFubThoNEZzVk5OY2dLQlVkUmJwOGNMSS15Tng1S2MtX0twMVhCczRpdjM4cUhqWQ?oc=5</t>
+        </is>
+      </c>
+      <c r="F107" t="n">
+        <v>7</v>
+      </c>
+      <c r="G107" s="1" t="n">
+        <v>46064.33512731481</v>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>LockBit</t>
+        </is>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>"LockBit ransomware" OR "LockBit threat actor" OR "LockBit cyber attack"</t>
+        </is>
+      </c>
+      <c r="C108" t="inlineStr">
+        <is>
+          <t>Exclusive: Aeromedical Society of Australasia listed by Lockbit ransomware gang - Cyber Daily</t>
+        </is>
+      </c>
+      <c r="D108" t="inlineStr">
+        <is>
+          <t>Tue, 17 Feb 2026 23:32:07 GMT</t>
+        </is>
+      </c>
+      <c r="E108" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiuwFBVV95cUxQOERZbVBhdjVTc1NkcEU3b21MdE1EOUFzSEo2WHFreldmdnRSX216WWE5aThPUlVvaUlSbXFrNzI2NnVwRlhtS08tQzVQSjJRcEpxaU40dnFnV29TdFYxaklkSTdVZ292UHRFRE94WElTbVNkVTlTanhuOWx0ZU9VMncteTYwVEVPN083bXc5NWZHbWsyVFItODF6QnlYWVZnVENNZFVPX1ZOaDhPQWo2RlMxaE51cHFfUEJR?oc=5</t>
+        </is>
+      </c>
+      <c r="F108" t="n">
+        <v>7</v>
+      </c>
+      <c r="G108" s="1" t="n">
+        <v>46070.98063657407</v>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>Medusa</t>
+        </is>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>"Medusa ransomware" OR "Medusa threat actor" OR "Medusa cyber attack"</t>
+        </is>
+      </c>
+      <c r="C109" t="inlineStr">
+        <is>
+          <t>Cyber Attack Rumors Swirl as NASCAR Faces $4 Million Ransom Demand - MSN</t>
+        </is>
+      </c>
+      <c r="D109" t="inlineStr">
+        <is>
+          <t>Sun, 15 Feb 2026 11:57:57 GMT</t>
+        </is>
+      </c>
+      <c r="E109" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMijwNBVV95cUxNWWNwUGdTZHJSSE5OS2RjRzlHS0FtTlhKTVNQREdqYkI2T1IwalBpSDdBUW9ENmdWcVpZckMzc0lwRkpYcGthV0hkLS1KVW1TRmI0Z3k2MUVhdFU3N3ZiS2NxUlZBZmJvRU13b3loYWNyNUdIbGcxUTVPWVlsVFpaWUt4V05EamxVcDVJMHBsOWI2b1hRcUhCSzZoVTQ4dnV3d3NudDlManRTbVQtRS1lc3J4TkVXLWhab2Z5MmRmNGRrVDd3RUdaNGtobDh5WHdSWEtyT2xFczlfbEU0cXpkUnRFQ2xNdEdBRDVzQXBudTJscnBBZ3I4SlFkVU1CMS1hY0V4WUtRVWtCcmluTTdIbDNqRThzaHEtWmljaThLQ0JNZ1VESE9USExCNm9Ub0MwZm01a2dvNFJFVWFEc3NWaGlDUXpfenloQjFtVG14ekppaW5ITjNTZnUwZTk5XzZ3M3pJT1Q1VFUwUVVwVGVUSGNVZlZ0eHotUDVJdXEzMWE3ZXgzV2xLQnp4WGRVUFE?oc=5</t>
+        </is>
+      </c>
+      <c r="F109" t="n">
+        <v>7</v>
+      </c>
+      <c r="G109" s="1" t="n">
+        <v>46068.49857638889</v>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>Medusa</t>
+        </is>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>"Medusa ransomware" OR "Medusa threat actor" OR "Medusa cyber attack"</t>
+        </is>
+      </c>
+      <c r="C110" t="inlineStr">
+        <is>
+          <t>Popular AI program spoofed in phishing campaign spawning fake Microsoft Sharepoint logins - MSN</t>
+        </is>
+      </c>
+      <c r="D110" t="inlineStr">
+        <is>
+          <t>Sun, 15 Feb 2026 18:58:20 GMT</t>
+        </is>
+      </c>
+      <c r="E110" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMi8wJBVV95cUxQQ1I1eFNYcjZGMGpPazAwbWIyS0pSTVpZLU9HUFBhQkpGX1NGRmJFYTA3emh5VVIxQWc0TGsyZk9YejFORnpNMDhSa2F3VVFMZkJST3pQRTlGYVNlT1VNamxsTS01dTB0YkZEdDc2LTVrUm5UTTFhRmoyQkRWb3FjY01KUl92TnBtTzZfWmhRY2FyMVhtT25EYVRoSElxMHNjaW43S3lrSU9DWWFmMjF6cVRQRG9BTnJtam9EbG1HWU9Mbnc0QXlUemRZT2Nqa3VFVGVvYzd6Mjg3QnFCenBYc3VIR1lmUDhNU1ZTR1VDbWhYYm5fNFgzTHhDNmVoSWpONXZfb01CT2I0NFhlQjg4TFQyeVVkNFdyWmNGRThLN2gwcnM5YVJ5UkRSVGZIX1NGaDd4Q2tmOFY3WDhhZVhUVUN4dXdjOHZYMVFtamlHTm9BWmRmbl9GdGdHTVN5N0s1SnQ0WWRGY2FKWWU0eGtVdWFGWQ?oc=5</t>
+        </is>
+      </c>
+      <c r="F110" t="n">
+        <v>7</v>
+      </c>
+      <c r="G110" s="1" t="n">
+        <v>46068.79050925926</v>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>Medusa</t>
+        </is>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>"Medusa ransomware" OR "Medusa threat actor" OR "Medusa cyber attack"</t>
+        </is>
+      </c>
+      <c r="C111" t="inlineStr">
+        <is>
+          <t>UnitedHealth is now asking doctors to repay the loans it gave out following major hack - MSN</t>
+        </is>
+      </c>
+      <c r="D111" t="inlineStr">
+        <is>
+          <t>Tue, 17 Feb 2026 09:47:17 GMT</t>
+        </is>
+      </c>
+      <c r="E111" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMimANBVV95cUxPMzQ0VWtjVUV1dlU4a01SMW9qZzJJWVZjeU5hYnY5anhiVHlnMWVOY0tlNXRVUHpoMlQxdUZWMWN2d1MzUHRLZFItc2d3RkpRdjhrN1JNY2dseWFmUG1hdXZPaFdfcDRMR2RZV19Kc3VQOUkwRGJ0V1B2a1ZrNXRFZDRQZ3hieklzSXRWZkpvRjRxbmItSUg2UDA3QTRWXy1hTDdxZU9rWGxrYXpVcHF2MHVYU3owLWlmV1FwaE5pSlF5TG1UVGUteHhCd3QwZ3UzT0lpY3E1Uk1yLXdzMW9DWkd5X1lFa3RYR0E3NDlpSGZ5aEVvOXhmbEpfMnRIMXpjN2pEa2dnZjBLRGlaUnZiaHNabFFnWHFENU5XbmxSQ3IySEZkRlhaN2VQejVKdDE1NFEySjNVc0RpaDZzRGZLVG94MVJvZkw3UnF3eWQ0ZFQtMGdXWVp4VlRPMlZfdjdmbjAzbUxaOTBLZVpLVWtrYnpTTi0yaEk1RUc3b2dTQ3lScmJNWDJPLUxaNWRCZFRjM2lzR2hSNko?oc=5</t>
+        </is>
+      </c>
+      <c r="F111" t="n">
+        <v>7</v>
+      </c>
+      <c r="G111" s="1" t="n">
+        <v>46070.40783564815</v>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>Safepay</t>
+        </is>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>"Safepay ransomware" OR "Safepay threat actor" OR "Safepay cyber attack"</t>
+        </is>
+      </c>
+      <c r="C112" t="inlineStr">
+        <is>
+          <t>Conduent case breaks open after Volvo reports third-party compromise - SC Media</t>
+        </is>
+      </c>
+      <c r="D112" t="inlineStr">
+        <is>
+          <t>Wed, 11 Feb 2026 21:29:00 GMT</t>
+        </is>
+      </c>
+      <c r="E112" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMingFBVV95cUxQdk1RdV9pR0k0eUtNa2dWVG5FdjZTVjIzN0VZeXdiV21QZFE0TE1XWjBTemRiUC13TndIdWFPLW9SZ2t2OVEzWGlDZWd5TVhYQU9nYWpIbmlNcVhZTDR1dnMzZ3Q3aTNUcUlBbEI4SjF4QzJ2ZXBVQjk0WnlJRWpSMVJtSnFOcWtTdjZZUm5TUnduUk9VTGV4eFdldUlWZw?oc=5</t>
+        </is>
+      </c>
+      <c r="F112" t="n">
+        <v>7</v>
+      </c>
+      <c r="G112" s="1" t="n">
+        <v>46064.89513888889</v>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>Safepay</t>
+        </is>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>"Safepay ransomware" OR "Safepay threat actor" OR "Safepay cyber attack"</t>
+        </is>
+      </c>
+      <c r="C113" t="inlineStr">
+        <is>
+          <t>Automotive Giant Volvo Employee Information Exposed via Third-Party Conduent Data Breach - TechNadu</t>
+        </is>
+      </c>
+      <c r="D113" t="inlineStr">
+        <is>
+          <t>Wed, 11 Feb 2026 10:27:34 GMT</t>
+        </is>
+      </c>
+      <c r="E113" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMivgFBVV95cUxQc1VrdVVaNEJ4UjNBWmVRY3VHTmtMdGJ3QXlNdEVLdWJCUmlpWXp4RnZKLVZZVFhTZVB3NTFfY0VvWXpHQkxJamZhdGdZZlRhOHVvZTQ2WjJHUUluQjlZb2J1RS1YUUdLcmdwSmNuTGNOamdWUmhTUVQ0TF9obldUOTNmWHdQRlFKREFYdXVadi1ZX1pxeWVIVXVubnNsTlJra3BmckwyVkl3cTZwMkVDcm01Z09Sc1VwSGh3U3Jn?oc=5</t>
+        </is>
+      </c>
+      <c r="F113" t="n">
+        <v>7</v>
+      </c>
+      <c r="G113" s="1" t="n">
+        <v>46064.43581018518</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/latest_ransomware_news.xlsx
+++ b/data/latest_ransomware_news.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G113"/>
+  <dimension ref="A1:G117"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4153,6 +4153,138 @@
         <v>46064.43581018518</v>
       </c>
     </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>Dragonforce</t>
+        </is>
+      </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>"Dragonforce ransomware" OR "Dragonforce threat actor" OR "Dragonforce cyber attack"</t>
+        </is>
+      </c>
+      <c r="C114" t="inlineStr">
+        <is>
+          <t>DragonForce Ransomware Attack on Jac Vandenberg - DeXpose</t>
+        </is>
+      </c>
+      <c r="D114" t="inlineStr">
+        <is>
+          <t>Tue, 24 Feb 2026 00:00:00 GMT</t>
+        </is>
+      </c>
+      <c r="E114" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMie0FVX3lxTE1vS25QNDBGemFhbGVWU0U3eTVuNjB5YWRHMzBCWUZ1NDZxTlVRcnFCa212QnJHbF84YmxsUVJ4emVlMThOY2JHU2FQRkl6OF9GbnZ4azZTZlBMRllXNnBmelVLSWdlTHZIWmJaeTlwWEFzVXY0WkJjWUxWZw?oc=5</t>
+        </is>
+      </c>
+      <c r="F114" t="n">
+        <v>7</v>
+      </c>
+      <c r="G114" s="1" t="n">
+        <v>46077</v>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>Everest</t>
+        </is>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>"Everest ransomware" OR "Everest threat actor" OR "Everest cyber attack"</t>
+        </is>
+      </c>
+      <c r="C115" t="inlineStr">
+        <is>
+          <t>Operation MacroMaze: APT28 exploits webhooks for covert data exfiltration - Security Affairs</t>
+        </is>
+      </c>
+      <c r="D115" t="inlineStr">
+        <is>
+          <t>Tue, 24 Feb 2026 09:10:59 GMT</t>
+        </is>
+      </c>
+      <c r="E115" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMivAFBVV95cUxOY1Jmb2hQeU1iRzhSSDVfX0ZTcFVEejJtcElVa1QtVk01eTRxWW5oQ0FnTWtHUEs5VGVVeXFpd0p1SHY1d3haWUhGOFZRcjJiVWR5NHlhVkMzbUpBMC1zWmhrRjRRc2FBZ2l0bE1JYThqdUd4WWxLT054aDVCcy0xZFMzSWJaSE13RVRaRHl0LVFRbF92dXg0d0VBNmlXVHd2UVFfNWhXNmRHcl8xNzhwZTNpLVRlRGx0a2daZQ?oc=5</t>
+        </is>
+      </c>
+      <c r="F115" t="n">
+        <v>7</v>
+      </c>
+      <c r="G115" s="1" t="n">
+        <v>46077.38262731482</v>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>Everest</t>
+        </is>
+      </c>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>"Everest ransomware" OR "Everest threat actor" OR "Everest cyber attack"</t>
+        </is>
+      </c>
+      <c r="C116" t="inlineStr">
+        <is>
+          <t>Arkanix Stealer: AI-assisted info-stealer shuts down after brief campaign - Security Affairs</t>
+        </is>
+      </c>
+      <c r="D116" t="inlineStr">
+        <is>
+          <t>Tue, 24 Feb 2026 10:53:20 GMT</t>
+        </is>
+      </c>
+      <c r="E116" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiwgFBVV95cUxOVzMzVnJIc2lKQmp1aHdyTG9FT25XeGNlN1o2SGtUWU5LeGt1aGNVNEozUVk2SGRSQjVqTWU2YVJETW90b3Vpdm5WQXBIYmVCQXdtVURXWTlSWjZSSnhKeVZrQmE1VEp2Zm5GZTRENnR5MlIzaEh6N0N0eTRPeHRzLUNZVGt3TjVPdW90OGRxY2JHUDFKY2JrMk0xNlJjOWxXYzFGQTQtTFJEVUZEbHJMd2FSamNNUm42U1FSbHlCS0FfQQ?oc=5</t>
+        </is>
+      </c>
+      <c r="F116" t="n">
+        <v>7</v>
+      </c>
+      <c r="G116" s="1" t="n">
+        <v>46077.4537037037</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>Safepay</t>
+        </is>
+      </c>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>"Safepay ransomware" OR "Safepay threat actor" OR "Safepay cyber attack"</t>
+        </is>
+      </c>
+      <c r="C117" t="inlineStr">
+        <is>
+          <t>Microsoft Copilot Chat Error Exposes Confidential Emails to AI Tool - The Plunge Daily</t>
+        </is>
+      </c>
+      <c r="D117" t="inlineStr">
+        <is>
+          <t>Mon, 23 Feb 2026 12:36:56 GMT</t>
+        </is>
+      </c>
+      <c r="E117" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMingFBVV95cUxOVWtqakJHa1BUSjJ4ZkxMX0djZkplbU14cmhBVEctalpRYjZ6U3VHajJ1RjZVYmk2dHdLVWVtLXQzWGo5QU12ZHkzNThmUHhTZExkRlIxcU5iMVFtUFRUamFPcEhUdGp2MXJjTXliNWQwcHd1emdka1BMNEprY253a1g4VUFkRVJBakJVdUxmSmYzNGhjcmNaU3dTdFRMdw?oc=5</t>
+        </is>
+      </c>
+      <c r="F117" t="n">
+        <v>7</v>
+      </c>
+      <c r="G117" s="1" t="n">
+        <v>46076.52564814815</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/latest_ransomware_news.xlsx
+++ b/data/latest_ransomware_news.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G117"/>
+  <dimension ref="A1:G128"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4285,6 +4285,369 @@
         <v>46076.52564814815</v>
       </c>
     </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>Dragonforce</t>
+        </is>
+      </c>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>"Dragonforce ransomware" OR "Dragonforce threat actor" OR "Dragonforce cyber attack"</t>
+        </is>
+      </c>
+      <c r="C118" t="inlineStr">
+        <is>
+          <t>DragonForce Ransomware Attack on Aegis Project Controls - DeXpose</t>
+        </is>
+      </c>
+      <c r="D118" t="inlineStr">
+        <is>
+          <t>Sun, 01 Mar 2026 00:00:00 GMT</t>
+        </is>
+      </c>
+      <c r="E118" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMihgFBVV95cUxOUUR3N3lSYzVKNTIwZUZocWgtcnZVZEVmeDV3Z3ZUTlBZUjd4RHZMU0lNRmRyMWNsQmh2eUNDWVlIMzNEUUMtZ0dqb1RXQ045V2tHZUZOcnVwbEJMekw3Z1oxTC1LYnFURjlkNGd4eGZQRVZiZ1ZDYkFUbzlNTnFQeTl6ZXVadw?oc=5</t>
+        </is>
+      </c>
+      <c r="F118" t="n">
+        <v>7</v>
+      </c>
+      <c r="G118" s="1" t="n">
+        <v>46082</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>Qilin</t>
+        </is>
+      </c>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>"Qilin ransomware" OR "Qilin threat actor" OR "Qilin cyber attack"</t>
+        </is>
+      </c>
+      <c r="C119" t="inlineStr">
+        <is>
+          <t>USA Herald - USA Herald</t>
+        </is>
+      </c>
+      <c r="D119" t="inlineStr">
+        <is>
+          <t>Tue, 03 Mar 2026 11:01:54 GMT</t>
+        </is>
+      </c>
+      <c r="E119" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMisgFBVV95cUxOZGlfMF9xVWdCTXhxNGhhZk55b0QyLU1fTkZfT0VoOE5TX2Z3Yi1neC1URlk2R1JQR0ZKU2YyNUVrbFNvaWtmcmdMZ3A1OUhPbmRVdXNONFAyVm9CUHBqZ3RMT3I0OHJEY18wdEhfeDc3bFM3RTZNaDdJTDB2dGlOdzI1RUlkUVFCSExNU0JsRnllNGhSUi1HdTlwQXJ3Y0o1TzI0ZGZYVUktaFFaNW1uQnRR?oc=5</t>
+        </is>
+      </c>
+      <c r="F119" t="n">
+        <v>7</v>
+      </c>
+      <c r="G119" s="1" t="n">
+        <v>46084.45965277778</v>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>Akira</t>
+        </is>
+      </c>
+      <c r="B120" t="inlineStr">
+        <is>
+          <t>"Akira ransomware" OR "Akira threat actor" OR "Akira cyber attack"</t>
+        </is>
+      </c>
+      <c r="C120" t="inlineStr">
+        <is>
+          <t>The InterTech Group Data Breach Exposes Social Security Numberes - Claim Depot</t>
+        </is>
+      </c>
+      <c r="D120" t="inlineStr">
+        <is>
+          <t>Mon, 02 Mar 2026 22:25:50 GMT</t>
+        </is>
+      </c>
+      <c r="E120" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiY0FVX3lxTFByV29VSjQzTWNaVjVxcTBTT2lfRmpkcVk4Ykx2NU55aThsQUlicnhQWE5yUEZnOEVLdzl5UWprWVZqMU5TR0drbDJ5dWZjRzl1UVh1NTNtSmdpYkNXQkotOWFSSQ?oc=5</t>
+        </is>
+      </c>
+      <c r="F120" t="n">
+        <v>7</v>
+      </c>
+      <c r="G120" s="1" t="n">
+        <v>46083.93460648148</v>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>LockBit</t>
+        </is>
+      </c>
+      <c r="B121" t="inlineStr">
+        <is>
+          <t>"LockBit ransomware" OR "LockBit threat actor" OR "LockBit cyber attack"</t>
+        </is>
+      </c>
+      <c r="C121" t="inlineStr">
+        <is>
+          <t>Apache ActiveMQ Vulnerability Used To Deploy LockBit Ransomware via RDP Access - Cyber Press</t>
+        </is>
+      </c>
+      <c r="D121" t="inlineStr">
+        <is>
+          <t>Wed, 25 Feb 2026 12:05:44 GMT</t>
+        </is>
+      </c>
+      <c r="E121" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiZ0FVX3lxTE9VS1h4Sk4ycVhZM1RFdHE2U0VUSVc4dmJkYWhuU0k0TEdkb0RyYThROUFsRW9VdWVxSW5fY2VHRlUyZnloemRVa2hkT25yYS1jRmlSaHdpUmxQTjJxWU11Yzc5cUgyX1E?oc=5</t>
+        </is>
+      </c>
+      <c r="F121" t="n">
+        <v>7</v>
+      </c>
+      <c r="G121" s="1" t="n">
+        <v>46078.50398148148</v>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>Medusa</t>
+        </is>
+      </c>
+      <c r="B122" t="inlineStr">
+        <is>
+          <t>"Medusa ransomware" OR "Medusa threat actor" OR "Medusa cyber attack"</t>
+        </is>
+      </c>
+      <c r="C122" t="inlineStr">
+        <is>
+          <t>Security Affairs newsletter Round 565 by Pierluigi Paganini – INTERNATIONAL EDITION - Security Affairs</t>
+        </is>
+      </c>
+      <c r="D122" t="inlineStr">
+        <is>
+          <t>Sun, 01 Mar 2026 00:47:26 GMT</t>
+        </is>
+      </c>
+      <c r="E122" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiygFBVV95cUxNQ214OGh6enpFRnMtcUF0R1VpTmVqNnRLNHZoTGktN0tVVWtHU3RFN3EtMXZ1eFFTOE5nMlBYamFkQVVHZk5QQ2g1S0ZXU0dTbXpuRENpQlRGdGNfN2E2elo3ZjJXMHlPbFdPZDZSYzZHN2RLN2VFcmR2Mk13eWliUXhGbVFHQnJwYWtOYXRCM0pnQ2FqcGY2dktCSVljM2ZKZEpsbW10LTRKYm9lVjVQYWR5Uy14M3ZINjB6aHoyaWp0R05sUEdBM29R0gHPAUFVX3lxTE5Yb0ppNmQzeWxTZDl5TFUzTGRBWWhfdGhZMmtpZ0FfWGp2amp2TUJxbkw4OThwRWgyblZScW9LQ1dFdWcySzRWT2NxRTltTmlabDdzbDVzZWQySGgwX0tlRW11aUt3OUJzZExpX2JoOW1RUXI0dVNid2I0MkRRRTFiMmoxWUVtVk1jeTBrVUpCRTdEcUF6T2l1WDhENk5jbHQ1emhMdFBrT1BXN0hUUnp6V1lINTZRbDlsazZLb21WeHRGSFI4R1BpMGtLUWE5aw?oc=5</t>
+        </is>
+      </c>
+      <c r="F122" t="n">
+        <v>7</v>
+      </c>
+      <c r="G122" s="1" t="n">
+        <v>46082.03293981482</v>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>Cl0p</t>
+        </is>
+      </c>
+      <c r="B123" t="inlineStr">
+        <is>
+          <t>"Cl0p ransomware" OR "Cl0p threat actor" OR "Cl0p cyber attack"</t>
+        </is>
+      </c>
+      <c r="C123" t="inlineStr">
+        <is>
+          <t>Madison Square Garden Data Breach Confirmed Months After Hacker Attack - SecurityWeek</t>
+        </is>
+      </c>
+      <c r="D123" t="inlineStr">
+        <is>
+          <t>Mon, 02 Mar 2026 14:07:56 GMT</t>
+        </is>
+      </c>
+      <c r="E123" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMipwFBVV95cUxQeVJVOWZqNkxwMlRmTGZ5YkszTWNuWjY2SFVGUjJpTDNHT0sya3R4cGhEOWZNeUl6U2VFWHlWc2ZRbTZtV0U5Vy12dkhZY0ZxUDFYSXp3cUFXMEo2M1l0REVTTWlpMjJKNEc0c1ZNVlVvNnpVS0s2VHdOSUpYWXR4bHpveE1qRmNqYUo3Wng5dGVkY3E2anZDZjQzbUp2YU9naWlEQTNQWdIBpwFBVV95cUxQeVJVOWZqNkxwMlRmTGZ5YkszTWNuWjY2SFVGUjJpTDNHT0sya3R4cGhEOWZNeUl6U2VFWHlWc2ZRbTZtV0U5Vy12dkhZY0ZxUDFYSXp3cUFXMEo2M1l0REVTTWlpMjJKNEc0c1ZNVlVvNnpVS0s2VHdOSUpYWXR4bHpveE1qRmNqYUo3Wng5dGVkY3E2anZDZjQzbUp2YU9naWlEQTNQWQ?oc=5</t>
+        </is>
+      </c>
+      <c r="F123" t="n">
+        <v>7</v>
+      </c>
+      <c r="G123" s="1" t="n">
+        <v>46083.5888425926</v>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>Safepay</t>
+        </is>
+      </c>
+      <c r="B124" t="inlineStr">
+        <is>
+          <t>"Safepay ransomware" OR "Safepay threat actor" OR "Safepay cyber attack"</t>
+        </is>
+      </c>
+      <c r="C124" t="inlineStr">
+        <is>
+          <t>Weekly Intelligence Report – 27 February 2026 - cyfirma</t>
+        </is>
+      </c>
+      <c r="D124" t="inlineStr">
+        <is>
+          <t>Fri, 27 Feb 2026 01:57:05 GMT</t>
+        </is>
+      </c>
+      <c r="E124" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMifkFVX3lxTE05ZU5hcllzWGpvN2ZnOVJ5NVd6NXd4d2poemdCYkFoTFgxemQ2OS14eV9xMVJ3dUEtc3hEcGxsUHhucjFsQ1JreTh4MElKd2NsaWdRUHZadkowbzdJS2I0bHZWck5FY1BqTkJ0dHNyVDA4NjdzNzhnWHpkNzlXZw?oc=5</t>
+        </is>
+      </c>
+      <c r="F124" t="n">
+        <v>7</v>
+      </c>
+      <c r="G124" s="1" t="n">
+        <v>46080.08130787037</v>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>Safepay</t>
+        </is>
+      </c>
+      <c r="B125" t="inlineStr">
+        <is>
+          <t>"Safepay ransomware" OR "Safepay threat actor" OR "Safepay cyber attack"</t>
+        </is>
+      </c>
+      <c r="C125" t="inlineStr">
+        <is>
+          <t>Data Breach Expands To 25 Million People: Massive Third-Party Cyberattack Shakes Client Service Network - The420.in</t>
+        </is>
+      </c>
+      <c r="D125" t="inlineStr">
+        <is>
+          <t>Fri, 27 Feb 2026 09:41:17 GMT</t>
+        </is>
+      </c>
+      <c r="E125" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMieEFVX3lxTFBVWVZGdnhlcE0zQzVDbmhPaWV3YXFhVmtLQ3lmMnozX2xHclhldE5idFhsTlFmUTFDT0pLSnJzczhsdFZ4V2ttaVluQi1rcGcyWEpBa1FmVnE4VnByMnZNaks4czFvb3lOTnFJRVAyM0ZTYVFYU01Ebw?oc=5</t>
+        </is>
+      </c>
+      <c r="F125" t="n">
+        <v>7</v>
+      </c>
+      <c r="G125" s="1" t="n">
+        <v>46080.40366898148</v>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="inlineStr">
+        <is>
+          <t>Safepay</t>
+        </is>
+      </c>
+      <c r="B126" t="inlineStr">
+        <is>
+          <t>"Safepay ransomware" OR "Safepay threat actor" OR "Safepay cyber attack"</t>
+        </is>
+      </c>
+      <c r="C126" t="inlineStr">
+        <is>
+          <t>'Largest breach in US history' exposes records of 26 million Americans - MSN</t>
+        </is>
+      </c>
+      <c r="D126" t="inlineStr">
+        <is>
+          <t>Thu, 26 Feb 2026 03:39:18 GMT</t>
+        </is>
+      </c>
+      <c r="E126" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMigwNBVV95cUxOMWNpTnN3RXA3ckUtRThXUVZEdGxlV3pmYjNkUExEQnhqZU1Jak1meDZsd3pZVnU2SUt6cU1LdG5Xc25SWHVLSUtpSWd2a0ZITXU5Q3NGcU1oRmVxN3FYakVkVmZJaDNwX2d1QlJVeVQ4Vm9QV25sTXE1TXlMT1VVYVczUFI3R1lpQ0t4bDJ4VGI0QmxuOXRhdTVOOWhaZ3BHUFdXNnI1WVBydWhfYVpTS2dtSUlFVmM1VDFIdG5xNDBaVnhKS293U3ZsVTFrMTJ3ZnI5dUlYLXd0M00xdEtyY0tiNFVhbzg0Si1va2lpcVdOZnlILUMxZ0ZvaXdDZjh2Z2c0TTlpa2tOTGlaMEVBdzFEOFg2MWx0RjQzWU12MXdPZlBGVGl0N1hMMEV4OXVndjNJSGZjVWF4UFhPTDQxdm5ZNkVWZlFMdVJLQTY2a29Dei1EMTRMUlptN2ptY0JuRUFtYy1qRTBacW16Z0psX1NIamN5b3RYbkRXMWVlX2tXV0U?oc=5</t>
+        </is>
+      </c>
+      <c r="F126" t="n">
+        <v>7</v>
+      </c>
+      <c r="G126" s="1" t="n">
+        <v>46079.15229166667</v>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>Safepay</t>
+        </is>
+      </c>
+      <c r="B127" t="inlineStr">
+        <is>
+          <t>"Safepay ransomware" OR "Safepay threat actor" OR "Safepay cyber attack"</t>
+        </is>
+      </c>
+      <c r="C127" t="inlineStr">
+        <is>
+          <t>This Massive Healthcare Data Breach Is Even Bigger Than Previously Reported - Lifehacker</t>
+        </is>
+      </c>
+      <c r="D127" t="inlineStr">
+        <is>
+          <t>Thu, 26 Feb 2026 15:00:00 GMT</t>
+        </is>
+      </c>
+      <c r="E127" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMivgFBVV95cUxPdmhqdmZNUVR3azFaVm1kYUVkWU84Yl9XcGIydHdkaTJKdDJYZGFJeGFYS28ydjlnb0xCc2RFQ0c5OERUN1ZJN3ZXUWtNbzhkd3ZiZkZwYjdGNm5naDY3RTdfS1hLMEN4Uk81a043Uk5qcTc3aHBHQ1VGeHlqcFdsQ291Vk9KbWt2azNWWXQ4MUE3RzJCeU1YNjdqQmdFaTJ2YnA0NDFPeEo3b25tNzZMWHVRanRCMW5FSDFpSGp3?oc=5</t>
+        </is>
+      </c>
+      <c r="F127" t="n">
+        <v>7</v>
+      </c>
+      <c r="G127" s="1" t="n">
+        <v>46079.625</v>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="inlineStr">
+        <is>
+          <t>Safepay</t>
+        </is>
+      </c>
+      <c r="B128" t="inlineStr">
+        <is>
+          <t>"Safepay ransomware" OR "Safepay threat actor" OR "Safepay cyber attack"</t>
+        </is>
+      </c>
+      <c r="C128" t="inlineStr">
+        <is>
+          <t>CloudSEK Uncovers Fake “Red Alert” App Exploiting Conflict-Driven Panic - The Plunge Daily</t>
+        </is>
+      </c>
+      <c r="D128" t="inlineStr">
+        <is>
+          <t>Tue, 03 Mar 2026 13:14:28 GMT</t>
+        </is>
+      </c>
+      <c r="E128" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMirAFBVV95cUxONnBqb0pZTHJmS19qdUNNT1BVUDFhRWRfTGk4eF9MVHpicU5GM04zR0YyZkxaR2x5R1NheUpxbmRsWV9ZQndUVGtibEpHWHU1MTdUQ0dfZ3pxV25uNF9adWd3SzFYZUVtQzFHUW5hMWg5YV9lRzZObWExTms0NUFSTzBISEI1TmRGTk1hcVYzMS0waDZwd0FJajJFMWtKWEgybjdET2QyM0VJdzdE?oc=5</t>
+        </is>
+      </c>
+      <c r="F128" t="n">
+        <v>7</v>
+      </c>
+      <c r="G128" s="1" t="n">
+        <v>46084.55171296297</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/latest_ransomware_news.xlsx
+++ b/data/latest_ransomware_news.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G128"/>
+  <dimension ref="A1:G139"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4648,6 +4648,369 @@
         <v>46084.55171296297</v>
       </c>
     </row>
+    <row r="129">
+      <c r="A129" t="inlineStr">
+        <is>
+          <t>Dragonforce</t>
+        </is>
+      </c>
+      <c r="B129" t="inlineStr">
+        <is>
+          <t>"Dragonforce ransomware" OR "Dragonforce threat actor" OR "Dragonforce cyber attack"</t>
+        </is>
+      </c>
+      <c r="C129" t="inlineStr">
+        <is>
+          <t>Dragonforce Ransomware Attack on Salford City College - DeXpose</t>
+        </is>
+      </c>
+      <c r="D129" t="inlineStr">
+        <is>
+          <t>Fri, 06 Mar 2026 00:00:00 GMT</t>
+        </is>
+      </c>
+      <c r="E129" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMigwFBVV95cUxQZmVmUV90aV9TVm5acXNFbTZETEJEOEpVbmhpWE9xN0pLR3U4OXU1THA3VWZmQmg2Z1M3MEJDRUU2ZG5HV0ZrQW9ENzE2U0s3bmxPWFRtT09YSEVVb254NGZNYlBwS0ZSb3RxTHR1SnlCeWswNGlZMTI2eTZwRnh2UVY4VQ?oc=5</t>
+        </is>
+      </c>
+      <c r="F129" t="n">
+        <v>7</v>
+      </c>
+      <c r="G129" s="1" t="n">
+        <v>46087</v>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="inlineStr">
+        <is>
+          <t>Qilin</t>
+        </is>
+      </c>
+      <c r="B130" t="inlineStr">
+        <is>
+          <t>"Qilin ransomware" OR "Qilin threat actor" OR "Qilin cyber attack"</t>
+        </is>
+      </c>
+      <c r="C130" t="inlineStr">
+        <is>
+          <t>Qilin purports breach of US electric cooperative - SC Media</t>
+        </is>
+      </c>
+      <c r="D130" t="inlineStr">
+        <is>
+          <t>Tue, 10 Mar 2026 00:15:38 GMT</t>
+        </is>
+      </c>
+      <c r="E130" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMihAFBVV95cUxQQXZNMjVoT3RjclhOZUZ1eEFKYVdwOXpJWjdONW1JcHhWMWdIc3RMSUdzc1Q0YXJRU0djd0p3anItb0RzdVdyNHlqUklyb2VpdTI1VDdBMVAyZy1GY2FQTXp3Yi0xSkMtZzVHYVdPRTRfeVh4alVfR0NKRkIteHJjY3JUMEw?oc=5</t>
+        </is>
+      </c>
+      <c r="F130" t="n">
+        <v>7</v>
+      </c>
+      <c r="G130" s="1" t="n">
+        <v>46091.01085648148</v>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="inlineStr">
+        <is>
+          <t>Qilin</t>
+        </is>
+      </c>
+      <c r="B131" t="inlineStr">
+        <is>
+          <t>"Qilin ransomware" OR "Qilin threat actor" OR "Qilin cyber attack"</t>
+        </is>
+      </c>
+      <c r="C131" t="inlineStr">
+        <is>
+          <t>“US power provider attacked,” claim Russian cyber gang - Cybernews</t>
+        </is>
+      </c>
+      <c r="D131" t="inlineStr">
+        <is>
+          <t>Fri, 06 Mar 2026 15:15:15 GMT</t>
+        </is>
+      </c>
+      <c r="E131" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMieEFVX3lxTFB2djBTeTkzRFk5aEpuM193ajM0Ykg4aFpBN3dzS002ZW1hM3BXQkxiMkxXUjB1TmYxX2dRZ25IdExOUVJmNU1OV3hMcGlobmY4ZV9hMHg0X0pMN25rSXhmN2pmNjJBRDFHSnlqX1RJbDc3WURjWnRreg?oc=5</t>
+        </is>
+      </c>
+      <c r="F131" t="n">
+        <v>7</v>
+      </c>
+      <c r="G131" s="1" t="n">
+        <v>46087.63559027778</v>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="inlineStr">
+        <is>
+          <t>Warlock</t>
+        </is>
+      </c>
+      <c r="B132" t="inlineStr">
+        <is>
+          <t>"Warlock ransomware" OR "Warlock threat actor" OR "Warlock cyber attack"</t>
+        </is>
+      </c>
+      <c r="C132" t="inlineStr">
+        <is>
+          <t>Colt confirms customer data stolen as Warlock ransomware crew auctions off details - MSN</t>
+        </is>
+      </c>
+      <c r="D132" t="inlineStr">
+        <is>
+          <t>Mon, 09 Mar 2026 09:22:04 GMT</t>
+        </is>
+      </c>
+      <c r="E132" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMi6AJBVV95cUxNNzdWMTI0eTZkQ3R0cjlWTjB0QlRzWnVhWG5fWDc4Ung4NVREb01vVnVQX3M2TnBraHg4SWFMMzdQUWNGcXl5UWtXSGlfUlc4TnJ4cXY2aUljQVZYaVIwVTlmUkJsM2VReVpLWjZ0c3R4SDFTOEgyYjNQc0lWY2tiTzBwdHNseTVVY3hFaU1hY1dBV2NxR3ljTHBfNUtqdzFhTGswek9ka3V1OVVsUG9Cb0puRDF5a0lVQzRZSnFfak9Rbk9wVU5UNkdBZDBDTklsR2FXWHJpNFA2LUVNMnVCVG94QUZyeS1CRjNlZHVEYTVKY1hEXzhHOU9qRDJXQkhhRjBNQmJkUlFyMjlsYXNHWlRwaVFDRGlRNkxSbUt3TnlyUUlWNkhZSDhqQ1JYelhHX1dRWF9IR1RVT0lGeVdzNnU0djh4cE03U2p0MGdTM2RkSTRReUR3M3dhdkktTEdIdUtERV9Pak8?oc=5</t>
+        </is>
+      </c>
+      <c r="F132" t="n">
+        <v>7</v>
+      </c>
+      <c r="G132" s="1" t="n">
+        <v>46090.39032407408</v>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="inlineStr">
+        <is>
+          <t>LockBit</t>
+        </is>
+      </c>
+      <c r="B133" t="inlineStr">
+        <is>
+          <t>"LockBit ransomware" OR "LockBit threat actor" OR "LockBit cyber attack"</t>
+        </is>
+      </c>
+      <c r="C133" t="inlineStr">
+        <is>
+          <t>Stopping ransomware disruption with better planning - Healthcare IT News</t>
+        </is>
+      </c>
+      <c r="D133" t="inlineStr">
+        <is>
+          <t>Mon, 09 Mar 2026 17:50:00 GMT</t>
+        </is>
+      </c>
+      <c r="E133" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMijAFBVV95cUxNVXoxdEpvcGE1d0FmRkgwVzVIcFdMdWRsNTN0VWtMY2RJdjdmT2xfcmplQ2Zna2llaWhzNmZ2RDRGaTB6VGF3WTNneVhnUFdCM2pQcHA0SjlTMXBBU1lWTDlRc1BxMTgzdDBlUWREbzBkZnAyRFd5WG1fU1lWeGpBWk81X1BqeDFReVE5bg?oc=5</t>
+        </is>
+      </c>
+      <c r="F133" t="n">
+        <v>7</v>
+      </c>
+      <c r="G133" s="1" t="n">
+        <v>46090.74305555555</v>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="inlineStr">
+        <is>
+          <t>LockBit</t>
+        </is>
+      </c>
+      <c r="B134" t="inlineStr">
+        <is>
+          <t>"LockBit ransomware" OR "LockBit threat actor" OR "LockBit cyber attack"</t>
+        </is>
+      </c>
+      <c r="C134" t="inlineStr">
+        <is>
+          <t>Europol, FBI wipe major cybercrime forum LeakBase off the web - TradingView</t>
+        </is>
+      </c>
+      <c r="D134" t="inlineStr">
+        <is>
+          <t>Thu, 05 Mar 2026 04:21:00 GMT</t>
+        </is>
+      </c>
+      <c r="E134" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiwgFBVV95cUxNUUlqQXlUaThpUTRpdS00Z1M2SnVDa252WnFhcEFXdTlVUDQwczRUQ1FpazZXX0JyM1FaU191cTlUNFJLSkNhTzB4LThlS3F0OHVkN2ZDZWRjcUFkcVFKZ3prbnBDZ1dsZ1p5OGFERXVFOFlwUWtSUGRZR0ktY1Fydk9EVWkyUVBralJvQ3RFTFJVTnBFWGsyYmhpdzVmd1lFSzJfUVkxajV6SkFldGRUdlBuajZFVW4xNVd4X29IcmZhUQ?oc=5</t>
+        </is>
+      </c>
+      <c r="F134" t="n">
+        <v>7</v>
+      </c>
+      <c r="G134" s="1" t="n">
+        <v>46086.18125</v>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="inlineStr">
+        <is>
+          <t>Play</t>
+        </is>
+      </c>
+      <c r="B135" t="inlineStr">
+        <is>
+          <t>"Play ransomware" OR "Play threat actor" OR "Play cyber attack"</t>
+        </is>
+      </c>
+      <c r="C135" t="inlineStr">
+        <is>
+          <t>Play Ransomware Destroys EDR/EPP via Disk Manager - Seizes Network Firewalls - Halcyon</t>
+        </is>
+      </c>
+      <c r="D135" t="inlineStr">
+        <is>
+          <t>Tue, 10 Mar 2026 10:02:00 GMT</t>
+        </is>
+      </c>
+      <c r="E135" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiwwFBVV95cUxOb2ZxRzRUbVgyOGVvOUs1QXVWNzl6YmJGRGFUZ3hOSmNtOE9rQm0tWUVsX2tlQktjYVFJUDdUZXN5UTJOZWpJcml0alA0YUwtNUVNWmdXbUNWQzlWU3BHZUlQRjVxdDB5U2N1Y0dFSkl5UjFUOWxpV0h2OUNSMEVrNFB5LWdka3A4YUFQWFVEdTd1ZEVEdHdHMDZLcW5BNDExMEg1T2d3VkNCUmcxV2ZkTEpnVlh2bjlYQUhFLWZqdkZGWXM?oc=5</t>
+        </is>
+      </c>
+      <c r="F135" t="n">
+        <v>7</v>
+      </c>
+      <c r="G135" s="1" t="n">
+        <v>46091.41805555556</v>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="inlineStr">
+        <is>
+          <t>Play</t>
+        </is>
+      </c>
+      <c r="B136" t="inlineStr">
+        <is>
+          <t>"Play ransomware" OR "Play threat actor" OR "Play cyber attack"</t>
+        </is>
+      </c>
+      <c r="C136" t="inlineStr">
+        <is>
+          <t>Nicole Kidman and Hilary Clinton's luxury hat brand hit by hackers - Cybernews</t>
+        </is>
+      </c>
+      <c r="D136" t="inlineStr">
+        <is>
+          <t>Mon, 09 Mar 2026 15:45:40 GMT</t>
+        </is>
+      </c>
+      <c r="E136" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiggFBVV95cUxNclpEQmFnWmJYdWZvMkRWTmNpRk0wZktyOTNXR2tNdDBQUTRvV1hmZkdPQ19Sdnc5SkpndDVoZF85WXV4M0xHVjVZSHJKSkRGWElVeF9qZ2ZLZWhJYUpFb2xpV3ZyTnlfUGpoU0lMWlNiV2lXVWFXX2hEeHBOWk9VVVVB?oc=5</t>
+        </is>
+      </c>
+      <c r="F136" t="n">
+        <v>7</v>
+      </c>
+      <c r="G136" s="1" t="n">
+        <v>46090.65671296296</v>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="inlineStr">
+        <is>
+          <t>Play</t>
+        </is>
+      </c>
+      <c r="B137" t="inlineStr">
+        <is>
+          <t>"Play ransomware" OR "Play threat actor" OR "Play cyber attack"</t>
+        </is>
+      </c>
+      <c r="C137" t="inlineStr">
+        <is>
+          <t>Tyree Oil Data Breach Exposes PHI and PII: SSN, Financial Details, and More Exposed - Claim Depot</t>
+        </is>
+      </c>
+      <c r="D137" t="inlineStr">
+        <is>
+          <t>Tue, 10 Mar 2026 20:36:17 GMT</t>
+        </is>
+      </c>
+      <c r="E137" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiY0FVX3lxTE40aVJxSFBrVHQ4TTB5ZmEwaG5jbVRtaDZoaVVlbjFTUTM3WWNQSzE4V2ItOUs1TWRvckhTbWhZZktOajItbVNDRl9lNU9leS1sclhmaWdTLVBJLUFadnBKa042cw?oc=5</t>
+        </is>
+      </c>
+      <c r="F137" t="n">
+        <v>7</v>
+      </c>
+      <c r="G137" s="1" t="n">
+        <v>46091.85853009259</v>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="inlineStr">
+        <is>
+          <t>Safepay</t>
+        </is>
+      </c>
+      <c r="B138" t="inlineStr">
+        <is>
+          <t>"Safepay ransomware" OR "Safepay threat actor" OR "Safepay cyber attack"</t>
+        </is>
+      </c>
+      <c r="C138" t="inlineStr">
+        <is>
+          <t>Exclusive: SafePay ransomware claims hack of Smile Team Orthodontics - Cyber Daily</t>
+        </is>
+      </c>
+      <c r="D138" t="inlineStr">
+        <is>
+          <t>Tue, 10 Mar 2026 00:44:14 GMT</t>
+        </is>
+      </c>
+      <c r="E138" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMirAFBVV95cUxPQ19veFZEcDc3QUdaN3l6SmJBbU9ZUGhTZjBFeW56cnJXWFBybkJSWFdRckVWS24tTTVEaUlPcENHNjB4M3U3M3FwZUFmUXJfUUhGYVNPa2VUWk92YjMzZF95NUxSc2w2MXF5UjBaRGUxUVRGendvQnpyR1kzM2xpQjVKZktpMXZOVFZzR2YwSWQ5NUZ4YnRUeTZud3lJTWc5c3VLd3R0Y2gxbnJL?oc=5</t>
+        </is>
+      </c>
+      <c r="F138" t="n">
+        <v>7</v>
+      </c>
+      <c r="G138" s="1" t="n">
+        <v>46091.03071759259</v>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="inlineStr">
+        <is>
+          <t>Safepay</t>
+        </is>
+      </c>
+      <c r="B139" t="inlineStr">
+        <is>
+          <t>"Safepay ransomware" OR "Safepay threat actor" OR "Safepay cyber attack"</t>
+        </is>
+      </c>
+      <c r="C139" t="inlineStr">
+        <is>
+          <t>'Largest breach in US history' exposes records of 26 million Americans - MSN</t>
+        </is>
+      </c>
+      <c r="D139" t="inlineStr">
+        <is>
+          <t>Tue, 10 Mar 2026 03:16:57 GMT</t>
+        </is>
+      </c>
+      <c r="E139" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMizgJBVV95cUxNYTRHMzFvalBsSVp5MEoxR21QX2gyUzFOaG1wVHBCeGplS3l2RVNROTFYR0hzSWp0X01MSlZMZVBCYzJfZWxkalk2bG5YOWhFYnNOel91bTV2YkdybUpnQl9NcXRHMF81bncxa01PSEVidWNZdFBYcXdWM3NfczVMdkpJQkhHQk1Lam5LSnV1X1VUY2hGcUY2R1hpYTN0aHJxQnlsMnROY0NCNFBhQ21YRi1kcjA4dW1LdjhFSFV2dm9DR3UyLTc2Qnh2MVBuSEZmNEZwT3RVbEg3X3NOMl9MWTVHSXBJVTYzdW1aZi1KcVdwSlh5enFaT1ctd1hIRWtrbmJ6V0ltcDB1U3hWakZYbkZHTzJQMjNKdWZlR0dFOElpa1c5QUthZFUwc2lQWjV5NVIwbXNQRmFMUFZxTjdXQ0hnZjd0MmJONURuNnhn?oc=5</t>
+        </is>
+      </c>
+      <c r="F139" t="n">
+        <v>7</v>
+      </c>
+      <c r="G139" s="1" t="n">
+        <v>46091.13677083333</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/latest_ransomware_news.xlsx
+++ b/data/latest_ransomware_news.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G139"/>
+  <dimension ref="A1:G146"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5011,6 +5011,237 @@
         <v>46091.13677083333</v>
       </c>
     </row>
+    <row r="140">
+      <c r="A140" t="inlineStr">
+        <is>
+          <t>Qilin</t>
+        </is>
+      </c>
+      <c r="B140" t="inlineStr">
+        <is>
+          <t>"Qilin ransomware" OR "Qilin threat actor" OR "Qilin cyber attack"</t>
+        </is>
+      </c>
+      <c r="C140" t="inlineStr">
+        <is>
+          <t>Qilin Ransomware Targets Australian Electronics Firm Fortress Systems - DeXpose</t>
+        </is>
+      </c>
+      <c r="D140" t="inlineStr">
+        <is>
+          <t>Wed, 11 Mar 2026 07:00:00 GMT</t>
+        </is>
+      </c>
+      <c r="E140" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMimAFBVV95cUxQUDlsdUlsXzlXUVpZSFhxcGd3UC1FaTJBQ2RMSGZlQ3FpUUFoc2xxWEFJVUpRSzJTeEtkT3lDTlM0OG0yWDliRWlfR1E0UkR5dHpEMXRoWjVfY1RCaXZibTMtaFlMSlNOUnh4THpvSy1xZzNsQzNLUGtDUFBRZC1KNDlOYjJYc3dBbTdicGE4VlUzM3VNbzMyQw?oc=5</t>
+        </is>
+      </c>
+      <c r="F140" t="n">
+        <v>7</v>
+      </c>
+      <c r="G140" s="1" t="n">
+        <v>46092.29166666666</v>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="inlineStr">
+        <is>
+          <t>Qilin</t>
+        </is>
+      </c>
+      <c r="B141" t="inlineStr">
+        <is>
+          <t>"Qilin ransomware" OR "Qilin threat actor" OR "Qilin cyber attack"</t>
+        </is>
+      </c>
+      <c r="C141" t="inlineStr">
+        <is>
+          <t>Cedar Valley Services Data Breach Exposes Sensitive Patient Info - Claim Depot</t>
+        </is>
+      </c>
+      <c r="D141" t="inlineStr">
+        <is>
+          <t>Wed, 11 Mar 2026 18:21:57 GMT</t>
+        </is>
+      </c>
+      <c r="E141" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMic0FVX3lxTE40U3FvVUxVc0JOMmo1anphTDhNZ1lFOUZKTjhFNmlNY3I4OWlscUFVazZsV0JVdVdWM2RqNWxwSVV1b2MyQl9ybDh2TmQ1WHJMMW1lTmNVb1JrQXdZX0o2MVdkMzZKaDJET0dCb1V1NXJ5TUU?oc=5</t>
+        </is>
+      </c>
+      <c r="F141" t="n">
+        <v>7</v>
+      </c>
+      <c r="G141" s="1" t="n">
+        <v>46092.76524305555</v>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="inlineStr">
+        <is>
+          <t>Lynx</t>
+        </is>
+      </c>
+      <c r="B142" t="inlineStr">
+        <is>
+          <t>"Lynx ransomware" OR "Lynx threat actor" OR "Lynx cyber attack"</t>
+        </is>
+      </c>
+      <c r="C142" t="inlineStr">
+        <is>
+          <t>Lynx Ransomware Targets Lion of Africa Insurance - DeXpose</t>
+        </is>
+      </c>
+      <c r="D142" t="inlineStr">
+        <is>
+          <t>Fri, 13 Mar 2026 00:00:00 GMT</t>
+        </is>
+      </c>
+      <c r="E142" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMifEFVX3lxTE83cU9UZ1NvckdnSjh5U0JFX1lKczQzQzJ2ZlBLZkRBeXhkSGZpU2hwWTBtamdQSDJvMExVNEZONS1PY192Rms5WVk3ODB4VTRUcUVPdjN3S0NCRHdVYVk1cjlsaThZWm91LUtRQXpqdVZkQ2JaWmZpeHlLV18?oc=5</t>
+        </is>
+      </c>
+      <c r="F142" t="n">
+        <v>7</v>
+      </c>
+      <c r="G142" s="1" t="n">
+        <v>46094</v>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="inlineStr">
+        <is>
+          <t>Medusa</t>
+        </is>
+      </c>
+      <c r="B143" t="inlineStr">
+        <is>
+          <t>"Medusa ransomware" OR "Medusa threat actor" OR "Medusa cyber attack"</t>
+        </is>
+      </c>
+      <c r="C143" t="inlineStr">
+        <is>
+          <t>Medusa ransomware gang claims attacks on prominent Mississippi hospital, New Jersey county - The Record from Recorded Future News</t>
+        </is>
+      </c>
+      <c r="D143" t="inlineStr">
+        <is>
+          <t>Tue, 17 Mar 2026 19:57:25 GMT</t>
+        </is>
+      </c>
+      <c r="E143" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMia0FVX3lxTFBscjNfejhacTh4dE50MFRQcFpkNG96R21IakJFTEZrbG43RG50dHI5RkExNWV0UmV4U2E3TTBGNnVtVTVjdkloR1BFVkRiMWtONHBudkd6d3dkUTNUeVplVHVnaU9PSlJCM2VJ?oc=5</t>
+        </is>
+      </c>
+      <c r="F143" t="n">
+        <v>7</v>
+      </c>
+      <c r="G143" s="1" t="n">
+        <v>46098.83153935185</v>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="inlineStr">
+        <is>
+          <t>Cl0p</t>
+        </is>
+      </c>
+      <c r="B144" t="inlineStr">
+        <is>
+          <t>"Cl0p ransomware" OR "Cl0p threat actor" OR "Cl0p cyber attack"</t>
+        </is>
+      </c>
+      <c r="C144" t="inlineStr">
+        <is>
+          <t>Oracle EBS Hack: Only 4 Corporate Giants Still Silent on Potential Impact - SecurityWeek</t>
+        </is>
+      </c>
+      <c r="D144" t="inlineStr">
+        <is>
+          <t>Sun, 15 Mar 2026 11:44:51 GMT</t>
+        </is>
+      </c>
+      <c r="E144" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiqgFBVV95cUxNb3lIOVczcGZVblNTWkJ2b2RSbHZPMXZEaTNtNUFWR2w0YUR5QVFOMFlNcHpsUFhtbDM5SEhrdnN4cG81b3BkRjdLSWNUVGJVMU5xZTNBbk9FMk9qNXJRR1pWWWRmeVR5R3kwZHhnNjVQV2x6YUZabFVsVmVxN2sxLWprVDdmY0g4UGVjdWFXcUtfaG1MRHR4LTNlbFE1TVhQel8yYmJuQXE2d9IBqgFBVV95cUxNb3lIOVczcGZVblNTWkJ2b2RSbHZPMXZEaTNtNUFWR2w0YUR5QVFOMFlNcHpsUFhtbDM5SEhrdnN4cG81b3BkRjdLSWNUVGJVMU5xZTNBbk9FMk9qNXJRR1pWWWRmeVR5R3kwZHhnNjVQV2x6YUZabFVsVmVxN2sxLWprVDdmY0g4UGVjdWFXcUtfaG1MRHR4LTNlbFE1TVhQel8yYmJuQXE2dw?oc=5</t>
+        </is>
+      </c>
+      <c r="F144" t="n">
+        <v>7</v>
+      </c>
+      <c r="G144" s="1" t="n">
+        <v>46096.48947916667</v>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="inlineStr">
+        <is>
+          <t>Interlock</t>
+        </is>
+      </c>
+      <c r="B145" t="inlineStr">
+        <is>
+          <t>"Interlock ransomware" OR "Interlock threat actor" OR "Interlock cyber attack"</t>
+        </is>
+      </c>
+      <c r="C145" t="inlineStr">
+        <is>
+          <t>Dozens of Lawsuits Filed in Response to Kettering Health Ransomware Attack - The HIPAA Journal</t>
+        </is>
+      </c>
+      <c r="D145" t="inlineStr">
+        <is>
+          <t>Wed, 11 Mar 2026 07:00:00 GMT</t>
+        </is>
+      </c>
+      <c r="E145" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMickFVX3lxTE96YUxlZzNDWURueG1OcEN5QW9DSGlyel9KeDdfblNxNkg1akQ5OTRvd3Y4OGFYd1lLbG94Y3FjZ1pta21mQzJUV1dYUHVDYzkwR1dTTDZHYVk3ZkxtU0YtdGc0MDNDMmREdS1yRTJUZERldw?oc=5</t>
+        </is>
+      </c>
+      <c r="F145" t="n">
+        <v>7</v>
+      </c>
+      <c r="G145" s="1" t="n">
+        <v>46092.29166666666</v>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="inlineStr">
+        <is>
+          <t>Safepay</t>
+        </is>
+      </c>
+      <c r="B146" t="inlineStr">
+        <is>
+          <t>"Safepay ransomware" OR "Safepay threat actor" OR "Safepay cyber attack"</t>
+        </is>
+      </c>
+      <c r="C146" t="inlineStr">
+        <is>
+          <t>'Largest breach in US history' exposes records of 26 million Americans - MSN</t>
+        </is>
+      </c>
+      <c r="D146" t="inlineStr">
+        <is>
+          <t>Sun, 15 Mar 2026 10:41:04 GMT</t>
+        </is>
+      </c>
+      <c r="E146" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMipwNBVV95cUxNMFVaamNHb3lKUVVmZHd2SFYyaUtHZ3NPSm0ycVJnZ1BhUmhwd2lpT0ZQYzhsazY0WnhHMjl1ZzI4bTRYVlhNYXB6aFJXenhWX1lRcUpDUHl0bkdQUVFrSHVpV1FScnVQYktoNm5YVkhHdzFma052U0Q3UVp1MFUxbERoNmVKTE1ZRnVFQUlTaTVYdDVzLVdoQ0ZMYlBnaHNzNy1kOXNha3RYVUMzRHNYXzN2ZzA3TmdScjdEaWNjNDhmU3U1T1YtZzVFYkdtNzRNSnp0OUZSTVZSMm5GaTZTWDNyT3pIWmhWMHo2OEZodUNWTDh4N3g3M1c4NjRwY1BuQkQwaTVKUDRkS29CNWUyT09zWWp5X1hWRGNCdVhjZG44Ynk0NkdxX2pZdW5lM0ppZ3Y1RUxjbEpBUGlzY0p1aVlrU0Z4MFlaVks4NENKVWlVcy1WaVVhSjY2b3hZbVMtSlQ5UTZuNzVfN2JNUzBDOEdvRmZManA1dFNweC1FNVZ2aFVUU1ROeTJzUnFXRkx3OG5ycFVNN0xmZmlSQnJUUXZkR3lRNVU?oc=5</t>
+        </is>
+      </c>
+      <c r="F146" t="n">
+        <v>7</v>
+      </c>
+      <c r="G146" s="1" t="n">
+        <v>46096.44518518518</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/latest_ransomware_news.xlsx
+++ b/data/latest_ransomware_news.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G146"/>
+  <dimension ref="A1:G154"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5242,6 +5242,270 @@
         <v>46096.44518518518</v>
       </c>
     </row>
+    <row r="147">
+      <c r="A147" t="inlineStr">
+        <is>
+          <t>Qilin</t>
+        </is>
+      </c>
+      <c r="B147" t="inlineStr">
+        <is>
+          <t>"Qilin ransomware" OR "Qilin threat actor" OR "Qilin cyber attack"</t>
+        </is>
+      </c>
+      <c r="C147" t="inlineStr">
+        <is>
+          <t>Qilin ransomware attack Accolend - DeXpose</t>
+        </is>
+      </c>
+      <c r="D147" t="inlineStr">
+        <is>
+          <t>Fri, 20 Mar 2026 00:00:00 GMT</t>
+        </is>
+      </c>
+      <c r="E147" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiZ0FVX3lxTE1TNlZUc0pWWWNyV1I5UDVfSzlQS1RqLTNqX3l3MndZMy1JOEpGWklsS3hoMzRVU211MzZfY2t4U3hYb1hzLTBEdzhBcFoyR0ZTZWtQbU9SV1RNY3pIamJseVh6LVVqWXc?oc=5</t>
+        </is>
+      </c>
+      <c r="F147" t="n">
+        <v>7</v>
+      </c>
+      <c r="G147" s="1" t="n">
+        <v>46101</v>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="inlineStr">
+        <is>
+          <t>Qilin</t>
+        </is>
+      </c>
+      <c r="B148" t="inlineStr">
+        <is>
+          <t>"Qilin ransomware" OR "Qilin threat actor" OR "Qilin cyber attack"</t>
+        </is>
+      </c>
+      <c r="C148" t="inlineStr">
+        <is>
+          <t>BMG Data Breach Lawsuit Investigation - Claim Depot</t>
+        </is>
+      </c>
+      <c r="D148" t="inlineStr">
+        <is>
+          <t>Tue, 24 Mar 2026 18:36:15 GMT</t>
+        </is>
+      </c>
+      <c r="E148" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMib0FVX3lxTE0xb1RIaEFlSk1kVlVSVkpiRW5QRjdUVTdtd19vcDJNR3F6NDQxb25lczJYM1ZTZTBQZ3M4bU55bzhpX291V1B4UXJXOVlhaHZDVGcxWC1YTFF0aWZ5bXRQektwRVFNVUxqTmwyb2Z4OA?oc=5</t>
+        </is>
+      </c>
+      <c r="F148" t="n">
+        <v>7</v>
+      </c>
+      <c r="G148" s="1" t="n">
+        <v>46105.77517361111</v>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" t="inlineStr">
+        <is>
+          <t>Akira</t>
+        </is>
+      </c>
+      <c r="B149" t="inlineStr">
+        <is>
+          <t>"Akira ransomware" OR "Akira threat actor" OR "Akira cyber attack"</t>
+        </is>
+      </c>
+      <c r="C149" t="inlineStr">
+        <is>
+          <t>ITPartners+ - Kaseya</t>
+        </is>
+      </c>
+      <c r="D149" t="inlineStr">
+        <is>
+          <t>Thu, 19 Mar 2026 20:35:16 GMT</t>
+        </is>
+      </c>
+      <c r="E149" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiW0FVX3lxTE9GN2J4Qk4zZVk3UUJRc3hzMXlUUU9BV1QzdEFQYWJsMVNPYVJ1NjEweWZNOXVFdHZNMHdMYWtET3Q4Yi1pc3ZKZVE2aTR1ZXdVWjlBMk5RVVdDZFU?oc=5</t>
+        </is>
+      </c>
+      <c r="F149" t="n">
+        <v>7</v>
+      </c>
+      <c r="G149" s="1" t="n">
+        <v>46100.85782407408</v>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" t="inlineStr">
+        <is>
+          <t>Everest</t>
+        </is>
+      </c>
+      <c r="B150" t="inlineStr">
+        <is>
+          <t>"Everest ransomware" OR "Everest threat actor" OR "Everest cyber attack"</t>
+        </is>
+      </c>
+      <c r="C150" t="inlineStr">
+        <is>
+          <t>Under Armour data breach: Names, emails, DOB and other details of 7,20,00,000 customers leaked online - MSN</t>
+        </is>
+      </c>
+      <c r="D150" t="inlineStr">
+        <is>
+          <t>Sat, 21 Mar 2026 15:45:13 GMT</t>
+        </is>
+      </c>
+      <c r="E150" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMi9AFBVV95cUxQNEp2NTFiVG9VVzd3eTM3ZTRUMkoxSnhieTllcU5pblFlWWtYRlc2aTYwRDhZNTlxYlVRMHJYNGNEOUVZcXFiS1pUdXNMTXRIb1lsaTlBZjlOT2NIN045MU1hSkZmR1NLUlFaYVFVa1pZUnZLbVBDSzdkZnBPSGF2eG02VHVNcnRwU1QzSFpBWkpjZl8yUFpvRF9XcUtLOWZMaUZMWkQ0VHdjWms4OFV5STYzZVFZUXR4d1NhOUZlYkRGOV85T2x5eU9XcTJwRzctek5aVFc0TTA2a2pzaTVVVnFTeXFVVjNDdDRzMi1ieEo2RTk3?oc=5</t>
+        </is>
+      </c>
+      <c r="F150" t="n">
+        <v>7</v>
+      </c>
+      <c r="G150" s="1" t="n">
+        <v>46102.65640046296</v>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" t="inlineStr">
+        <is>
+          <t>LockBit</t>
+        </is>
+      </c>
+      <c r="B151" t="inlineStr">
+        <is>
+          <t>"LockBit ransomware" OR "LockBit threat actor" OR "LockBit cyber attack"</t>
+        </is>
+      </c>
+      <c r="C151" t="inlineStr">
+        <is>
+          <t>Accenture and Microsoft Forge Cybersecurity Alliance: Strategic Revenue Move in Response to Persistent Zero-Day Threats - Bitget</t>
+        </is>
+      </c>
+      <c r="D151" t="inlineStr">
+        <is>
+          <t>Thu, 19 Mar 2026 04:03:51 GMT</t>
+        </is>
+      </c>
+      <c r="E151" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiXkFVX3lxTFByY0g4SU1BUkRVV3hsQ0s5R3JwTlIwY18ydXVrcjdFYnp6eU9nSllVeTR1T0tRUHNHUFE2a0FsTWJ2RmhabWppb016VHhUWWxpZ0lvNHBwX2lwSFpURkHSAWNBVV95cUxNWmU4ckhoc2JmRnZkM3l0dG56M1ZQc1E3QmN0MXV2ZjQ0Xy15c0hpbzBTYnB5Y29BVGZpN0xrVWo4aFBWN01fT1V5ZVhJVEFpc2Z1T3YzLWhteTRLLVVSVEFkUDA?oc=5</t>
+        </is>
+      </c>
+      <c r="F151" t="n">
+        <v>7</v>
+      </c>
+      <c r="G151" s="1" t="n">
+        <v>46100.16934027777</v>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" t="inlineStr">
+        <is>
+          <t>Medusa</t>
+        </is>
+      </c>
+      <c r="B152" t="inlineStr">
+        <is>
+          <t>"Medusa ransomware" OR "Medusa threat actor" OR "Medusa cyber attack"</t>
+        </is>
+      </c>
+      <c r="C152" t="inlineStr">
+        <is>
+          <t>Medusa ransomware purportedly hits University of Mississippi Medical Center, New Jersey county - SC Media</t>
+        </is>
+      </c>
+      <c r="D152" t="inlineStr">
+        <is>
+          <t>Wed, 18 Mar 2026 23:45:19 GMT</t>
+        </is>
+      </c>
+      <c r="E152" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiwAFBVV95cUxOY0ItODBlZXRYbHZoRDFGaHNRNElrX1c0ajZpcU9YbEl4YVNFNjVlVURCdXowZnpWMjNnRWNkcEpBUkljSHM1MDB5Z19VaFBNSDhyMUFBUjdvVWlrV2ozRDZ1RzFqOXJ2QjYzZFpmNjFoNDJnTkxpT0dXbjdta0x2X3Z5NDcwWUlTRUN4VkJwbXlXRjJxR0pxUS1pMG5ReHFIZFVQUzZkV2xfWHU1MllubkRndVFSLVJZX1FfMmtsRDU?oc=5</t>
+        </is>
+      </c>
+      <c r="F152" t="n">
+        <v>7</v>
+      </c>
+      <c r="G152" s="1" t="n">
+        <v>46099.98980324074</v>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" t="inlineStr">
+        <is>
+          <t>Cl0p</t>
+        </is>
+      </c>
+      <c r="B153" t="inlineStr">
+        <is>
+          <t>"Cl0p ransomware" OR "Cl0p threat actor" OR "Cl0p cyber attack"</t>
+        </is>
+      </c>
+      <c r="C153" t="inlineStr">
+        <is>
+          <t>Billion-Dollar Bank Handing $2,400,000 To Customers and Attorneys In Settlement Over Data Breach That Impacted 204,291 People - dailyhodl.com</t>
+        </is>
+      </c>
+      <c r="D153" t="inlineStr">
+        <is>
+          <t>Sun, 22 Mar 2026 17:12:36 GMT</t>
+        </is>
+      </c>
+      <c r="E153" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiRkFVX3lxTE1fd1hEUmpDejlwanJHaHJFSnNTcWFFcE5xSTV2b0RJM3Z2azNHQ2lPeUY2cVlwU0tLREFRNFNyQ2JiQTBseUHSAfABQVVfeXFMTzBEWHJOak5haGRXSjNmdzdtNEtIdFlhYWc1U2djZmFvc0RKcXUyWXoxNi1hUzRnV3d4Z1AwdmtfdG1IeDFadXJXTXZWTDVPZ0dscFcyb1d3bzAwOXF4WWtkQmZ6emZ0RnF6RG11c25XYkdBYk1Ebkw0c1p4ZS1SdG55aTdTUDNZSGJiME1HTVBib3MwYW9WTXJrRnlUSVBHZ3NrQ1FEcVZKdEo4UnRSSG4wZ3pmN3BRSWpkRU5WRjhXeEYxa2JGX0hNSUpPWHZVYjBNNzFWdlBUc0UtbS1FVktJc2ZORkliaWJld0RpT20x?oc=5</t>
+        </is>
+      </c>
+      <c r="F153" t="n">
+        <v>7</v>
+      </c>
+      <c r="G153" s="1" t="n">
+        <v>46103.71708333334</v>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" t="inlineStr">
+        <is>
+          <t>Safepay</t>
+        </is>
+      </c>
+      <c r="B154" t="inlineStr">
+        <is>
+          <t>"Safepay ransomware" OR "Safepay threat actor" OR "Safepay cyber attack"</t>
+        </is>
+      </c>
+      <c r="C154" t="inlineStr">
+        <is>
+          <t>'Largest breach in US history' exposes records of 26 million Americans - MSN</t>
+        </is>
+      </c>
+      <c r="D154" t="inlineStr">
+        <is>
+          <t>Thu, 19 Mar 2026 05:35:38 GMT</t>
+        </is>
+      </c>
+      <c r="E154" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMizgJBVV95cUxOdWplNEVxYXNDX0swM1NGQlR4ekNhMHlYNUdCUmdraXdHQ0ticWpic3BXZW9Cb0hfaUVJcTZjcmFGeUVySVhTdzVud083VFZxaVNYd1MxQUhTRHVqZGtPMk95U3VhaENoSmJsV1hwd0l4T1pwWEFtQXJYaWV4YmhiVHNJalh3ZHBZclBIcHR6eDFrRnJpRGhwb3B6VjZlSDJpNHN1V0RPUjUzUHItXzh6QTN5cWo4QWM3N3h6dlJlVkNsd0xSaWNnek5FS08ycFhrR2xRYWZWdGJMemtmTnI1OGllMDRFQzVFdVlHdWtMMjZ6aFZhVllvdWE1QndCWUxVWDRncFMzSFFUdEMzQUt3LWowbHdMYmtQeDA0Wl9UNjFpM18tT1NlMnV1dDdJcWlPVVJvVXF4VEotbE83LWxMUWtURDJyNXlPSHBscDRR?oc=5</t>
+        </is>
+      </c>
+      <c r="F154" t="n">
+        <v>7</v>
+      </c>
+      <c r="G154" s="1" t="n">
+        <v>46100.23307870371</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/latest_ransomware_news.xlsx
+++ b/data/latest_ransomware_news.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G154"/>
+  <dimension ref="A1:G165"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5506,6 +5506,369 @@
         <v>46100.23307870371</v>
       </c>
     </row>
+    <row r="155">
+      <c r="A155" t="inlineStr">
+        <is>
+          <t>Qilin</t>
+        </is>
+      </c>
+      <c r="B155" t="inlineStr">
+        <is>
+          <t>"Qilin ransomware" OR "Qilin threat actor" OR "Qilin cyber attack"</t>
+        </is>
+      </c>
+      <c r="C155" t="inlineStr">
+        <is>
+          <t>Qilin Ransomware allegedly breached chemical manufacturer giant Dow Inc - Security Affairs</t>
+        </is>
+      </c>
+      <c r="D155" t="inlineStr">
+        <is>
+          <t>Tue, 31 Mar 2026 07:24:25 GMT</t>
+        </is>
+      </c>
+      <c r="E155" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiwAFBVV95cUxOQkt5Zm1raGlFQ3ZFTWk2U01zUlZERzVMSTNPNTZhcHFCTkNqOThqUXpmVFNrVEdoUjVCZEhSSzAxV0wtS3p3NFRIeEJBempCQVd1cFRBS2JGdHpHQm5vNU5RZW4yaW10MTdJLTBpYnZ2Sm5wdXpxbDlmZnRrWTV2dGM0d3VDWVhYVmFGQ0RMWFFoaEgxd3NuMXdxRGdRdm1xTlREUm9fTjJ4YXJscWFwcFFYVWlXR2ZQX3BCZmFGUVI?oc=5</t>
+        </is>
+      </c>
+      <c r="F155" t="n">
+        <v>7</v>
+      </c>
+      <c r="G155" s="1" t="n">
+        <v>46112.30862268519</v>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" t="inlineStr">
+        <is>
+          <t>Qilin</t>
+        </is>
+      </c>
+      <c r="B156" t="inlineStr">
+        <is>
+          <t>"Qilin ransomware" OR "Qilin threat actor" OR "Qilin cyber attack"</t>
+        </is>
+      </c>
+      <c r="C156" t="inlineStr">
+        <is>
+          <t>Shwapno files GD seven months after customer data breach - The Business Standard</t>
+        </is>
+      </c>
+      <c r="D156" t="inlineStr">
+        <is>
+          <t>Sun, 29 Mar 2026 13:20:00 GMT</t>
+        </is>
+      </c>
+      <c r="E156" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMipgFBVV95cUxOV2t1VDZjSnhNR09hUHBiWEFFVlV0ZUtkaVVNUVUtSkwtUHNMTk11bEZRZ190a0lqYWM3eGltMThCNkFuT2tXbGxib3VFNF9TdDZKWEtNcUxOUlZEdXBONy1QTjZOME9PTkdnNzJNWWwxT2c5ZEVyb2h5ZDRPSk1LbmVTd28zdENtZm9BQ010OWZEWUM5WWhrNENnclE1V1o1elZiTlR30gGmAUFVX3lxTE5Xa3VUNmNKeE1HT2FQcGJYQUVWVXRlS2RpVU1RVS1KTC1Qc0xOTXVsRlFnX3RrSWphYzd4aW0xOEI2QW5Pa1dsbGJvdUU0X1N0NkpYS01xTE5SVkR1cE43LVBONk4wT09OR2c3Mk1ZbDFPZzlkRXJvaHlkNE9KTUtuZVN3bzN0Q21mb0FDTXQ5ZkRZQzlZaGs0Q2dyUTVXWjV6VmJOVHc?oc=5</t>
+        </is>
+      </c>
+      <c r="F156" t="n">
+        <v>7</v>
+      </c>
+      <c r="G156" s="1" t="n">
+        <v>46110.55555555555</v>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" t="inlineStr">
+        <is>
+          <t>Qilin</t>
+        </is>
+      </c>
+      <c r="B157" t="inlineStr">
+        <is>
+          <t>"Qilin ransomware" OR "Qilin threat actor" OR "Qilin cyber attack"</t>
+        </is>
+      </c>
+      <c r="C157" t="inlineStr">
+        <is>
+          <t>Rocky Mountain Care Cybersecurity Incident Triggers Legal, Regulatory, and Public Relations Crisis—Ongoing Pattern Indicates Persistent Threat, Potential Settlements Ahead - Bitget</t>
+        </is>
+      </c>
+      <c r="D157" t="inlineStr">
+        <is>
+          <t>Sat, 28 Mar 2026 01:41:02 GMT</t>
+        </is>
+      </c>
+      <c r="E157" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiY0FVX3lxTE4yRDJFemt6OUx6Nm14N1F4YjJGczdmLWI0OTFIeWpEc2dPeGhBZGlNS2x2RHdFdGRqWDU2c3FVeFBVcXBaa0lHN3hNbTN5Ukc1bkdpX2tqNlFSbE9qMTlnenVmb9IBY0FVX3lxTE4yRDJFemt6OUx6Nm14N1F4YjJGczdmLWI0OTFIeWpEc2dPeGhBZGlNS2x2RHdFdGRqWDU2c3FVeFBVcXBaa0lHN3hNbTN5Ukc1bkdpX2tqNlFSbE9qMTlnenVmbw?oc=5</t>
+        </is>
+      </c>
+      <c r="F157" t="n">
+        <v>7</v>
+      </c>
+      <c r="G157" s="1" t="n">
+        <v>46109.07016203704</v>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" t="inlineStr">
+        <is>
+          <t>Qilin</t>
+        </is>
+      </c>
+      <c r="B158" t="inlineStr">
+        <is>
+          <t>"Qilin ransomware" OR "Qilin threat actor" OR "Qilin cyber attack"</t>
+        </is>
+      </c>
+      <c r="C158" t="inlineStr">
+        <is>
+          <t>Rocky Mountain Care Discloses Data Breach Following Ransomware Attack - Claim Depot</t>
+        </is>
+      </c>
+      <c r="D158" t="inlineStr">
+        <is>
+          <t>Sun, 29 Mar 2026 03:26:34 GMT</t>
+        </is>
+      </c>
+      <c r="E158" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMicEFVX3lxTE9pc3FORzFtZDhURkRHUURBX0RFS3k5dVVUU0QxYV9Ec01pdGRXMFFDN3B0SVF5VGxPX1ZvYVJIWUh1eVExVEwzQXNZb3NhdzBkN3ozTGZvY3lKV1pfbS1xdXBvZFRLYTNoR3k1UmVYNXQ?oc=5</t>
+        </is>
+      </c>
+      <c r="F158" t="n">
+        <v>7</v>
+      </c>
+      <c r="G158" s="1" t="n">
+        <v>46110.14344907407</v>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" t="inlineStr">
+        <is>
+          <t>Qilin</t>
+        </is>
+      </c>
+      <c r="B159" t="inlineStr">
+        <is>
+          <t>"Qilin ransomware" OR "Qilin threat actor" OR "Qilin cyber attack"</t>
+        </is>
+      </c>
+      <c r="C159" t="inlineStr">
+        <is>
+          <t>Probe body inspects Daulatdia ferry site after Padma bus tragedy - The Business Standard</t>
+        </is>
+      </c>
+      <c r="D159" t="inlineStr">
+        <is>
+          <t>Sun, 29 Mar 2026 13:50:00 GMT</t>
+        </is>
+      </c>
+      <c r="E159" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiqwFBVV95cUxPbGNvQVZsaS1PWUg0Mk82WUlBUWs3M0JVU0djRWRmYWhRMXh0c1JTeEV4dFhiZURCelBXUmRpWF9fc0Z3UHhpdnVSakZFTzNuczktQmUwRDRzSmhfY1MySUtXSkp3RFF6cFJhQldQUElqcEowanBOUUo4c2dQNWc4MS1FM0ZIdjZaamxWOWp4c3FiWFJ5eUJRaDNNUmFTV1BtVDhyYmozOWo3Q1HSAbABQVVfeXFMT3Nqa2ZJdFRVLUNTdl9aYk9KMzgxUU1jMmFmLU0tbkRUbUVkZFNmVFF2dGxKQW5lMnJYVzU2OFhTVlNoaWdRR2g2bS1lNzJHVkRYZzNDWUNteU5zX0trSUg2S016VGZsTlptTmdNT3Z5aXdVOXpia3VVb3h4MlE3YUtaMlFoMkU3R2JDWXRJU0VMczFIMXlLMm44dlRJRXp3Nk1lS3FfRkNmQkpRVGt0VDE?oc=5</t>
+        </is>
+      </c>
+      <c r="F159" t="n">
+        <v>7</v>
+      </c>
+      <c r="G159" s="1" t="n">
+        <v>46110.57638888889</v>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" t="inlineStr">
+        <is>
+          <t>Akira</t>
+        </is>
+      </c>
+      <c r="B160" t="inlineStr">
+        <is>
+          <t>"Akira ransomware" OR "Akira threat actor" OR "Akira cyber attack"</t>
+        </is>
+      </c>
+      <c r="C160" t="inlineStr">
+        <is>
+          <t>Marquis Cyber Attack Affected Over 672,000, Akira Ransomware Gang Exonerated - CPO Magazine</t>
+        </is>
+      </c>
+      <c r="D160" t="inlineStr">
+        <is>
+          <t>Tue, 24 Mar 2026 11:00:00 GMT</t>
+        </is>
+      </c>
+      <c r="E160" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiugFBVV95cUxOVFRyRmNLT19DeHZPcjUxNTF2QXdUd2RKWkR3aV9hSFNnemZ4cnN3ME51SWJ5VlV4RlI2Wm13UFBieGdBdDNyZnBOT2FkY3BSdWNQZExzaVJxaGN1dF9DNzZnNU1ENm9fa2E5NlZkQ29obnRBdUdySVQxcGlFckpwZXBLQjlVY2lwd044TmJqd0hsT19oUE9NX1hFSFpYRFFvUWxWMHUyX2FKeml4bzNzZ2FKRGtUaDgtbHc?oc=5</t>
+        </is>
+      </c>
+      <c r="F160" t="n">
+        <v>7</v>
+      </c>
+      <c r="G160" s="1" t="n">
+        <v>46105.45833333334</v>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" t="inlineStr">
+        <is>
+          <t>LockBit</t>
+        </is>
+      </c>
+      <c r="B161" t="inlineStr">
+        <is>
+          <t>"LockBit ransomware" OR "LockBit threat actor" OR "LockBit cyber attack"</t>
+        </is>
+      </c>
+      <c r="C161" t="inlineStr">
+        <is>
+          <t>Pro-Ukraine hacker group Bearlyfy targets Russian companies with custom ransomware - The Record from Recorded Future News</t>
+        </is>
+      </c>
+      <c r="D161" t="inlineStr">
+        <is>
+          <t>Thu, 26 Mar 2026 15:34:42 GMT</t>
+        </is>
+      </c>
+      <c r="E161" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiakFVX3lxTFBRd3ljUTJkWnlrU2lfWS1lUzBqN2ZuVENwR3lWWlJHQUhwMDhGWEMxZmxDd2VVV3VEMWx0WFpQak1mdVBUN0ZJbXBhVFRiZWRDbHgzRHRGTElXN1Y1bWdVOGpuWTVyQURaTlE?oc=5</t>
+        </is>
+      </c>
+      <c r="F161" t="n">
+        <v>7</v>
+      </c>
+      <c r="G161" s="1" t="n">
+        <v>46107.64909722222</v>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" t="inlineStr">
+        <is>
+          <t>LockBit</t>
+        </is>
+      </c>
+      <c r="B162" t="inlineStr">
+        <is>
+          <t>"LockBit ransomware" OR "LockBit threat actor" OR "LockBit cyber attack"</t>
+        </is>
+      </c>
+      <c r="C162" t="inlineStr">
+        <is>
+          <t>Kash Patel ‘spiderkash’ leak triggers dozens of Solana memecoin scams - Protos | Informed crypto news</t>
+        </is>
+      </c>
+      <c r="D162" t="inlineStr">
+        <is>
+          <t>Mon, 30 Mar 2026 11:27:24 GMT</t>
+        </is>
+      </c>
+      <c r="E162" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMikAFBVV95cUxNN2tSYmkwdi1rN2owM0M2S3haSzlfLW5GYk44TWhMQjlrWV9vaWRnc0g1cUNoZU1lVjFCdlFfeUp2QUx5RkN0dDVyTkZweTlzcjhxUWF2bjFnRzBTbXNJZGFrLUZzOXVKZWlqaFBDV3BiV2pBSG82MjZHTXZXYnFDN0N4OVg2VkFBYVhsUjB4Qmk?oc=5</t>
+        </is>
+      </c>
+      <c r="F162" t="n">
+        <v>7</v>
+      </c>
+      <c r="G162" s="1" t="n">
+        <v>46111.47736111111</v>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" t="inlineStr">
+        <is>
+          <t>Play</t>
+        </is>
+      </c>
+      <c r="B163" t="inlineStr">
+        <is>
+          <t>"Play ransomware" OR "Play threat actor" OR "Play cyber attack"</t>
+        </is>
+      </c>
+      <c r="C163" t="inlineStr">
+        <is>
+          <t>Play Ransomware Destroys EDR/EPP via Disk Manager - Seizes Network Firewalls - Halcyon</t>
+        </is>
+      </c>
+      <c r="D163" t="inlineStr">
+        <is>
+          <t>Fri, 27 Mar 2026 01:16:11 GMT</t>
+        </is>
+      </c>
+      <c r="E163" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMixwFBVV95cUxPZTRQRHRUR25vRmdXVTlVU1hNZW5JbDkwWFg0ejVKOWR6elpiek9YbEpHTFlKU2tZaXdBREoxbkp6TVdCMmVCeFJobUVWRHA2Wm1xRlhRZ2RCeWkzaFlqeXI0dTdhU2ZrS1BUTFdVdktvQ0pHVmUyXzc3enJIZ094RkdrRVhYS1FmTGJNdGhKeF9HYXhYdWlWWlRqdWd5NktPcEduMzJ2b29fSVNycXhHTlFRNTBLRUUwdXg5ejFMREM1eEZYc3dR?oc=5</t>
+        </is>
+      </c>
+      <c r="F163" t="n">
+        <v>7</v>
+      </c>
+      <c r="G163" s="1" t="n">
+        <v>46108.05290509259</v>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" t="inlineStr">
+        <is>
+          <t>Play</t>
+        </is>
+      </c>
+      <c r="B164" t="inlineStr">
+        <is>
+          <t>"Play ransomware" OR "Play threat actor" OR "Play cyber attack"</t>
+        </is>
+      </c>
+      <c r="C164" t="inlineStr">
+        <is>
+          <t>Play Ransomware Strikes All Real Estate Title Solutions - DeXpose</t>
+        </is>
+      </c>
+      <c r="D164" t="inlineStr">
+        <is>
+          <t>Wed, 25 Mar 2026 00:00:00 GMT</t>
+        </is>
+      </c>
+      <c r="E164" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMihgFBVV95cUxPcFFULWp1VnA2Vk5pM0lRellZM2tEOHpYMnQ0YVZMNEhNNVlJWWdJOTBHUmNjWEw0ZEZRTG5tS2pzR294SmVxaHRySC1mM0RZVGlNNGZMeXVDRmZLZTdGdUYwd2ZVU3VhZ05PaDVVSHJ6UjlXdmNTQkltUDVxd0JFSEtPdmNTdw?oc=5</t>
+        </is>
+      </c>
+      <c r="F164" t="n">
+        <v>7</v>
+      </c>
+      <c r="G164" s="1" t="n">
+        <v>46106</v>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" t="inlineStr">
+        <is>
+          <t>Medusa</t>
+        </is>
+      </c>
+      <c r="B165" t="inlineStr">
+        <is>
+          <t>"Medusa ransomware" OR "Medusa threat actor" OR "Medusa cyber attack"</t>
+        </is>
+      </c>
+      <c r="C165" t="inlineStr">
+        <is>
+          <t>Spyware combing for data 'of use to China' hidden inside religious and cultural apps - MSN</t>
+        </is>
+      </c>
+      <c r="D165" t="inlineStr">
+        <is>
+          <t>Wed, 25 Mar 2026 01:09:54 GMT</t>
+        </is>
+      </c>
+      <c r="E165" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMigANBVV95cUxPQ254TXh5eE5rWTVQTDB6bVFnaktzZUpldFQ4aUtPOFE4OWpJTjlLb3d1M3ZIcG4tdm91cE83R1BqNlNPZWlRVHBXLVpEYjEzTUU5cWJhcjdJOWNMZWE5Nkp1am1aeko2cnBtem9MbGh4c2E0ZDVaQUx1UzFjT1p1YVJiS3UxWFJ0bjJZdGxNc2tHOWpOR1JqUTdEVHFScktSQkx6STAwcGpmb2RMaVRwT3B2YWRqMGRPNnZCNEdDdmU0bnRYLXBnZzJ5YjdWMTdqTHRSUklPWmZLdlVsMnY3WGg4T3BWZFB3QXMtMnJWdjFFTHV1VWNnR3M3bFhacWNtNHNMcWtJOWl4S3c3ZFd5cUlRQ2tGV2w1SnU2TW81Q04zM2taRDh5enZtVXNWcGg2cmMyQW5rZjV1M21EQjliMFBjakNOWGtjbzFHdTEyTTRZMUZ4LV9fVlNqelpNM1FKUmY4aDJ6U1JVZGd1VWtDdy1uYlB4TE52OXdmcFZYS0k?oc=5</t>
+        </is>
+      </c>
+      <c r="F165" t="n">
+        <v>7</v>
+      </c>
+      <c r="G165" s="1" t="n">
+        <v>46106.04854166666</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/latest_ransomware_news.xlsx
+++ b/data/latest_ransomware_news.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G165"/>
+  <dimension ref="A1:G174"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5869,6 +5869,303 @@
         <v>46106.04854166666</v>
       </c>
     </row>
+    <row r="166">
+      <c r="A166" t="inlineStr">
+        <is>
+          <t>Qilin</t>
+        </is>
+      </c>
+      <c r="B166" t="inlineStr">
+        <is>
+          <t>"Qilin ransomware" OR "Qilin threat actor" OR "Qilin cyber attack"</t>
+        </is>
+      </c>
+      <c r="C166" t="inlineStr">
+        <is>
+          <t>Qilin Ransomware allegedly breached chemical manufacturer giant Dow Inc - Security Affairs</t>
+        </is>
+      </c>
+      <c r="D166" t="inlineStr">
+        <is>
+          <t>Mon, 30 Mar 2026 07:00:00 GMT</t>
+        </is>
+      </c>
+      <c r="E166" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMi3gFBVV95cUxOZE5ib19aMEdtVlZLeGJXd3JuLTQ3bXBvanI3RzhKV2luZThqOWhmTTFrY0R4c3ZvdENKV1NPT2NtZjFCcGRWT3lKQmUtVjRZMXNkazdxNE9zbzExWVJZeUViWkxrU2NZbGpER1VsZXltWHVON21XMUNCbGxxXzFSblk3c0VZM1dRekU0bTJESjRXTUUzWWZqS3FmQzN2aXdIaWt0QVhXcWF3bV95eld0Y0JBRzdyUElOU3poY09XbFBJN2hQWUE0SUJ6amViVjZMbDEyMmtqZUFCUkozOXc?oc=5</t>
+        </is>
+      </c>
+      <c r="F166" t="n">
+        <v>7</v>
+      </c>
+      <c r="G166" s="1" t="n">
+        <v>46111.29166666666</v>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" t="inlineStr">
+        <is>
+          <t>Qilin</t>
+        </is>
+      </c>
+      <c r="B167" t="inlineStr">
+        <is>
+          <t>"Qilin ransomware" OR "Qilin threat actor" OR "Qilin cyber attack"</t>
+        </is>
+      </c>
+      <c r="C167" t="inlineStr">
+        <is>
+          <t>AI in Local Government: Lessons from 2025 and Emerging Cyber Threats in 2026 - National League of Cities</t>
+        </is>
+      </c>
+      <c r="D167" t="inlineStr">
+        <is>
+          <t>Fri, 27 Mar 2026 14:35:04 GMT</t>
+        </is>
+      </c>
+      <c r="E167" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMitgFBVV95cUxPWWNtSjZkYnZYQ1ZUZUMycUJwMmNDd1hSdmQyeDlFSUV6dFJ1bEQ0TTFNdTRkUDBTZmFCM2FPWlZYMVBQYkVzdzl2b3NfNkJrU016VXIwVmdDcEtWRGpSQ2l4NnF2ZjVsSUxqMUt3STR4MG5OcHgtZEwxalQtc1ZMQnBSbl9pNkVBYjZVN0ZnV3lzcHA2YnJzNUhxLW1QVVoyMTJnZFR6MFFKN0x0V3dzNDNjU0hZUQ?oc=5</t>
+        </is>
+      </c>
+      <c r="F167" t="n">
+        <v>7</v>
+      </c>
+      <c r="G167" s="1" t="n">
+        <v>46108.60768518518</v>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" t="inlineStr">
+        <is>
+          <t>Qilin</t>
+        </is>
+      </c>
+      <c r="B168" t="inlineStr">
+        <is>
+          <t>"Qilin ransomware" OR "Qilin threat actor" OR "Qilin cyber attack"</t>
+        </is>
+      </c>
+      <c r="C168" t="inlineStr">
+        <is>
+          <t>Rocky Mountain Care Cybersecurity Incident Triggers Legal, Regulatory, and Public Relations Crisis—Ongoing Pattern Indicates Persistent Threat, Potential Settlements Ahead - bitget.com</t>
+        </is>
+      </c>
+      <c r="D168" t="inlineStr">
+        <is>
+          <t>Fri, 27 Mar 2026 10:36:55 GMT</t>
+        </is>
+      </c>
+      <c r="E168" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiXkFVX3lxTE9aQTJPdGMzRDRpR1hRUjBLMENELUlDMlZfbS0xemo0RWk5eklXZkpqemNET2tfQ1cyeXRkWWRtbU9zdmp3bmFSZzBqUno0aWdtb1dRdWo3bXctaEItdGfSAWNBVV95cUxOMkQyRXprejlMejZteDdReGIyRnM3Zi1iNDkxSHlqRHNnT3hoQWRpTUtsdkR3RXRkalg1NnNxVXhQVXFwWmtJRzd4TW0zeVJHNW5HaV9rajZRUmxPajE5Z3p1Zm8?oc=5</t>
+        </is>
+      </c>
+      <c r="F168" t="n">
+        <v>7</v>
+      </c>
+      <c r="G168" s="1" t="n">
+        <v>46108.44230324074</v>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" t="inlineStr">
+        <is>
+          <t>Akira</t>
+        </is>
+      </c>
+      <c r="B169" t="inlineStr">
+        <is>
+          <t>"Akira ransomware" OR "Akira threat actor" OR "Akira cyber attack"</t>
+        </is>
+      </c>
+      <c r="C169" t="inlineStr">
+        <is>
+          <t>Akira Ransomware Targets Cox Design &amp; Metal Fabrication in the USA - DeXpose</t>
+        </is>
+      </c>
+      <c r="D169" t="inlineStr">
+        <is>
+          <t>Wed, 01 Apr 2026 00:00:00 GMT</t>
+        </is>
+      </c>
+      <c r="E169" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMikgFBVV95cUxPZFdDbkdKZ281cjFaQVpqcTE1SU1WZTJudnp6cDQ3ZWdhaG81TXBGUGJIaGhmRWhOQWxPRld1dDNKbkxNODIxckN4R0lJZkxTOE9sUTNNdTZ4OVpIbHJNdEVwZUJGakl4cktGZGY2WFZUWlNfdy1JZmU3LV9EMVJWMkxBc2MwZkxzT2FXMER3NHdYQQ?oc=5</t>
+        </is>
+      </c>
+      <c r="F169" t="n">
+        <v>7</v>
+      </c>
+      <c r="G169" s="1" t="n">
+        <v>46113</v>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" t="inlineStr">
+        <is>
+          <t>Everest</t>
+        </is>
+      </c>
+      <c r="B170" t="inlineStr">
+        <is>
+          <t>"Everest ransomware" OR "Everest threat actor" OR "Everest cyber attack"</t>
+        </is>
+      </c>
+      <c r="C170" t="inlineStr">
+        <is>
+          <t>Everest Ransomware Targets Panamanian Wind Farm Parque Eólico Toabré - DeXpose</t>
+        </is>
+      </c>
+      <c r="D170" t="inlineStr">
+        <is>
+          <t>Tue, 31 Mar 2026 00:00:00 GMT</t>
+        </is>
+      </c>
+      <c r="E170" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMilwFBVV95cUxPUXZLME4wNXM1NWctUlk3ei1qWF9ncUFrcl96ZFItUlBnNjlzTEs3QUdMbGVJNTBUZlNtdDFQX1VmTTN3aUcyMEZOWENHUVRlNjlOa2Z6NkJRcnRsZUloNmxMejRhaG94QWdDVWJaOFVNNDl6bERtV2tyaDRNYmZMS05hdUJSRHI2SU4yREJfc0xUeHJ5Z3I4?oc=5</t>
+        </is>
+      </c>
+      <c r="F170" t="n">
+        <v>7</v>
+      </c>
+      <c r="G170" s="1" t="n">
+        <v>46112</v>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" t="inlineStr">
+        <is>
+          <t>LockBit</t>
+        </is>
+      </c>
+      <c r="B171" t="inlineStr">
+        <is>
+          <t>"LockBit ransomware" OR "LockBit threat actor" OR "LockBit cyber attack"</t>
+        </is>
+      </c>
+      <c r="C171" t="inlineStr">
+        <is>
+          <t>Exclusive: Cuddly toy maker Charlie Bears allegedly hacked - Cyber Daily</t>
+        </is>
+      </c>
+      <c r="D171" t="inlineStr">
+        <is>
+          <t>Wed, 01 Apr 2026 00:18:14 GMT</t>
+        </is>
+      </c>
+      <c r="E171" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMinwFBVV95cUxOUFRiUHJic2FvbXFWamhEakl0QlllSWxCRmhwVGxCUl8xUFphMU9sRENSRE9neklXbmh5Rk1WR3lGZnNndnA2dFBQaVo1Ylc2UW9Xcy1UbURiUDkzWjZ1MzJQTUdTN0Zab0hMNW1SYnJKamluSnpneldpcnBsLWJ4UnZNYkdpek9Dd2J6VXI1U0FJWXFyTFlKUWtvUW1KZTA?oc=5</t>
+        </is>
+      </c>
+      <c r="F171" t="n">
+        <v>7</v>
+      </c>
+      <c r="G171" s="1" t="n">
+        <v>46113.01266203704</v>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" t="inlineStr">
+        <is>
+          <t>Lynx</t>
+        </is>
+      </c>
+      <c r="B172" t="inlineStr">
+        <is>
+          <t>"Lynx ransomware" OR "Lynx threat actor" OR "Lynx cyber attack"</t>
+        </is>
+      </c>
+      <c r="C172" t="inlineStr">
+        <is>
+          <t>Royal Chemical Data Breach Investigation - Claim Depot</t>
+        </is>
+      </c>
+      <c r="D172" t="inlineStr">
+        <is>
+          <t>Wed, 25 Mar 2026 21:06:58 GMT</t>
+        </is>
+      </c>
+      <c r="E172" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMifkFVX3lxTE1JUDJHRlItNWx5OVpvaW5ET2x0RGc3cExaY0dsTDIyNFlOVmFWSk9feWJVMGN3bXY5WkgxbF8taTBqYkplVWI0SmVRRjFzS2VUaHJJNk5wSTNkSk5HYzlXb1otUjFaeUNvOHJqU3ZOZnNUalVDOGVTZXliUWNPQQ?oc=5</t>
+        </is>
+      </c>
+      <c r="F172" t="n">
+        <v>7</v>
+      </c>
+      <c r="G172" s="1" t="n">
+        <v>46106.87983796297</v>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" t="inlineStr">
+        <is>
+          <t>Medusa</t>
+        </is>
+      </c>
+      <c r="B173" t="inlineStr">
+        <is>
+          <t>"Medusa ransomware" OR "Medusa threat actor" OR "Medusa cyber attack"</t>
+        </is>
+      </c>
+      <c r="C173" t="inlineStr">
+        <is>
+          <t>Myrtle Beach/Florence Topic Medusa ransomware | News, Weather, Sports, Breaking News - WPDE</t>
+        </is>
+      </c>
+      <c r="D173" t="inlineStr">
+        <is>
+          <t>Fri, 27 Mar 2026 18:56:55 GMT</t>
+        </is>
+      </c>
+      <c r="E173" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiVEFVX3lxTE1naHJfZkVrbm1BUW9Ba1ZVcWJzd0V4WFRKcS1HNWRDdUNxX0NzUmJnOHk0cmszT1cyVV9XNTFrSG5sQWNBemJabmtVTmdBZVF2ZHRmag?oc=5</t>
+        </is>
+      </c>
+      <c r="F173" t="n">
+        <v>7</v>
+      </c>
+      <c r="G173" s="1" t="n">
+        <v>46108.78952546296</v>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" t="inlineStr">
+        <is>
+          <t>Medusa</t>
+        </is>
+      </c>
+      <c r="B174" t="inlineStr">
+        <is>
+          <t>"Medusa ransomware" OR "Medusa threat actor" OR "Medusa cyber attack"</t>
+        </is>
+      </c>
+      <c r="C174" t="inlineStr">
+        <is>
+          <t>Acme Truck Line Data Breach Lawsuit Investigation - Claim Depot</t>
+        </is>
+      </c>
+      <c r="D174" t="inlineStr">
+        <is>
+          <t>Mon, 30 Mar 2026 16:00:13 GMT</t>
+        </is>
+      </c>
+      <c r="E174" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMif0FVX3lxTFB4T1pDTkJTb3NjWVczTHF3ZmpXNWYzelA1NDJtY3BKdU1Va093WXZ4VVU3YlpLZFpHcFRuVzV3ZTJyc3VVNkpvX0hlY3JveWg5aU51ejRxeFNDV3dBYUV0WE9sTFlhYndlVkRzNHh2eDZmcGNWU0Qyc2NKa0xxWWs?oc=5</t>
+        </is>
+      </c>
+      <c r="F174" t="n">
+        <v>7</v>
+      </c>
+      <c r="G174" s="1" t="n">
+        <v>46111.66681712963</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/latest_ransomware_news.xlsx
+++ b/data/latest_ransomware_news.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G174"/>
+  <dimension ref="A1:G178"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6166,6 +6166,138 @@
         <v>46111.66681712963</v>
       </c>
     </row>
+    <row r="175">
+      <c r="A175" t="inlineStr">
+        <is>
+          <t>Dragonforce</t>
+        </is>
+      </c>
+      <c r="B175" t="inlineStr">
+        <is>
+          <t>"Dragonforce ransomware" OR "Dragonforce threat actor" OR "Dragonforce cyber attack"</t>
+        </is>
+      </c>
+      <c r="C175" t="inlineStr">
+        <is>
+          <t>Watch: DragonForce Ransomware and the Evolving Affiliate Ecosystem - Sophos</t>
+        </is>
+      </c>
+      <c r="D175" t="inlineStr">
+        <is>
+          <t>Fri, 03 Apr 2026 07:00:00 GMT</t>
+        </is>
+      </c>
+      <c r="E175" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiuwFBVV95cUxOQXp6MDlPRXR4SGxuMDZXX09LSWVrYmw4M0hWUDJsUUdROXJWLXhzakljR29wdUp4a0pVeHJyX2RMSFo1eEJyazE4NzZTTk1QeEtXRjdqQWxUT2tsZzR3VUdqNmJaU1laNlg3WDBUV0VRNDF0VXNWcDdROWpHSzlsaGlUeUxUZXp4SGRJZEJCOThIQVVfTUtkTWZyanZscF82UURVdUZtMFp5cXJIUE9sS0ktRGlVdlFVOHR3?oc=5</t>
+        </is>
+      </c>
+      <c r="F175" t="n">
+        <v>7</v>
+      </c>
+      <c r="G175" s="1" t="n">
+        <v>46115.29166666666</v>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" t="inlineStr">
+        <is>
+          <t>Everest</t>
+        </is>
+      </c>
+      <c r="B176" t="inlineStr">
+        <is>
+          <t>"Everest ransomware" OR "Everest threat actor" OR "Everest cyber attack"</t>
+        </is>
+      </c>
+      <c r="C176" t="inlineStr">
+        <is>
+          <t>Everest increases pressure on Nissan, but desperation creeps in - cybernews.com</t>
+        </is>
+      </c>
+      <c r="D176" t="inlineStr">
+        <is>
+          <t>Wed, 01 Apr 2026 10:17:28 GMT</t>
+        </is>
+      </c>
+      <c r="E176" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMid0FVX3lxTE5YOEpIMnJTanpGRnRvOUNzSFBfWEFJM1Y4SnA2LXRLdGFNMTJmaGFsZmpYNm45TWh2RUhhS1N3VmFMLTBxOEhJN2p0UmJsRWM4c2xObjJzZU45VnNGNVlyT1RhUFhBbXZTQnhNQ3l0S0YyNjVZYmJr?oc=5</t>
+        </is>
+      </c>
+      <c r="F176" t="n">
+        <v>7</v>
+      </c>
+      <c r="G176" s="1" t="n">
+        <v>46113.4287962963</v>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" t="inlineStr">
+        <is>
+          <t>Play</t>
+        </is>
+      </c>
+      <c r="B177" t="inlineStr">
+        <is>
+          <t>"Play ransomware" OR "Play threat actor" OR "Play cyber attack"</t>
+        </is>
+      </c>
+      <c r="C177" t="inlineStr">
+        <is>
+          <t>World’s most powerful demolition robot maker allegedly hacked - cybernews.com</t>
+        </is>
+      </c>
+      <c r="D177" t="inlineStr">
+        <is>
+          <t>Thu, 02 Apr 2026 15:17:13 GMT</t>
+        </is>
+      </c>
+      <c r="E177" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMibEFVX3lxTE94WlRwVV8zWWxrbXg1cTRzaXN1Y3NLRmZ5MUxLNWFGei1GQXZJR3lIbnQtNDRzLVFoc1NRVGI5bnVmbW9wMVEyREtMQksxZzAwLUtOUWs0MG04NWdfbW0zZ2R4WGM4SURWeTIydg?oc=5</t>
+        </is>
+      </c>
+      <c r="F177" t="n">
+        <v>7</v>
+      </c>
+      <c r="G177" s="1" t="n">
+        <v>46114.63695601852</v>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" t="inlineStr">
+        <is>
+          <t>Cl0p</t>
+        </is>
+      </c>
+      <c r="B178" t="inlineStr">
+        <is>
+          <t>"Cl0p ransomware" OR "Cl0p threat actor" OR "Cl0p cyber attack"</t>
+        </is>
+      </c>
+      <c r="C178" t="inlineStr">
+        <is>
+          <t>Check City ties 320,000-customer breach to Clop, sends notices a year later - cybernews.com</t>
+        </is>
+      </c>
+      <c r="D178" t="inlineStr">
+        <is>
+          <t>Fri, 03 Apr 2026 02:18:32 GMT</t>
+        </is>
+      </c>
+      <c r="E178" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMihwFBVV95cUxPVjh1dnZNRTVTaTZRaTU5VEVndENhVzBmb0pnOUtzSW5XcW1IRTM4YU5uQ1NPRTJnbVRHQzJTSllvaTFLVTRaN2xkZDl1WDl3dVdVZUJ1YkVCajZpTzdjdGtuT0pEV1FJS0R0emJ2UTNpeHNIOEtLMUVKTVgyRWxSUVJPR2xBalU?oc=5</t>
+        </is>
+      </c>
+      <c r="F178" t="n">
+        <v>7</v>
+      </c>
+      <c r="G178" s="1" t="n">
+        <v>46115.0962037037</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/latest_ransomware_news.xlsx
+++ b/data/latest_ransomware_news.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G178"/>
+  <dimension ref="A1:G183"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6298,6 +6298,171 @@
         <v>46115.0962037037</v>
       </c>
     </row>
+    <row r="179">
+      <c r="A179" t="inlineStr">
+        <is>
+          <t>Qilin</t>
+        </is>
+      </c>
+      <c r="B179" t="inlineStr">
+        <is>
+          <t>"Qilin ransomware" OR "Qilin threat actor" OR "Qilin cyber attack"</t>
+        </is>
+      </c>
+      <c r="C179" t="inlineStr">
+        <is>
+          <t>Qilin ransomware group targets German political party Die Linke, threatens data leak | brief | SC Media - SC Media</t>
+        </is>
+      </c>
+      <c r="D179" t="inlineStr">
+        <is>
+          <t>Mon, 06 Apr 2026 14:19:14 GMT</t>
+        </is>
+      </c>
+      <c r="E179" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiswFBVV95cUxOY2JTM3NacE5HbmdJYnF2VzlYMDNiVWgxWWVzY0JkS2d4dHlNRmg5ZUF4TGZKUW1WeHQtTnpSU2s1ekgxRWpMbHM1V3I3WVNZVWhRbFF1VUduS091bXMwM1NLb2hvbzZ1aWFqUWM5ZWs3OHBzenhLZm9xU1NUVmk2VHBJMFc4YjVQQ2xYYzN0ZFBfQnpnVWUtMllJVlFfd2tJU1kxWGt0UFZ6SW1PcHpjRDA0UQ?oc=5</t>
+        </is>
+      </c>
+      <c r="F179" t="n">
+        <v>7</v>
+      </c>
+      <c r="G179" s="1" t="n">
+        <v>46118.59668981482</v>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" t="inlineStr">
+        <is>
+          <t>Qilin</t>
+        </is>
+      </c>
+      <c r="B180" t="inlineStr">
+        <is>
+          <t>"Qilin ransomware" OR "Qilin threat actor" OR "Qilin cyber attack"</t>
+        </is>
+      </c>
+      <c r="C180" t="inlineStr">
+        <is>
+          <t>Seeing Machines Faces Unsubstantiated Cyber Allegation—Analysts Predict 166% Growth as Market Overlooks the Opportunity - Bitget</t>
+        </is>
+      </c>
+      <c r="D180" t="inlineStr">
+        <is>
+          <t>Thu, 09 Apr 2026 17:21:41 GMT</t>
+        </is>
+      </c>
+      <c r="E180" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiXkFVX3lxTE56UnlnZl9sTjQ2ay03TjJsV3VTTWFrMnBQR0pCaTBDUnoxckVVcXh3SjJiaVZQbHNQWllQUVMwbTlibTRMeGJBZk5tbnNtYzRKU18wRkxiZDBoTjE4eWfSAWNBVV95cUxObV9HOXJhb0pFNnB6eWMwWnZWaDRPUl9WMUdKaTdjalRhVW5kcnllV1V2bnRXbDA2b21haU13NU9OSWFGNjF0Y24yUzk4YldFcVlRODltejVtZ1pDbVY3aTUwVTA?oc=5</t>
+        </is>
+      </c>
+      <c r="F180" t="n">
+        <v>7</v>
+      </c>
+      <c r="G180" s="1" t="n">
+        <v>46121.7233912037</v>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" t="inlineStr">
+        <is>
+          <t>Qilin</t>
+        </is>
+      </c>
+      <c r="B181" t="inlineStr">
+        <is>
+          <t>"Qilin ransomware" OR "Qilin threat actor" OR "Qilin cyber attack"</t>
+        </is>
+      </c>
+      <c r="C181" t="inlineStr">
+        <is>
+          <t>Exclusive: Aussie tech firm Seeing Machines confirms potential cyber security incident - Cyber Daily</t>
+        </is>
+      </c>
+      <c r="D181" t="inlineStr">
+        <is>
+          <t>Wed, 08 Apr 2026 03:47:41 GMT</t>
+        </is>
+      </c>
+      <c r="E181" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMixAFBVV95cUxPVHhUVUl5RzZJdTM2VGFZbEt1emRaVDltTnB2RTBLNTNvNjBVZGZBRDFta3E4WlFSYlh5b2ZHZ1pWbzZ1SjRFZlNqeDM1QVgtOGZkX2pzWnc5dGVTRUNOaDkzYUpWNS1QV0xSWUhQenJ1bnRSMlJleG56bngyVUhmcTVlY1JtZzJ1TzFkcnhtZU1sTzFvU1RoakswSlZTNl9YVXJiemhoempCa2FwV1JEd0FOSEJLNXd3Z3hFeDc1aHVtbjBz?oc=5</t>
+        </is>
+      </c>
+      <c r="F181" t="n">
+        <v>7</v>
+      </c>
+      <c r="G181" s="1" t="n">
+        <v>46120.15811342592</v>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" t="inlineStr">
+        <is>
+          <t>Play</t>
+        </is>
+      </c>
+      <c r="B182" t="inlineStr">
+        <is>
+          <t>"Play ransomware" OR "Play threat actor" OR "Play cyber attack"</t>
+        </is>
+      </c>
+      <c r="C182" t="inlineStr">
+        <is>
+          <t>Netherlands refuses to ban ransom payments despite hacker extortion surge - Cybernews</t>
+        </is>
+      </c>
+      <c r="D182" t="inlineStr">
+        <is>
+          <t>Fri, 10 Apr 2026 08:31:18 GMT</t>
+        </is>
+      </c>
+      <c r="E182" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMihAFBVV95cUxQQnMySG1ocUhBNkxWaTRSYWpuR3BOV3dTVmpXbUZFTmNNa0dJNkQzV2hKNmFZRi0zYUo2NDVhdFhaazdFc2FoTjRNRVpnLVZpNHdYNWxSN3lEeEV5R1l0b3otb0lKemdfNTlDc1hIMFowSklUNVVuNHZpZlpYbExHZm4tMnA?oc=5</t>
+        </is>
+      </c>
+      <c r="F182" t="n">
+        <v>7</v>
+      </c>
+      <c r="G182" s="1" t="n">
+        <v>46122.35506944444</v>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" t="inlineStr">
+        <is>
+          <t>Safepay</t>
+        </is>
+      </c>
+      <c r="B183" t="inlineStr">
+        <is>
+          <t>"Safepay ransomware" OR "Safepay threat actor" OR "Safepay cyber attack"</t>
+        </is>
+      </c>
+      <c r="C183" t="inlineStr">
+        <is>
+          <t>Jeff Shell Steps Down as Paramount President Amid Legal Turmoil and Fresh Controversy - The Plunge Daily</t>
+        </is>
+      </c>
+      <c r="D183" t="inlineStr">
+        <is>
+          <t>Thu, 09 Apr 2026 10:18:23 GMT</t>
+        </is>
+      </c>
+      <c r="E183" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMi_wFBVV95cUxNWU1McXFRUGhLNWdFcWE5RS1CTXR2M2h5ZEkwWVZtLUwyQkRiMkNSZnRRVUIyZ1R5c2l2TXRXNllNVXZDOGRDb3ZyZ1FCZUd0VjhWQ1g1dGdlUnhSVTJsTGtuUl9LZlVEVWhja2xoSWtNbW9RNmRRTndreV8tREphY1NWSFVUT0tRQkhRSlUzVExhY2ZGVFlSUXlIWmY2c0pHemZ1VXhPaGJGbmxLYkpGLUdENDladTJnd2dhOVVGcTVIdzRkc0dUYzQ4eDRMN1BtVU5TRno3aWFYSjMtRzYtNHRwN3NPVXNzZU5MRnBxcE1aR1h0N25FTkRwaGtrX0E?oc=5</t>
+        </is>
+      </c>
+      <c r="F183" t="n">
+        <v>7</v>
+      </c>
+      <c r="G183" s="1" t="n">
+        <v>46121.42943287037</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/latest_ransomware_news.xlsx
+++ b/data/latest_ransomware_news.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G183"/>
+  <dimension ref="A1:G186"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6463,6 +6463,105 @@
         <v>46121.42943287037</v>
       </c>
     </row>
+    <row r="184">
+      <c r="A184" t="inlineStr">
+        <is>
+          <t>Qilin</t>
+        </is>
+      </c>
+      <c r="B184" t="inlineStr">
+        <is>
+          <t>"Qilin ransomware" OR "Qilin threat actor" OR "Qilin cyber attack"</t>
+        </is>
+      </c>
+      <c r="C184" t="inlineStr">
+        <is>
+          <t>NYC Transit Workers Hit by Qilin Ransomware: Thousands of Members Potentially Affected in Major Data Breach - ekhbary.com</t>
+        </is>
+      </c>
+      <c r="D184" t="inlineStr">
+        <is>
+          <t>Sun, 12 Apr 2026 14:23:53 GMT</t>
+        </is>
+      </c>
+      <c r="E184" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMi4gFBVV95cUxOd1FXQVFjTWxNaEFIUkY4THBVZmFHWldVeENHOFZLbk1qSUNyeGw2WElQUTE2ZG9ocGxsS3V6XzdKR3ZfTTVMdUlQQVpBLTh5dkNyVVphZDFmUGw1RkhwalczOWJJemdmTGc2MXIta05xV0pNelhxTVF1U2dmRmxKeWJHNk5ETThhMG1CX0NJRjlld0xKNDRIblYyRzhUdlRJbmVZNFhkSGRVa1RWU0g1QVEtenlUT1cwUVdfY3h5TWQzWEZrR0pXM3NPLVloaERWMnBuNUFIeHhIaWk3V3RHMm5R?oc=5</t>
+        </is>
+      </c>
+      <c r="F184" t="n">
+        <v>30</v>
+      </c>
+      <c r="G184" s="1" t="n">
+        <v>46124.59991898148</v>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" t="inlineStr">
+        <is>
+          <t>Cl0p</t>
+        </is>
+      </c>
+      <c r="B185" t="inlineStr">
+        <is>
+          <t>"Cl0p ransomware" OR "Cl0p threat actor" OR "Cl0p cyber attack"</t>
+        </is>
+      </c>
+      <c r="C185" t="inlineStr">
+        <is>
+          <t>Oracle EBS Hack: Only 4 Corporate Giants Still Silent on Potential Impact - SecurityWeek</t>
+        </is>
+      </c>
+      <c r="D185" t="inlineStr">
+        <is>
+          <t>Mon, 16 Mar 2026 07:00:00 GMT</t>
+        </is>
+      </c>
+      <c r="E185" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMipAFBVV95cUxPMFJyOUtVUndEV0tOLTJ2NGluWEo4allSbTY5dmVLcEFrUUI4Ym1IX2tJMDcxWDNJZTVDSGdNREpqMTJGRUhrQ1dzWTdHdVJSRWxsMTNPOXpfdUNoNC1ydXMtSW5BSzdHVTB4TTFPVS1HNnVkcExSYzJTT3hlVDR0TEw0bXhrOGhVT0dDTWt2ZmtSb0drVmhzdXFCVlJRSGZ2Nlp6SdIBqgFBVV95cUxNb3lIOVczcGZVblNTWkJ2b2RSbHZPMXZEaTNtNUFWR2w0YUR5QVFOMFlNcHpsUFhtbDM5SEhrdnN4cG81b3BkRjdLSWNUVGJVMU5xZTNBbk9FMk9qNXJRR1pWWWRmeVR5R3kwZHhnNjVQV2x6YUZabFVsVmVxN2sxLWprVDdmY0g4UGVjdWFXcUtfaG1MRHR4LTNlbFE1TVhQel8yYmJuQXE2dw?oc=5</t>
+        </is>
+      </c>
+      <c r="F185" t="n">
+        <v>30</v>
+      </c>
+      <c r="G185" s="1" t="n">
+        <v>46097.29166666666</v>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" t="inlineStr">
+        <is>
+          <t>Interlock</t>
+        </is>
+      </c>
+      <c r="B186" t="inlineStr">
+        <is>
+          <t>"Interlock ransomware" OR "Interlock threat actor" OR "Interlock cyber attack"</t>
+        </is>
+      </c>
+      <c r="C186" t="inlineStr">
+        <is>
+          <t>Cisco’s latest vulnerability spree has a more troubling pattern underneath - CyberScoop</t>
+        </is>
+      </c>
+      <c r="D186" t="inlineStr">
+        <is>
+          <t>Wed, 18 Mar 2026 07:00:00 GMT</t>
+        </is>
+      </c>
+      <c r="E186" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMie0FVX3lxTE9iSGlPV1BTWUYzbFl5blZwd21tcG1TelI5OEZXNnhUbXlOWDFzNjQ3R0Z3RnhtUGtxbmNNVC0wLTEwWVl0OWdCRDZCVmpaZDZZSlFkVzZmU1ZaTjZhSFhOWjhzVW1HWHhpNU4tS2xReWxKY2FvcmdiQUFkaw?oc=5</t>
+        </is>
+      </c>
+      <c r="F186" t="n">
+        <v>30</v>
+      </c>
+      <c r="G186" s="1" t="n">
+        <v>46099.29166666666</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/latest_ransomware_news.xlsx
+++ b/data/latest_ransomware_news.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G186"/>
+  <dimension ref="A1:G189"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6562,6 +6562,105 @@
         <v>46099.29166666666</v>
       </c>
     </row>
+    <row r="187">
+      <c r="A187" t="inlineStr">
+        <is>
+          <t>Dragonforce</t>
+        </is>
+      </c>
+      <c r="B187" t="inlineStr">
+        <is>
+          <t>"Dragonforce ransomware" OR "Dragonforce threat actor" OR "Dragonforce cyber attack"</t>
+        </is>
+      </c>
+      <c r="C187" t="inlineStr">
+        <is>
+          <t>Ransomware-Linked ViperTunnel Malware Hits UK and US Businesses - Hackread</t>
+        </is>
+      </c>
+      <c r="D187" t="inlineStr">
+        <is>
+          <t>Tue, 14 Apr 2026 10:02:28 GMT</t>
+        </is>
+      </c>
+      <c r="E187" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMieEFVX3lxTE9WQlQ0T1ZyWUtQTXpMZzZNZTIydlV4OFlTbG9Pd3B5cHNyclNrZzEyWjdkSjYtSlV6ZVdfbGFJc1lJbWVpZmM2bDZrZENwNkZiSkYxVlpwOE5BT3NFbEJ5eV9yNUt0aks1OTdSNUVKbFI2OVBaaHB4LQ?oc=5</t>
+        </is>
+      </c>
+      <c r="F187" t="n">
+        <v>30</v>
+      </c>
+      <c r="G187" s="1" t="n">
+        <v>46126.41837962963</v>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" t="inlineStr">
+        <is>
+          <t>Dragonforce</t>
+        </is>
+      </c>
+      <c r="B188" t="inlineStr">
+        <is>
+          <t>"Dragonforce ransomware" OR "Dragonforce threat actor" OR "Dragonforce cyber attack"</t>
+        </is>
+      </c>
+      <c r="C188" t="inlineStr">
+        <is>
+          <t>Obfuscated Loader Chain Delivers VIPERTUNNEL Backdoor via Fake DLL - cyberpress.org</t>
+        </is>
+      </c>
+      <c r="D188" t="inlineStr">
+        <is>
+          <t>Tue, 14 Apr 2026 05:58:05 GMT</t>
+        </is>
+      </c>
+      <c r="E188" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiZ0FVX3lxTE14dTI0cUZmR3Y3cjAtWlVKMkVzSmlMZ3N2ODRYZURLaF9xbjJCQ0dJUmNqWGJKNjFXdDBIYk93QUctc2ZRem1rb0IwcFAwc3NFWGx3YTZoNmI1cnl6dEVka3hqdjZPV1U?oc=5</t>
+        </is>
+      </c>
+      <c r="F188" t="n">
+        <v>30</v>
+      </c>
+      <c r="G188" s="1" t="n">
+        <v>46126.24866898148</v>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" t="inlineStr">
+        <is>
+          <t>Interlock</t>
+        </is>
+      </c>
+      <c r="B189" t="inlineStr">
+        <is>
+          <t>"Interlock ransomware" OR "Interlock threat actor" OR "Interlock cyber attack"</t>
+        </is>
+      </c>
+      <c r="C189" t="inlineStr">
+        <is>
+          <t>Hacker group claims theft of over 730K patient files from hospital in region - MSN</t>
+        </is>
+      </c>
+      <c r="D189" t="inlineStr">
+        <is>
+          <t>Mon, 13 Apr 2026 18:58:59 GMT</t>
+        </is>
+      </c>
+      <c r="E189" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMi-AJBVV95cUxOd0R3ajlIYVB5bkMwX0N1NjVaQnQ3Nml5RUVEeTlFeWY4Z0Z0Vk51WEhnWUxuc0FicTFranc2VWZzeF83cVJOMkJuZDhwZXEzYXdpZ09WdjBtVmR3SmJDMGpReXctd0NybGl1ZVU5cGRzUGpOY0xOSVZfQ0ZOWDg3XzV4WllMV01IRElUOUFoVF91MXdZaTFFODUwbFFVcHd5d0FuZkdkRlY2THV3YzZWTXBFckc3Zk15OGdLTXd2bnUzSUUxNGFhdGVGUkI0NFNXQ0VSLU9rT2J4N2NzZjVrM0FvTnVyTWktS3FveGVIaW5MZDFRdWYtMVpnYnNXNC1NdUl5bjhPcnpFUEFUUUVack9pTV9YSk5VY3p3SW43Q0ZmQlVtQ0JSUHdVLU9nWjA5VGtOVDlpSHJBbjd1ZE5DQWJQaENRdFpLN0JhZ1JaRWg2QWFKNkZabjNsUHdyUWJ1enNGNElySnpPVVZ0XzlvRGJFSER6eEFz?oc=5</t>
+        </is>
+      </c>
+      <c r="F189" t="n">
+        <v>30</v>
+      </c>
+      <c r="G189" s="1" t="n">
+        <v>46125.79096064815</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/latest_ransomware_news.xlsx
+++ b/data/latest_ransomware_news.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G189"/>
+  <dimension ref="A1:G199"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6661,6 +6661,336 @@
         <v>46125.79096064815</v>
       </c>
     </row>
+    <row r="190">
+      <c r="A190" t="inlineStr">
+        <is>
+          <t>Dragonforce</t>
+        </is>
+      </c>
+      <c r="B190" t="inlineStr">
+        <is>
+          <t>"Dragonforce ransomware" OR "Dragonforce threat actor" OR "Dragonforce cyber attack"</t>
+        </is>
+      </c>
+      <c r="C190" t="inlineStr">
+        <is>
+          <t>DragonForce Ransomware Attack on Champion Homes - DeXpose</t>
+        </is>
+      </c>
+      <c r="D190" t="inlineStr">
+        <is>
+          <t>Tue, 21 Apr 2026 00:00:00 GMT</t>
+        </is>
+      </c>
+      <c r="E190" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMie0FVX3lxTFBuYk1KdVpTUUo5bVBsUE5zc25hY3BrRXdPMjluSTkxWmsyak0temQ1UUdFSWhYTUlJV1VlYi1kQnM0VVlMRi04Zl94cEE4WERsV3ktRU04MEdDRWM1WEZOX0xjNWlGZUJUVGFwaW9RRERGVjlTRGpjLW51OA?oc=5</t>
+        </is>
+      </c>
+      <c r="F190" t="n">
+        <v>30</v>
+      </c>
+      <c r="G190" s="1" t="n">
+        <v>46133</v>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" t="inlineStr">
+        <is>
+          <t>Qilin</t>
+        </is>
+      </c>
+      <c r="B191" t="inlineStr">
+        <is>
+          <t>"Qilin ransomware" OR "Qilin threat actor" OR "Qilin cyber attack"</t>
+        </is>
+      </c>
+      <c r="C191" t="inlineStr">
+        <is>
+          <t>Qilin EDR killer infection chain - Cisco Talos Blog</t>
+        </is>
+      </c>
+      <c r="D191" t="inlineStr">
+        <is>
+          <t>Thu, 02 Apr 2026 07:00:00 GMT</t>
+        </is>
+      </c>
+      <c r="E191" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiYkFVX3lxTE03aDVvVHpVOXQyTG85WnBacWs5V05BNzJLbFVMVFR4NFBDN3czY0NDak5zV2RfZDVISHM3TElBdW5rS0Nwa1g3ci1lYVlyaTVRMV9qdTJkQnlmeTBQd2hpTUpB?oc=5</t>
+        </is>
+      </c>
+      <c r="F191" t="n">
+        <v>30</v>
+      </c>
+      <c r="G191" s="1" t="n">
+        <v>46114.29166666666</v>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" t="inlineStr">
+        <is>
+          <t>Everest</t>
+        </is>
+      </c>
+      <c r="B192" t="inlineStr">
+        <is>
+          <t>"Everest ransomware" OR "Everest threat actor" OR "Everest cyber attack"</t>
+        </is>
+      </c>
+      <c r="C192" t="inlineStr">
+        <is>
+          <t>60K Bitcoin addresses leaked as LockBit ransomware gang gets hacked - MSN</t>
+        </is>
+      </c>
+      <c r="D192" t="inlineStr">
+        <is>
+          <t>Sun, 19 Apr 2026 15:38:00 GMT</t>
+        </is>
+      </c>
+      <c r="E192" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMi1AJBVV95cUxQWXdUWFVQUURMcnlWRXFKemMyV2RUQVB5cVpGdVp6Ylc3amtCNFd5Wm5JQUd6cXFfNkFqSHA3YVY2THhDQ2I1MUFlTkUzRDFVUTZZeXZIeTNSdUJiVExCZHVpYTRKblFIaHFyRVVNTzBnMy12ZXY0VmdESnJDeWRRQ25UcW5EeHNZV09CX25LNmVOeDR3bFBlR0tJSkF4azZkRF9KVUp3dTNYbjBQdkRZbVdGVEl2T21sVFRRWnpvb1VPZF9hRjFuLVVHVHNQWDgwZ09MS21Cck5KZmM2RDJRclZMR1diUC1QbzkzbkdjME0wX0VSUVBGZ0pYZkF2S3RLamROMlBmUVB0N0g4blNXdE9NWkVXbzZyUlFqeFBNY29KcEE5Z2FvUFM3OG9CZmRuM3hNbVgyWmxseDFUM3BlQVlfZFVVUlRfaGR1Q1ZpbENzNjRk?oc=5</t>
+        </is>
+      </c>
+      <c r="F192" t="n">
+        <v>30</v>
+      </c>
+      <c r="G192" s="1" t="n">
+        <v>46131.65138888889</v>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" t="inlineStr">
+        <is>
+          <t>Everest</t>
+        </is>
+      </c>
+      <c r="B193" t="inlineStr">
+        <is>
+          <t>"Everest ransomware" OR "Everest threat actor" OR "Everest cyber attack"</t>
+        </is>
+      </c>
+      <c r="C193" t="inlineStr">
+        <is>
+          <t>Frost Bank, Citizens Bank data leak: Hackers set 6-day deadline for full dump - Cybernews</t>
+        </is>
+      </c>
+      <c r="D193" t="inlineStr">
+        <is>
+          <t>Tue, 21 Apr 2026 14:17:13 GMT</t>
+        </is>
+      </c>
+      <c r="E193" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMigwFBVV95cUxNUWpXLTZIaDdRb1hGQ2JHVE9IUllhaHNzVEpQemRqRGt0Xzh1NWVoOEo4MXVxcU9SN1hZVjFfeHJ0bHN4LTNCeFdRMU1VU2wyRkJ4RmdUa04wd1FaeDRCUFkzZjlXeXdoR0kwQlA4cG9CRm9DOVRiU05NQzFkOXNGbms0aw?oc=5</t>
+        </is>
+      </c>
+      <c r="F193" t="n">
+        <v>30</v>
+      </c>
+      <c r="G193" s="1" t="n">
+        <v>46133.59528935186</v>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" t="inlineStr">
+        <is>
+          <t>TheGentlemen</t>
+        </is>
+      </c>
+      <c r="B194" t="inlineStr">
+        <is>
+          <t>"The Gentlemen ransomware" OR "The Gentlemen threat actor" OR "The Gentlemen cyber attack"</t>
+        </is>
+      </c>
+      <c r="C194" t="inlineStr">
+        <is>
+          <t>DFIR Report – The Gentlemen &amp; SystemBC: A Sneak Peek Behind the Proxy - Check Point Research</t>
+        </is>
+      </c>
+      <c r="D194" t="inlineStr">
+        <is>
+          <t>Mon, 20 Apr 2026 12:59:45 GMT</t>
+        </is>
+      </c>
+      <c r="E194" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMicEFVX3lxTE5TNFo0NVdKT29oOWt4YVlBTlJvYy1rVUwyaVVjWERmVG93UEYxeXlabmxTUkUzNVhJRnJWQXpmTlpIM0l1bVVOaVdKNlcwdWlCV200TkhLclpMMEItTi0yWDhtN0JaaU9lMGdPbnZNLWU?oc=5</t>
+        </is>
+      </c>
+      <c r="F194" t="n">
+        <v>30</v>
+      </c>
+      <c r="G194" s="1" t="n">
+        <v>46132.54149305556</v>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" t="inlineStr">
+        <is>
+          <t>Medusa</t>
+        </is>
+      </c>
+      <c r="B195" t="inlineStr">
+        <is>
+          <t>"Medusa ransomware" OR "Medusa threat actor" OR "Medusa cyber attack"</t>
+        </is>
+      </c>
+      <c r="C195" t="inlineStr">
+        <is>
+          <t>Ninja Forms – File Upload: Vulnerability Puts Thousands of WordPress Sites at Risk - SecNews.gr</t>
+        </is>
+      </c>
+      <c r="D195" t="inlineStr">
+        <is>
+          <t>Tue, 07 Apr 2026 11:48:00 GMT</t>
+        </is>
+      </c>
+      <c r="E195" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMigwFBVV95cUxQaUh3ankyVndaMzk5WHpRSTlaWHBMY1BCMzdrdXl3aXNKV1B2ZlYtQkFXaXRMNzI3QnF0RGU0cl9kWVhyczVlUjBUTkhPNE5lLUpsX3NlT0ZqTGhWUmRFSEp1ZWhBOXU5SVhYV3V1NXZDclNoTkJVZTlOMlBtYnI5YWVrbw?oc=5</t>
+        </is>
+      </c>
+      <c r="F195" t="n">
+        <v>30</v>
+      </c>
+      <c r="G195" s="1" t="n">
+        <v>46119.49166666667</v>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" t="inlineStr">
+        <is>
+          <t>Interlock</t>
+        </is>
+      </c>
+      <c r="B196" t="inlineStr">
+        <is>
+          <t>"Interlock ransomware" OR "Interlock threat actor" OR "Interlock cyber attack"</t>
+        </is>
+      </c>
+      <c r="C196" t="inlineStr">
+        <is>
+          <t>March 2026 CVE Landscape: 31 High-Impact Vulnerabilities Identified, Interlock Ransomware Group Exploits Cisco FMC Zero-Day - Recorded Future</t>
+        </is>
+      </c>
+      <c r="D196" t="inlineStr">
+        <is>
+          <t>Mon, 13 Apr 2026 17:56:08 GMT</t>
+        </is>
+      </c>
+      <c r="E196" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMibEFVX3lxTE5jT3dKNGlENm5NemlhRWhfeUZuMTRyWkNHenU3ZXA0VXlDT2w3NV9wN2xWcGZScEpUenVTMUYxdXcwMlV5RUkxZXhDREFyQ2RFN1FkeGduZzM0dTZGOHh4NDRkMzE3b2I1emd1Zw?oc=5</t>
+        </is>
+      </c>
+      <c r="F196" t="n">
+        <v>30</v>
+      </c>
+      <c r="G196" s="1" t="n">
+        <v>46125.74731481481</v>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" t="inlineStr">
+        <is>
+          <t>Interlock</t>
+        </is>
+      </c>
+      <c r="B197" t="inlineStr">
+        <is>
+          <t>"Interlock ransomware" OR "Interlock threat actor" OR "Interlock cyber attack"</t>
+        </is>
+      </c>
+      <c r="C197" t="inlineStr">
+        <is>
+          <t>RedSun Zero-Day: New Microsoft Defender Vulnerability - SecNews.gr</t>
+        </is>
+      </c>
+      <c r="D197" t="inlineStr">
+        <is>
+          <t>Fri, 17 Apr 2026 08:32:21 GMT</t>
+        </is>
+      </c>
+      <c r="E197" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMigAFBVV95cUxQQUU4UFZNd0RzcGhnOGFURThuV1k4dEE4NTJYMktxcU5od056cmdmTlVGYzdGVXNqWDJ1N2d2U0VuMVRXeDNHVFRpVEFJQVFQN2hsNFh1c3JXSkNpR09tTmdYaGdVOFN4SmVRTHltVmpyRlhlREVjMnBNRlBMUFh6Nw?oc=5</t>
+        </is>
+      </c>
+      <c r="F197" t="n">
+        <v>30</v>
+      </c>
+      <c r="G197" s="1" t="n">
+        <v>46129.35579861111</v>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" t="inlineStr">
+        <is>
+          <t>Safepay</t>
+        </is>
+      </c>
+      <c r="B198" t="inlineStr">
+        <is>
+          <t>"Safepay ransomware" OR "Safepay threat actor" OR "Safepay cyber attack"</t>
+        </is>
+      </c>
+      <c r="C198" t="inlineStr">
+        <is>
+          <t>Exclusive: Aussie passports compromised in alleged Favelle Favco data breach - Cyber Daily</t>
+        </is>
+      </c>
+      <c r="D198" t="inlineStr">
+        <is>
+          <t>Wed, 22 Apr 2026 02:52:25 GMT</t>
+        </is>
+      </c>
+      <c r="E198" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMitwFBVV95cUxQNHRLZ2Z2WU1JWFFac3pOQXk2Q3hfSFZveFNZMzhtd1V0alZETi14R0l6dTd3U2JxOE94NnMxYXJDSlpYY0ctOHQ3YXZQTmdrQWZicjBoS1lvZmtfYXltaUxuUFlGQjlRLXM1MUYtMlJZeEtVWmZ0dTRkYnNNeWx4Q2QyMWdNSGFKQWZTR3BmRFdjSEVEVHR1WGJXZWpQamxvaWRRMVF1U0M5NE1PV0J2T2Y0aEZxd1E?oc=5</t>
+        </is>
+      </c>
+      <c r="F198" t="n">
+        <v>30</v>
+      </c>
+      <c r="G198" s="1" t="n">
+        <v>46134.11973379629</v>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" t="inlineStr">
+        <is>
+          <t>Safepay</t>
+        </is>
+      </c>
+      <c r="B199" t="inlineStr">
+        <is>
+          <t>"Safepay ransomware" OR "Safepay threat actor" OR "Safepay cyber attack"</t>
+        </is>
+      </c>
+      <c r="C199" t="inlineStr">
+        <is>
+          <t>Court Rules State Regulator’s Investigation of Blue Cross Blue Shield of Montana May Proceed - The HIPAA Journal</t>
+        </is>
+      </c>
+      <c r="D199" t="inlineStr">
+        <is>
+          <t>Tue, 21 Apr 2026 09:55:49 GMT</t>
+        </is>
+      </c>
+      <c r="E199" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMihAFBVV95cUxQYTF6UXk1cVhMWW5MRkxmU2JOckw0LWp5eHNXN19JMEVSaWxacm9kSWZvMF96T0NicVh3eVRNblZxYUVnWG00RTNTQUFUMHlmZDdIbGtmYW9sbWFFcGhJb3lNR3NvUFpWbUczbTNzV2hwU0Q1QkRSUTRnNGpwOU5pZWhxSTM?oc=5</t>
+        </is>
+      </c>
+      <c r="F199" t="n">
+        <v>30</v>
+      </c>
+      <c r="G199" s="1" t="n">
+        <v>46133.41376157408</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/latest_ransomware_news.xlsx
+++ b/data/latest_ransomware_news.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G199"/>
+  <dimension ref="A1:G207"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6991,6 +6991,270 @@
         <v>46133.41376157408</v>
       </c>
     </row>
+    <row r="200">
+      <c r="A200" t="inlineStr">
+        <is>
+          <t>Dragonforce</t>
+        </is>
+      </c>
+      <c r="B200" t="inlineStr">
+        <is>
+          <t>"Dragonforce ransomware" OR "Dragonforce threat actor" OR "Dragonforce cyber attack"</t>
+        </is>
+      </c>
+      <c r="C200" t="inlineStr">
+        <is>
+          <t>DragonForce Ransomware Attack on Wm. Sopko &amp; Sons Co. - DeXpose</t>
+        </is>
+      </c>
+      <c r="D200" t="inlineStr">
+        <is>
+          <t>Tue, 28 Apr 2026 00:39:05 GMT</t>
+        </is>
+      </c>
+      <c r="E200" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMifkFVX3lxTE1HRkRkakZrU2JBNkI2bXlZbzIzSGlwQW1ReE9wMTE4cW9kNlJMdlhOQ205VlNVNDZ3UkhFeXR5Z05SeGRhSVJoMnFvemIySnk1M2daZHhyclMxQWhycGMtRGdBLXNGb0lkQzQxSEJkNk1LMlhkdXJZWmt3XzY5Zw?oc=5</t>
+        </is>
+      </c>
+      <c r="F200" t="n">
+        <v>30</v>
+      </c>
+      <c r="G200" s="1" t="n">
+        <v>46140.0271412037</v>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" t="inlineStr">
+        <is>
+          <t>Dragonforce</t>
+        </is>
+      </c>
+      <c r="B201" t="inlineStr">
+        <is>
+          <t>"Dragonforce ransomware" OR "Dragonforce threat actor" OR "Dragonforce cyber attack"</t>
+        </is>
+      </c>
+      <c r="C201" t="inlineStr">
+        <is>
+          <t>CISA KEV: 4 Exploited CVEs — SimpleHelp, Samsung MagicINFO, D-Link — May 8 Deadline - abhs.in</t>
+        </is>
+      </c>
+      <c r="D201" t="inlineStr">
+        <is>
+          <t>Sat, 25 Apr 2026 18:24:00 GMT</t>
+        </is>
+      </c>
+      <c r="E201" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMipAFBVV95cUxOcy1Na1FuVmhYT3JqVE00MzZWWFQxVWhQdzF4RW8zWmNxYlZIRnI1dVl2amNCLWl3bVRZUHdGd0NJUkcwU1JWVTQ1TGJ4NERXbTA1dWxUb3A3clI5clJlaTZIYjVHdkVET2EzQ3MySjlBRF8xSjRXVEQ1eFJ0VzFBQWRTbjlHRjRra1NGY25JNVE4ME55QjVXSEFVODBfMW42c25KMQ?oc=5</t>
+        </is>
+      </c>
+      <c r="F201" t="n">
+        <v>30</v>
+      </c>
+      <c r="G201" s="1" t="n">
+        <v>46137.76666666667</v>
+      </c>
+    </row>
+    <row r="202">
+      <c r="A202" t="inlineStr">
+        <is>
+          <t>Akira</t>
+        </is>
+      </c>
+      <c r="B202" t="inlineStr">
+        <is>
+          <t>"Akira ransomware" OR "Akira threat actor" OR "Akira cyber attack"</t>
+        </is>
+      </c>
+      <c r="C202" t="inlineStr">
+        <is>
+          <t>1 in 3 Ransomware Claims Started with SonicWall in 2025 as VPN Attacks Nearly Double in Two Years - Morningstar</t>
+        </is>
+      </c>
+      <c r="D202" t="inlineStr">
+        <is>
+          <t>Wed, 22 Apr 2026 12:00:00 GMT</t>
+        </is>
+      </c>
+      <c r="E202" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMi8AFBVV95cUxNdTFlVEJQcTFjdFBwUUNnQWpFMFpiUmRONGxIbVVnZ1NDYjJCbTFFTFVhMWMtZXJlQ0lsUF9kdXZCX1NJSlBiVDJGZllRTzlHbDdkenkyWGZwYmFyb1VFbEhZR3QteXR4VkhQcjlOSExMM29BZUpQWWNlbEhBN2NBYTRoY1dtc0ZwaG42eC1rVGZqeGV0VHJMNUdhY2lYNDJQSXNtN3JGWUhUMy0yTUc2V19ydTVrZldiT2hWVHk5bnVtR0ozVTIwVnJBejV1RnJfU0VhTnQ2WGNIV3N4a1JQQjE2bUctb002S1JxMEktOXQ?oc=5</t>
+        </is>
+      </c>
+      <c r="F202" t="n">
+        <v>30</v>
+      </c>
+      <c r="G202" s="1" t="n">
+        <v>46134.5</v>
+      </c>
+    </row>
+    <row r="203">
+      <c r="A203" t="inlineStr">
+        <is>
+          <t>TheGentlemen</t>
+        </is>
+      </c>
+      <c r="B203" t="inlineStr">
+        <is>
+          <t>"The Gentlemen ransomware" OR "The Gentlemen threat actor" OR "The Gentlemen cyber attack"</t>
+        </is>
+      </c>
+      <c r="C203" t="inlineStr">
+        <is>
+          <t>Gentlemen RaaS Adds C-Based ESXi Locker To Cross-Platform Attacks - cyberpress.org</t>
+        </is>
+      </c>
+      <c r="D203" t="inlineStr">
+        <is>
+          <t>Wed, 22 Apr 2026 06:38:36 GMT</t>
+        </is>
+      </c>
+      <c r="E203" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiX0FVX3lxTE5ZLWc2YklCS3JybDhJaE9qMi15U3Q3b2ptWUtHTzRzTEw2OHQ5MDh3Nmx6MjVvYTMyeVRaTkx6UUVBaElvdjV4dFNTZ0NUN2tYdUJodjlKZUNCaEtCT180?oc=5</t>
+        </is>
+      </c>
+      <c r="F203" t="n">
+        <v>30</v>
+      </c>
+      <c r="G203" s="1" t="n">
+        <v>46134.27680555556</v>
+      </c>
+    </row>
+    <row r="204">
+      <c r="A204" t="inlineStr">
+        <is>
+          <t>TheGentlemen</t>
+        </is>
+      </c>
+      <c r="B204" t="inlineStr">
+        <is>
+          <t>"The Gentlemen ransomware" OR "The Gentlemen threat actor" OR "The Gentlemen cyber attack"</t>
+        </is>
+      </c>
+      <c r="C204" t="inlineStr">
+        <is>
+          <t>One Click and Your Phone Is Gone: Fake Update Scam Targets Vivo and iQOO Users - The420.in</t>
+        </is>
+      </c>
+      <c r="D204" t="inlineStr">
+        <is>
+          <t>Tue, 21 Apr 2026 09:43:01 GMT</t>
+        </is>
+      </c>
+      <c r="E204" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMimAFBVV95cUxNd2JvRkE5MktUTkNYWnFlcGZfS3ZvVTNLZ2FCeVhSTENQeGlCcEpxcFdhTkpxY1V2am81c0R6alloYm1KOWV4MlZFZG1TV1BmdjNrWEtrZk1WVU1sY01tdUdhTzA5bHpFcF9lelU0dVhpU1FrWWliamJGU0tvcUFXVmVVNUpzemxVZUtGbngweFZGSEFTdEJENA?oc=5</t>
+        </is>
+      </c>
+      <c r="F204" t="n">
+        <v>30</v>
+      </c>
+      <c r="G204" s="1" t="n">
+        <v>46133.40487268518</v>
+      </c>
+    </row>
+    <row r="205">
+      <c r="A205" t="inlineStr">
+        <is>
+          <t>Cl0p</t>
+        </is>
+      </c>
+      <c r="B205" t="inlineStr">
+        <is>
+          <t>"Cl0p ransomware" OR "Cl0p threat actor" OR "Cl0p cyber attack"</t>
+        </is>
+      </c>
+      <c r="C205" t="inlineStr">
+        <is>
+          <t>Google says hackers are sending extortion emails to executives - MSN</t>
+        </is>
+      </c>
+      <c r="D205" t="inlineStr">
+        <is>
+          <t>Tue, 28 Apr 2026 03:25:42 GMT</t>
+        </is>
+      </c>
+      <c r="E205" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMixwJBVV95cUxNNjhpb0VqUWtuMDdvNEh5X09QNkEyZjV0bjdtMnhqUXJfU1BWMmZPa3B4a1RGUmY4RENWYm0zckE2bVQ3c1ZUNVZjUWlvdnlGNl9CampKZVZYSXlZcVk0ejhzUzBQd2s3aGt1MF9ESjIxZUpUZ2x4TjdCUGFkSC1PRUxoUG5tQjBQVDVzeG1Hd0VncmRqSTRVeUxEQ2RzQnVweHY2MTJKcXhYS1FtTmszTWYtVVFQVVdRdUU0U2lfd0lGdjZXQmxVS25Qa0YxMDc4ZWg0Vkl0TVR1YUNlSzFfZ29aYjRYcG82YUxQbndvaHA2V3ZYWkNvQnM0QmpEUUJpakdlYzlzQ0ZsWkhBLVhhLU9nb0JjMzhEbDRZRE5JWkJlS0Q4dWRlWUFBRVdHaE9pdkE1NFBGN2hXQ2FjODlNeXBaRTV2dnM?oc=5</t>
+        </is>
+      </c>
+      <c r="F205" t="n">
+        <v>30</v>
+      </c>
+      <c r="G205" s="1" t="n">
+        <v>46140.14284722223</v>
+      </c>
+    </row>
+    <row r="206">
+      <c r="A206" t="inlineStr">
+        <is>
+          <t>Interlock</t>
+        </is>
+      </c>
+      <c r="B206" t="inlineStr">
+        <is>
+          <t>"Interlock ransomware" OR "Interlock threat actor" OR "Interlock cyber attack"</t>
+        </is>
+      </c>
+      <c r="C206" t="inlineStr">
+        <is>
+          <t>Cisco FMC Zero-Day Among 31 High-Impact Vulnerabilities Exploited in March - gbhackers.com</t>
+        </is>
+      </c>
+      <c r="D206" t="inlineStr">
+        <is>
+          <t>Thu, 16 Apr 2026 07:00:00 GMT</t>
+        </is>
+      </c>
+      <c r="E206" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiU0FVX3lxTE4tVUs1dUxOWlVjUWt0TEpTdm8zN0NpcW9rWlFPemVlanBtVEtCZFRkakcxYlV6OXUtVzBhVWkwcjBtUlNQNVp5RXFfNDAtamFBbUNF?oc=5</t>
+        </is>
+      </c>
+      <c r="F206" t="n">
+        <v>30</v>
+      </c>
+      <c r="G206" s="1" t="n">
+        <v>46128.29166666666</v>
+      </c>
+    </row>
+    <row r="207">
+      <c r="A207" t="inlineStr">
+        <is>
+          <t>Safepay</t>
+        </is>
+      </c>
+      <c r="B207" t="inlineStr">
+        <is>
+          <t>"Safepay ransomware" OR "Safepay threat actor" OR "Safepay cyber attack"</t>
+        </is>
+      </c>
+      <c r="C207" t="inlineStr">
+        <is>
+          <t>Heavy-lift crane maker Favelle Favco faces 237GB data leak - Insurance Business</t>
+        </is>
+      </c>
+      <c r="D207" t="inlineStr">
+        <is>
+          <t>Wed, 22 Apr 2026 08:58:00 GMT</t>
+        </is>
+      </c>
+      <c r="E207" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMivAFBVV95cUxPaTBRN3JyLXoxZ3JkZS1obUdTZzlfWk9sMFBIeUxvQnVfVE5nclVxQVJGYUlqRk5aVHpZbDJsMTE3eUlQbmNXZXRKS2pHLWczeGtOWHg5ZjhNaFc1d1N5R2Zmc0R3R08wYVJIYTZzM3VaOUV3QXZocEFIakJVOG5aaEZPLThKakN3YVpEa0ZQLVVUWVdXNlByS0hpZVJLTW5faF9TdXVZQXJfeGcyOUo2ZkxFbWU2X1dOMUFKVw?oc=5</t>
+        </is>
+      </c>
+      <c r="F207" t="n">
+        <v>30</v>
+      </c>
+      <c r="G207" s="1" t="n">
+        <v>46134.37361111111</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/latest_ransomware_news.xlsx
+++ b/data/latest_ransomware_news.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G207"/>
+  <dimension ref="A1:G215"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -7255,6 +7255,270 @@
         <v>46134.37361111111</v>
       </c>
     </row>
+    <row r="208">
+      <c r="A208" t="inlineStr">
+        <is>
+          <t>Dragonforce</t>
+        </is>
+      </c>
+      <c r="B208" t="inlineStr">
+        <is>
+          <t>"Dragonforce ransomware" OR "Dragonforce threat actor" OR "Dragonforce cyber attack"</t>
+        </is>
+      </c>
+      <c r="C208" t="inlineStr">
+        <is>
+          <t>Cyber Crime - Dragonforce ransomware group targets Australian gelato giant Gelatissimo - teiss</t>
+        </is>
+      </c>
+      <c r="D208" t="inlineStr">
+        <is>
+          <t>Fri, 01 May 2026 07:00:00 GMT</t>
+        </is>
+      </c>
+      <c r="E208" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMitAFBVV95cUxPOVd3QXh4LWF3dkg1X2FwVUlaY09pMzZ1azNjOFZkaGhpdVQ2cHlVMS1RMXAxWDlEdFRMbzlzZlE4MEh4NWlVd2xMTU9BcW1hTWxTMjhFbE04eHVfYUZNYnI2VkVHV3l2bFY3aGNaWVRXUFI3aV9peGY0ZkQ3TlI2YkZvM2NrNFdTT2pKd3QwZnVJUnpZbEt3clZVLVJ0a0ZFN2dDM19OVGNlamJDOU1YalFodnA?oc=5</t>
+        </is>
+      </c>
+      <c r="F208" t="n">
+        <v>30</v>
+      </c>
+      <c r="G208" s="1" t="n">
+        <v>46143.29166666666</v>
+      </c>
+    </row>
+    <row r="209">
+      <c r="A209" t="inlineStr">
+        <is>
+          <t>Dragonforce</t>
+        </is>
+      </c>
+      <c r="B209" t="inlineStr">
+        <is>
+          <t>"Dragonforce ransomware" OR "Dragonforce threat actor" OR "Dragonforce cyber attack"</t>
+        </is>
+      </c>
+      <c r="C209" t="inlineStr">
+        <is>
+          <t>DragonForce Ransomware Attack on Cult Wines - DeXpose</t>
+        </is>
+      </c>
+      <c r="D209" t="inlineStr">
+        <is>
+          <t>Tue, 05 May 2026 00:00:00 GMT</t>
+        </is>
+      </c>
+      <c r="E209" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMidkFVX3lxTE1lWGRvUW5EczNockZBWHhnQzM5LXlkbVJqdHhBNjdBRjh0WVR3TG51MkFEazQ2ZjZKZ2czNmdvSlNCUVUxTUJQOHc0WklVbDYtd2llb0FrQlY3ODVwTEljclFpVURkNDRIZ2FNSmlnb3luU3AtbHc?oc=5</t>
+        </is>
+      </c>
+      <c r="F209" t="n">
+        <v>30</v>
+      </c>
+      <c r="G209" s="1" t="n">
+        <v>46147</v>
+      </c>
+    </row>
+    <row r="210">
+      <c r="A210" t="inlineStr">
+        <is>
+          <t>Dragonforce</t>
+        </is>
+      </c>
+      <c r="B210" t="inlineStr">
+        <is>
+          <t>"Dragonforce ransomware" OR "Dragonforce threat actor" OR "Dragonforce cyber attack"</t>
+        </is>
+      </c>
+      <c r="C210" t="inlineStr">
+        <is>
+          <t>Exclusive: Champion Homes confirms customer data compromised in ‘cyber event’ - Cyber Daily</t>
+        </is>
+      </c>
+      <c r="D210" t="inlineStr">
+        <is>
+          <t>Tue, 05 May 2026 05:02:48 GMT</t>
+        </is>
+      </c>
+      <c r="E210" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMitgFBVV95cUxOVUdWMWR0WnFlSnhMNkNxNU90ZGwyUTB1Uk5ISlJiQThmeVdQTlFQN1RrTlNRVS13RGphNGdJQXVJZnNuY1B3dllpdUNHdW9iSUlUcnFxeHU3M2czZzdJU2lFQVdNaGxUc2tncENJZkl4N05fYm1RVTlBUWRlb29CcVlaTDlXWldIVW9qTnlzdW9YQ2dIWWlBSUlvQ1k5enMxY3FzeEhUUll4ejNyV1ByOU9WNVRtdw?oc=5</t>
+        </is>
+      </c>
+      <c r="F210" t="n">
+        <v>30</v>
+      </c>
+      <c r="G210" s="1" t="n">
+        <v>46147.21027777778</v>
+      </c>
+    </row>
+    <row r="211">
+      <c r="A211" t="inlineStr">
+        <is>
+          <t>Dragonforce</t>
+        </is>
+      </c>
+      <c r="B211" t="inlineStr">
+        <is>
+          <t>"Dragonforce ransomware" OR "Dragonforce threat actor" OR "Dragonforce cyber attack"</t>
+        </is>
+      </c>
+      <c r="C211" t="inlineStr">
+        <is>
+          <t>News - JC Resorts data breach compromised close to 6,000 individuals - teiss</t>
+        </is>
+      </c>
+      <c r="D211" t="inlineStr">
+        <is>
+          <t>Wed, 29 Apr 2026 07:00:00 GMT</t>
+        </is>
+      </c>
+      <c r="E211" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMimwFBVV95cUxQUE44d3hnRWUxc3N4Zk5CZ1JyLUdwaW0yREZicHNzQW0zY1B1V1BWT1pVWjRQVGhxNnBTQkFydHRha01yUXJTem5WYVNobzlqUkY4UU9FN0hHci1NRXVWOFhPcHBtWkl0YnkwemtDQkR5TDh2ZDRrbDFBWm1wU0l0ZzBBangta1NHZWZpT3A0bHQxYXI1ODEyZzBOMA?oc=5</t>
+        </is>
+      </c>
+      <c r="F211" t="n">
+        <v>30</v>
+      </c>
+      <c r="G211" s="1" t="n">
+        <v>46141.29166666666</v>
+      </c>
+    </row>
+    <row r="212">
+      <c r="A212" t="inlineStr">
+        <is>
+          <t>Akira</t>
+        </is>
+      </c>
+      <c r="B212" t="inlineStr">
+        <is>
+          <t>"Akira ransomware" OR "Akira threat actor" OR "Akira cyber attack"</t>
+        </is>
+      </c>
+      <c r="C212" t="inlineStr">
+        <is>
+          <t>Conti, Akira ransomware affiliate given 8-year sentence - The Record from Recorded Future News</t>
+        </is>
+      </c>
+      <c r="D212" t="inlineStr">
+        <is>
+          <t>Tue, 05 May 2026 17:40:45 GMT</t>
+        </is>
+      </c>
+      <c r="E212" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMidEFVX3lxTE1QVnRFNVdjS1BJSGFuWHg3NXdXdXRtM3ZyamJpUTNocmctT1VHY0JkTjY3U1JPVTRkeldWWlVqNGM2WXdvOVVfdVdSVFk4OWUzMFZnX1I5M2RkbldVdXp4RDZpUElqcXgyS1lnelJYQUV2azR6?oc=5</t>
+        </is>
+      </c>
+      <c r="F212" t="n">
+        <v>30</v>
+      </c>
+      <c r="G212" s="1" t="n">
+        <v>46147.73663194444</v>
+      </c>
+    </row>
+    <row r="213">
+      <c r="A213" t="inlineStr">
+        <is>
+          <t>Akira</t>
+        </is>
+      </c>
+      <c r="B213" t="inlineStr">
+        <is>
+          <t>"Akira ransomware" OR "Akira threat actor" OR "Akira cyber attack"</t>
+        </is>
+      </c>
+      <c r="C213" t="inlineStr">
+        <is>
+          <t>1 in 3 Ransomware Claims Started with SonicWall in 2025 as VPN Attacks Nearly Double in Two Years - Business Wire</t>
+        </is>
+      </c>
+      <c r="D213" t="inlineStr">
+        <is>
+          <t>Wed, 22 Apr 2026 07:00:00 GMT</t>
+        </is>
+      </c>
+      <c r="E213" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMi6gFBVV95cUxQN0xyRXZzTklWaVV3MmptX0g3Q0hxNENtLWFTa1A2MHNtYWU4bzZ0SF93aWNTd2lSTGFXQV9ZamRsUi1CX2NadDRIMXZ4OHN3TzIzNndRbkRvalh6T1ZuTXVNTmNuLVVjM2c0SXJ1cmtBN1lIRXJCQmJPX3BPTGtFZHNPNGJrbzduNThmdEctTWhWaXliakNJSnhYZ0RyQi1aY2tsVGZFOFEzS2VvV1hlbVg4TWJuSExYTmJVVHppZlVvSVNZYnkwZnNDZFMzS1dBeV83bWtJOWpIWHZHVVo4eUF0RGpMRHAtZXc?oc=5</t>
+        </is>
+      </c>
+      <c r="F213" t="n">
+        <v>30</v>
+      </c>
+      <c r="G213" s="1" t="n">
+        <v>46134.29166666666</v>
+      </c>
+    </row>
+    <row r="214">
+      <c r="A214" t="inlineStr">
+        <is>
+          <t>Everest</t>
+        </is>
+      </c>
+      <c r="B214" t="inlineStr">
+        <is>
+          <t>"Everest ransomware" OR "Everest threat actor" OR "Everest cyber attack"</t>
+        </is>
+      </c>
+      <c r="C214" t="inlineStr">
+        <is>
+          <t>Did Ryanair's dirty laundry just hit hacker forums? Attackers claim to sell court documents and passenger data - Cybernews</t>
+        </is>
+      </c>
+      <c r="D214" t="inlineStr">
+        <is>
+          <t>Tue, 28 Apr 2026 09:03:43 GMT</t>
+        </is>
+      </c>
+      <c r="E214" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiakFVX3lxTFBpLU8yM0paTnl6ZGhqUHVacHNjaHBRcm00bE1PUnJIMDVCOTY4WFVfdGUwcXNlQXVpMm9MUk9lVnhYRllQSTNEX0FoNVl0SkJaM1JKNE5UZEFuRzVzS3VOYUVMSDVpdWltUUE?oc=5</t>
+        </is>
+      </c>
+      <c r="F214" t="n">
+        <v>30</v>
+      </c>
+      <c r="G214" s="1" t="n">
+        <v>46140.37758101852</v>
+      </c>
+    </row>
+    <row r="215">
+      <c r="A215" t="inlineStr">
+        <is>
+          <t>TheGentlemen</t>
+        </is>
+      </c>
+      <c r="B215" t="inlineStr">
+        <is>
+          <t>"The Gentlemen ransomware" OR "The Gentlemen threat actor" OR "The Gentlemen cyber attack"</t>
+        </is>
+      </c>
+      <c r="C215" t="inlineStr">
+        <is>
+          <t>SystemBC C2 Server Reveals 1,570+ Victims in The Gentlemen Ransomware Operation - The Hacker News</t>
+        </is>
+      </c>
+      <c r="D215" t="inlineStr">
+        <is>
+          <t>Tue, 21 Apr 2026 07:00:00 GMT</t>
+        </is>
+      </c>
+      <c r="E215" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMihAFBVV95cUxNRy1Benh3RDFCTzJqY0pXOEJxX01OSWh2Nmtqc2V4aHRUYVIxdGZqbmtPVWxGOElfZFA3OTVVaGxpeU5DS0t3MDZjSGJIUVI1Y3h5SURCbWI4ck1nWjZ3SGtOeWNzLW43S3p2N1VleEotRjN5RjNDM2NLLTIzeHRXbXZESGU?oc=5</t>
+        </is>
+      </c>
+      <c r="F215" t="n">
+        <v>30</v>
+      </c>
+      <c r="G215" s="1" t="n">
+        <v>46133.29166666666</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
